--- a/Documents/タスク編集設計書.xlsx
+++ b/Documents/タスク編集設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A1D60E-AC8B-4DFD-A6EB-58780888184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FEFF19-9658-495A-9BEE-A79274493329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="9" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="範囲１" localSheetId="6">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
@@ -1832,6 +1829,42 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="62" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="67" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1856,6 +1889,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1889,21 +1967,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1949,36 +2012,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2045,6 +2078,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2054,44 +2126,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2099,38 +2156,74 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2153,113 +2246,17 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="62" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="67" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2341,22 +2338,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>61176</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E50DE7E-6A27-61A4-EA4A-43806E766AEA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DF87EDC-3920-874D-81D8-273272731798}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2378,8 +2375,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="923925"/>
-          <a:ext cx="7772400" cy="4648200"/>
+          <a:off x="390525" y="1200150"/>
+          <a:ext cx="7772400" cy="3337776"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2958,24 +2955,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="JUnitテスト仕様書兼報告書"/>
-      <sheetName val="別紙"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3183,85 +3162,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3281,46 +3260,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="48" t="s">
+      <c r="H13" s="62"/>
+      <c r="I13" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="48"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="48"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3329,13 +3308,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4350,19 +4329,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="95"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="64"/>
+      <c r="G1" s="91"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4374,190 +4353,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="E2" s="105"/>
+      <c r="F2" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
+      <c r="G2" s="105"/>
+      <c r="H2" s="108">
         <v>45806</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="87"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="100"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="88"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="66"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="93"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70" t="s">
+      <c r="B6" s="69"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="71"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="70" t="s">
+      <c r="B7" s="69"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="71"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70" t="s">
+      <c r="B8" s="69"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="71"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="91" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="71"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90" t="s">
+      <c r="A10" s="79"/>
+      <c r="B10" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="71"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="89"/>
-      <c r="B11" s="90" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="91" t="s">
+      <c r="C11" s="70"/>
+      <c r="D11" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="71"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="70" t="s">
+      <c r="B12" s="69"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="71"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="93"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="96"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5548,6 +5527,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5563,18 +5554,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5594,19 +5573,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="95"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="64"/>
+      <c r="G1" s="91"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -5618,48 +5597,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="E2" s="105"/>
+      <c r="F2" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
+      <c r="G2" s="105"/>
+      <c r="H2" s="108">
         <v>45806</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="83" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="87"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="100"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="88"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -7016,19 +6995,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="126"/>
+      <c r="F1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="126"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7040,48 +7019,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="120"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115" t="s">
+      <c r="E2" s="128"/>
+      <c r="F2" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="128"/>
+      <c r="H2" s="110">
         <v>45810</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="114"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="115"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="122"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="116"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -8432,19 +8411,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="126"/>
+      <c r="F1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="126"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -8456,190 +8435,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="120"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115">
+      <c r="E2" s="128"/>
+      <c r="F2" s="127">
         <v>56</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="128"/>
+      <c r="H2" s="110">
         <v>45810</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="114"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="115"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="108"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="103"/>
+      <c r="A4" s="120"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="115"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="128" t="s">
+      <c r="B5" s="132"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="129"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="136"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="124"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="137"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="130"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="132"/>
+      <c r="A7" s="138"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="140"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="108"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="133"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="141"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="108"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="133"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="141"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="133"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="141"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="133"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="141"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="108"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="133"/>
+      <c r="A12" s="120"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="141"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="108"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="133"/>
+      <c r="A13" s="120"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="141"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="124"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="137"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="123" t="s">
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -8648,11 +8627,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -8665,18 +8644,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="134" t="s">
+      <c r="H16" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="124"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="137"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="122">
+      <c r="A17" s="133">
         <v>1</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="16" t="s">
         <v>71</v>
       </c>
@@ -8689,16 +8668,16 @@
       <c r="G17" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="123"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="124"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="137"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="122">
+      <c r="A18" s="133">
         <v>2</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
       <c r="D18" s="16" t="s">
         <v>77</v>
       </c>
@@ -8711,16 +8690,16 @@
       <c r="G18" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H18" s="123"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="124"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="137"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="122">
+      <c r="A19" s="133">
         <v>3</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="62"/>
       <c r="D19" s="16" t="s">
         <v>78</v>
       </c>
@@ -8733,16 +8712,16 @@
       <c r="G19" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="123"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="124"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="137"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="122">
+      <c r="A20" s="133">
         <v>4</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
       <c r="D20" s="16" t="s">
         <v>79</v>
       </c>
@@ -8755,16 +8734,16 @@
       <c r="G20" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="123"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="124"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="137"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="122">
+      <c r="A21" s="133">
         <v>5</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
       <c r="D21" s="16" t="s">
         <v>80</v>
       </c>
@@ -8777,16 +8756,16 @@
       <c r="G21" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="123"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="124"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="137"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="122">
+      <c r="A22" s="133">
         <v>6</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="16" t="s">
         <v>73</v>
       </c>
@@ -8799,16 +8778,16 @@
       <c r="G22" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H22" s="123"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="124"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="137"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="122">
+      <c r="A23" s="133">
         <v>7</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="62"/>
       <c r="D23" s="18" t="s">
         <v>73</v>
       </c>
@@ -8821,9 +8800,9 @@
       <c r="G23" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="119"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="121"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="146"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9804,11 +9783,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9825,16 +9809,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9854,186 +9833,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="113" t="s">
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="113" t="s">
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="113" t="s">
+      <c r="P1" s="126"/>
+      <c r="Q1" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="114"/>
-      <c r="S1" s="113" t="s">
+      <c r="R1" s="126"/>
+      <c r="S1" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="129"/>
+      <c r="T1" s="136"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="115" t="s">
+      <c r="A2" s="120"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="115" t="s">
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="115"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="132"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="128"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="140"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="133"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="129"/>
+      <c r="R3" s="121"/>
+      <c r="S3" s="129"/>
+      <c r="T3" s="141"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="145"/>
+      <c r="A4" s="122"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="130"/>
+      <c r="T4" s="152"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="131" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="142" t="s">
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
-      <c r="M5" s="126"/>
-      <c r="N5" s="126"/>
-      <c r="O5" s="126"/>
-      <c r="P5" s="126"/>
-      <c r="Q5" s="126"/>
-      <c r="R5" s="126"/>
-      <c r="S5" s="126"/>
-      <c r="T5" s="129"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="132"/>
+      <c r="T5" s="136"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="123" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="124"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="137"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="123" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="142" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="124"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="137"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -10232,37 +10211,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="144" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="134" t="s">
+      <c r="D15" s="62"/>
+      <c r="E15" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="134" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="134" t="s">
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="143" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="134" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="143" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="49"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="134" t="s">
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="143" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="50"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="62"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -10274,35 +10253,35 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="56.25" customHeight="1">
-      <c r="A16" s="135">
+      <c r="A16" s="155">
         <v>1</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="136" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="156" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="136" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="143" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="147" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="140" t="s">
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="147"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="M16" s="49"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="140" t="s">
+      <c r="M16" s="61"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="150" t="s">
         <v>109</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="62"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -10314,29 +10293,29 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="135">
+      <c r="A17" s="155">
         <v>2</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="136" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="136" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="143"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="140"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="140"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -10348,23 +10327,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="135"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="136"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="143"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="140"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="140"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="150"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="150"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -10376,23 +10355,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="135"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="143"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="140"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="140"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="50"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="147"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="150"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="62"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -10404,23 +10383,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="135"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="156"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="147"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="147"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="62"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -10432,23 +10411,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="135"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="140"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="50"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="156"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="147"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="147"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="150"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="150"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="62"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -10460,23 +10439,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="135"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="143"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="50"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="147"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="150"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="150"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="62"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -10488,23 +10467,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="135"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="143"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="140"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="50"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="150"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="62"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -10516,23 +10495,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="136"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="143"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="140"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
+      <c r="A24" s="155"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="156"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="147"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="147"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="150"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="150"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -10544,23 +10523,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="135"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="140"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="140"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
+      <c r="A25" s="155"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="150"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="150"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -10572,23 +10551,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="135"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="140"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="50"/>
+      <c r="A26" s="155"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="156"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="147"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="150"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="150"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="62"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -10600,23 +10579,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="135"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="143"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="140"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="140"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
+      <c r="A27" s="155"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="156"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="156"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="147"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="150"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="150"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="62"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -10628,23 +10607,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="135"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="143"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
+      <c r="A28" s="155"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="156"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="156"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="150"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="150"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="62"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -10656,23 +10635,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="135"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="143"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
+      <c r="A29" s="155"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="150"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="150"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="62"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -10684,23 +10663,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="135"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="136"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="140"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="140"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
+      <c r="A30" s="155"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="62"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -10712,23 +10691,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="147"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="147"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="141"/>
-      <c r="M31" s="120"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="141"/>
-      <c r="P31" s="120"/>
-      <c r="Q31" s="138"/>
+      <c r="A31" s="158"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="159"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="159"/>
+      <c r="F31" s="149"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="149"/>
+      <c r="J31" s="148"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="151"/>
+      <c r="M31" s="145"/>
+      <c r="N31" s="149"/>
+      <c r="O31" s="151"/>
+      <c r="P31" s="145"/>
+      <c r="Q31" s="149"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -11726,62 +11705,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11806,62 +11785,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11874,1329 +11853,1141 @@
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="156" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="190" customWidth="1"/>
-    <col min="3" max="6" width="8.140625" style="156" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="190" customWidth="1"/>
-    <col min="8" max="13" width="8.140625" style="156" customWidth="1"/>
-    <col min="14" max="19" width="12.140625" style="156" customWidth="1"/>
-    <col min="20" max="16384" width="8" style="156"/>
+    <col min="1" max="1" width="13.5703125" style="49" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="59" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="49" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="59" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="49" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="49" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="49"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="180" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="149" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="181" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="150"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="153"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="155" t="s">
+      <c r="D1" s="182"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="186"/>
+      <c r="N1" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="152"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="155" t="s">
+      <c r="O1" s="184"/>
+      <c r="P1" s="186"/>
+      <c r="Q1" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="152" t="s">
+      <c r="R1" s="184" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="154"/>
+      <c r="S1" s="186"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="148"/>
-      <c r="B2" s="148"/>
-      <c r="C2" s="149" t="s">
+      <c r="A2" s="180"/>
+      <c r="B2" s="180"/>
+      <c r="C2" s="181" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="150"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="153"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155" t="s">
+      <c r="D2" s="182"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="186"/>
+      <c r="N2" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="159" t="s">
+      <c r="O2" s="187"/>
+      <c r="P2" s="188"/>
+      <c r="Q2" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="R2" s="160">
+      <c r="R2" s="189">
         <v>44771</v>
       </c>
-      <c r="S2" s="161"/>
+      <c r="S2" s="190"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
-      <c r="A3" s="162"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="162"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="164" t="s">
+      <c r="A4" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="165" t="s">
+      <c r="B4" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="166" t="s">
+      <c r="C4" s="171" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="166" t="s">
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="167"/>
-      <c r="J4" s="167"/>
-      <c r="K4" s="167"/>
-      <c r="L4" s="167"/>
-      <c r="M4" s="168"/>
-      <c r="N4" s="166" t="s">
+      <c r="I4" s="172"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="172"/>
+      <c r="M4" s="173"/>
+      <c r="N4" s="171" t="s">
         <v>104</v>
       </c>
-      <c r="O4" s="167"/>
-      <c r="P4" s="168"/>
-      <c r="Q4" s="164" t="s">
+      <c r="O4" s="172"/>
+      <c r="P4" s="173"/>
+      <c r="Q4" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="166" t="s">
+      <c r="R4" s="171" t="s">
         <v>106</v>
       </c>
-      <c r="S4" s="168"/>
+      <c r="S4" s="173"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
-      <c r="A5" s="169"/>
-      <c r="B5" s="170"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="173"/>
-      <c r="P5" s="174"/>
-      <c r="Q5" s="169"/>
-      <c r="R5" s="175"/>
-      <c r="S5" s="176"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="174"/>
+      <c r="K5" s="174"/>
+      <c r="L5" s="174"/>
+      <c r="M5" s="174"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="176"/>
+      <c r="P5" s="177"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="178"/>
+      <c r="S5" s="179"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
-      <c r="A6" s="177"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="178"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="178"/>
-      <c r="N6" s="179"/>
-      <c r="O6" s="180"/>
-      <c r="P6" s="181"/>
-      <c r="Q6" s="182"/>
-      <c r="R6" s="183"/>
-      <c r="S6" s="183"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="160"/>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160"/>
+      <c r="L6" s="160"/>
+      <c r="M6" s="160"/>
+      <c r="N6" s="168"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="170"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="167"/>
+      <c r="S6" s="167"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="177"/>
-      <c r="B7" s="177"/>
-      <c r="C7" s="178"/>
-      <c r="D7" s="178"/>
-      <c r="E7" s="178"/>
-      <c r="F7" s="178"/>
-      <c r="G7" s="178"/>
-      <c r="H7" s="178"/>
-      <c r="I7" s="178"/>
-      <c r="J7" s="178"/>
-      <c r="K7" s="178"/>
-      <c r="L7" s="178"/>
-      <c r="M7" s="178"/>
-      <c r="N7" s="184"/>
-      <c r="O7" s="185"/>
-      <c r="P7" s="186"/>
-      <c r="Q7" s="182"/>
-      <c r="R7" s="183"/>
-      <c r="S7" s="183"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="160"/>
+      <c r="L7" s="160"/>
+      <c r="M7" s="160"/>
+      <c r="N7" s="164"/>
+      <c r="O7" s="165"/>
+      <c r="P7" s="166"/>
+      <c r="Q7" s="58"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="167"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
-      <c r="A8" s="177"/>
-      <c r="B8" s="177"/>
-      <c r="C8" s="178"/>
-      <c r="D8" s="178"/>
-      <c r="E8" s="178"/>
-      <c r="F8" s="178"/>
-      <c r="G8" s="178"/>
-      <c r="H8" s="178"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="178"/>
-      <c r="K8" s="178"/>
-      <c r="L8" s="178"/>
-      <c r="M8" s="178"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="185"/>
-      <c r="P8" s="186"/>
-      <c r="Q8" s="182"/>
-      <c r="R8" s="183"/>
-      <c r="S8" s="183"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
+      <c r="L8" s="160"/>
+      <c r="M8" s="160"/>
+      <c r="N8" s="164"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="166"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="167"/>
+      <c r="S8" s="167"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
-      <c r="A9" s="177"/>
-      <c r="B9" s="177"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="178"/>
-      <c r="E9" s="178"/>
-      <c r="F9" s="178"/>
-      <c r="G9" s="178"/>
-      <c r="H9" s="178"/>
-      <c r="I9" s="178"/>
-      <c r="J9" s="178"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="185"/>
-      <c r="P9" s="186"/>
-      <c r="Q9" s="177"/>
-      <c r="R9" s="183"/>
-      <c r="S9" s="183"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="160"/>
+      <c r="M9" s="160"/>
+      <c r="N9" s="164"/>
+      <c r="O9" s="165"/>
+      <c r="P9" s="166"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="167"/>
+      <c r="S9" s="167"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
-      <c r="A10" s="177"/>
-      <c r="B10" s="177"/>
-      <c r="C10" s="178"/>
-      <c r="D10" s="178"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="178"/>
-      <c r="G10" s="178"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="188"/>
-      <c r="J10" s="188"/>
-      <c r="K10" s="188"/>
-      <c r="L10" s="188"/>
-      <c r="M10" s="189"/>
-      <c r="N10" s="184"/>
-      <c r="O10" s="185"/>
-      <c r="P10" s="186"/>
-      <c r="Q10" s="182"/>
-      <c r="R10" s="183"/>
-      <c r="S10" s="183"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="161"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="162"/>
+      <c r="K10" s="162"/>
+      <c r="L10" s="162"/>
+      <c r="M10" s="163"/>
+      <c r="N10" s="164"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="166"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="167"/>
+      <c r="S10" s="167"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
-      <c r="A11" s="177"/>
-      <c r="B11" s="177"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="178"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="178"/>
-      <c r="G11" s="178"/>
-      <c r="H11" s="187"/>
-      <c r="I11" s="188"/>
-      <c r="J11" s="188"/>
-      <c r="K11" s="188"/>
-      <c r="L11" s="188"/>
-      <c r="M11" s="189"/>
-      <c r="N11" s="184"/>
-      <c r="O11" s="185"/>
-      <c r="P11" s="186"/>
-      <c r="Q11" s="177"/>
-      <c r="R11" s="183"/>
-      <c r="S11" s="183"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="162"/>
+      <c r="K11" s="162"/>
+      <c r="L11" s="162"/>
+      <c r="M11" s="163"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="165"/>
+      <c r="P11" s="166"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="167"/>
+      <c r="S11" s="167"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
-      <c r="A12" s="177"/>
-      <c r="B12" s="177"/>
-      <c r="C12" s="178"/>
-      <c r="D12" s="178"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="178"/>
-      <c r="G12" s="178"/>
-      <c r="H12" s="187"/>
-      <c r="I12" s="188"/>
-      <c r="J12" s="188"/>
-      <c r="K12" s="188"/>
-      <c r="L12" s="188"/>
-      <c r="M12" s="189"/>
-      <c r="N12" s="184"/>
-      <c r="O12" s="185"/>
-      <c r="P12" s="186"/>
-      <c r="Q12" s="177"/>
-      <c r="R12" s="183"/>
-      <c r="S12" s="183"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="161"/>
+      <c r="I12" s="162"/>
+      <c r="J12" s="162"/>
+      <c r="K12" s="162"/>
+      <c r="L12" s="162"/>
+      <c r="M12" s="163"/>
+      <c r="N12" s="164"/>
+      <c r="O12" s="165"/>
+      <c r="P12" s="166"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="167"/>
+      <c r="S12" s="167"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
-      <c r="A13" s="177"/>
-      <c r="B13" s="177"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="187"/>
-      <c r="I13" s="188"/>
-      <c r="J13" s="188"/>
-      <c r="K13" s="188"/>
-      <c r="L13" s="188"/>
-      <c r="M13" s="189"/>
-      <c r="N13" s="184"/>
-      <c r="O13" s="185"/>
-      <c r="P13" s="186"/>
-      <c r="Q13" s="177"/>
-      <c r="R13" s="183"/>
-      <c r="S13" s="183"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="161"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="162"/>
+      <c r="K13" s="162"/>
+      <c r="L13" s="162"/>
+      <c r="M13" s="163"/>
+      <c r="N13" s="164"/>
+      <c r="O13" s="165"/>
+      <c r="P13" s="166"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="167"/>
+      <c r="S13" s="167"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
-      <c r="A14" s="177"/>
-      <c r="B14" s="177"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="187"/>
-      <c r="I14" s="188"/>
-      <c r="J14" s="188"/>
-      <c r="K14" s="188"/>
-      <c r="L14" s="188"/>
-      <c r="M14" s="189"/>
-      <c r="N14" s="184"/>
-      <c r="O14" s="185"/>
-      <c r="P14" s="186"/>
-      <c r="Q14" s="177"/>
-      <c r="R14" s="183"/>
-      <c r="S14" s="183"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="160"/>
+      <c r="H14" s="161"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="162"/>
+      <c r="K14" s="162"/>
+      <c r="L14" s="162"/>
+      <c r="M14" s="163"/>
+      <c r="N14" s="164"/>
+      <c r="O14" s="165"/>
+      <c r="P14" s="166"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="167"/>
+      <c r="S14" s="167"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
-      <c r="A15" s="177"/>
-      <c r="B15" s="177"/>
-      <c r="C15" s="178"/>
-      <c r="D15" s="178"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="187"/>
-      <c r="I15" s="188"/>
-      <c r="J15" s="188"/>
-      <c r="K15" s="188"/>
-      <c r="L15" s="188"/>
-      <c r="M15" s="189"/>
-      <c r="N15" s="184"/>
-      <c r="O15" s="185"/>
-      <c r="P15" s="186"/>
-      <c r="Q15" s="177"/>
-      <c r="R15" s="183"/>
-      <c r="S15" s="183"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="162"/>
+      <c r="K15" s="162"/>
+      <c r="L15" s="162"/>
+      <c r="M15" s="163"/>
+      <c r="N15" s="164"/>
+      <c r="O15" s="165"/>
+      <c r="P15" s="166"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="167"/>
+      <c r="S15" s="167"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
-      <c r="A16" s="177"/>
-      <c r="B16" s="177"/>
-      <c r="C16" s="178"/>
-      <c r="D16" s="178"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="187"/>
-      <c r="I16" s="188"/>
-      <c r="J16" s="188"/>
-      <c r="K16" s="188"/>
-      <c r="L16" s="188"/>
-      <c r="M16" s="189"/>
-      <c r="N16" s="184"/>
-      <c r="O16" s="185"/>
-      <c r="P16" s="186"/>
-      <c r="Q16" s="177"/>
-      <c r="R16" s="183"/>
-      <c r="S16" s="183"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="160"/>
+      <c r="E16" s="160"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="160"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="162"/>
+      <c r="K16" s="162"/>
+      <c r="L16" s="162"/>
+      <c r="M16" s="163"/>
+      <c r="N16" s="164"/>
+      <c r="O16" s="165"/>
+      <c r="P16" s="166"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="167"/>
+      <c r="S16" s="167"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
-      <c r="A17" s="177"/>
-      <c r="B17" s="177"/>
-      <c r="C17" s="178"/>
-      <c r="D17" s="178"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="178"/>
-      <c r="G17" s="178"/>
-      <c r="H17" s="187"/>
-      <c r="I17" s="188"/>
-      <c r="J17" s="188"/>
-      <c r="K17" s="188"/>
-      <c r="L17" s="188"/>
-      <c r="M17" s="189"/>
-      <c r="N17" s="184"/>
-      <c r="O17" s="185"/>
-      <c r="P17" s="186"/>
-      <c r="Q17" s="177"/>
-      <c r="R17" s="183"/>
-      <c r="S17" s="183"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="160"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="162"/>
+      <c r="K17" s="162"/>
+      <c r="L17" s="162"/>
+      <c r="M17" s="163"/>
+      <c r="N17" s="164"/>
+      <c r="O17" s="165"/>
+      <c r="P17" s="166"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="167"/>
+      <c r="S17" s="167"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
-      <c r="A18" s="177"/>
-      <c r="B18" s="177"/>
-      <c r="C18" s="178"/>
-      <c r="D18" s="178"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="178"/>
-      <c r="G18" s="178"/>
-      <c r="H18" s="187"/>
-      <c r="I18" s="188"/>
-      <c r="J18" s="188"/>
-      <c r="K18" s="188"/>
-      <c r="L18" s="188"/>
-      <c r="M18" s="189"/>
-      <c r="N18" s="184"/>
-      <c r="O18" s="185"/>
-      <c r="P18" s="186"/>
-      <c r="Q18" s="177"/>
-      <c r="R18" s="183"/>
-      <c r="S18" s="183"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="160"/>
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="162"/>
+      <c r="K18" s="162"/>
+      <c r="L18" s="162"/>
+      <c r="M18" s="163"/>
+      <c r="N18" s="164"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="166"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="167"/>
+      <c r="S18" s="167"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
-      <c r="A19" s="177"/>
-      <c r="B19" s="177"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="178"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="178"/>
-      <c r="G19" s="178"/>
-      <c r="H19" s="187"/>
-      <c r="I19" s="188"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="188"/>
-      <c r="L19" s="188"/>
-      <c r="M19" s="189"/>
-      <c r="N19" s="184"/>
-      <c r="O19" s="185"/>
-      <c r="P19" s="186"/>
-      <c r="Q19" s="177"/>
-      <c r="R19" s="183"/>
-      <c r="S19" s="183"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="160"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="160"/>
+      <c r="F19" s="160"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="162"/>
+      <c r="K19" s="162"/>
+      <c r="L19" s="162"/>
+      <c r="M19" s="163"/>
+      <c r="N19" s="164"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="166"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="167"/>
+      <c r="S19" s="167"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
-      <c r="A20" s="177"/>
-      <c r="B20" s="177"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="178"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="178"/>
-      <c r="G20" s="178"/>
-      <c r="H20" s="187"/>
-      <c r="I20" s="188"/>
-      <c r="J20" s="188"/>
-      <c r="K20" s="188"/>
-      <c r="L20" s="188"/>
-      <c r="M20" s="189"/>
-      <c r="N20" s="184"/>
-      <c r="O20" s="185"/>
-      <c r="P20" s="186"/>
-      <c r="Q20" s="177"/>
-      <c r="R20" s="183"/>
-      <c r="S20" s="183"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="160"/>
+      <c r="D20" s="160"/>
+      <c r="E20" s="160"/>
+      <c r="F20" s="160"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="162"/>
+      <c r="K20" s="162"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="163"/>
+      <c r="N20" s="164"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="166"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="167"/>
+      <c r="S20" s="167"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
-      <c r="A21" s="177"/>
-      <c r="B21" s="177"/>
-      <c r="C21" s="178"/>
-      <c r="D21" s="178"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="178"/>
-      <c r="G21" s="178"/>
-      <c r="H21" s="187"/>
-      <c r="I21" s="188"/>
-      <c r="J21" s="188"/>
-      <c r="K21" s="188"/>
-      <c r="L21" s="188"/>
-      <c r="M21" s="189"/>
-      <c r="N21" s="184"/>
-      <c r="O21" s="185"/>
-      <c r="P21" s="186"/>
-      <c r="Q21" s="177"/>
-      <c r="R21" s="183"/>
-      <c r="S21" s="183"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="160"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="162"/>
+      <c r="K21" s="162"/>
+      <c r="L21" s="162"/>
+      <c r="M21" s="163"/>
+      <c r="N21" s="164"/>
+      <c r="O21" s="165"/>
+      <c r="P21" s="166"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="167"/>
+      <c r="S21" s="167"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
-      <c r="A22" s="177"/>
-      <c r="B22" s="177"/>
-      <c r="C22" s="178"/>
-      <c r="D22" s="178"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="178"/>
-      <c r="G22" s="178"/>
-      <c r="H22" s="187"/>
-      <c r="I22" s="188"/>
-      <c r="J22" s="188"/>
-      <c r="K22" s="188"/>
-      <c r="L22" s="188"/>
-      <c r="M22" s="189"/>
-      <c r="N22" s="184"/>
-      <c r="O22" s="185"/>
-      <c r="P22" s="186"/>
-      <c r="Q22" s="177"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="183"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="163"/>
+      <c r="N22" s="164"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="166"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="167"/>
+      <c r="S22" s="167"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
-      <c r="A23" s="177"/>
-      <c r="B23" s="177"/>
-      <c r="C23" s="178"/>
-      <c r="D23" s="178"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="178"/>
-      <c r="G23" s="178"/>
-      <c r="H23" s="187"/>
-      <c r="I23" s="188"/>
-      <c r="J23" s="188"/>
-      <c r="K23" s="188"/>
-      <c r="L23" s="188"/>
-      <c r="M23" s="189"/>
-      <c r="N23" s="184"/>
-      <c r="O23" s="185"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="177"/>
-      <c r="R23" s="183"/>
-      <c r="S23" s="183"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="160"/>
+      <c r="E23" s="160"/>
+      <c r="F23" s="160"/>
+      <c r="G23" s="160"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="162"/>
+      <c r="M23" s="163"/>
+      <c r="N23" s="164"/>
+      <c r="O23" s="165"/>
+      <c r="P23" s="166"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="167"/>
+      <c r="S23" s="167"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
-      <c r="A24" s="177"/>
-      <c r="B24" s="177"/>
-      <c r="C24" s="178"/>
-      <c r="D24" s="178"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="178"/>
-      <c r="G24" s="178"/>
-      <c r="H24" s="187"/>
-      <c r="I24" s="188"/>
-      <c r="J24" s="188"/>
-      <c r="K24" s="188"/>
-      <c r="L24" s="188"/>
-      <c r="M24" s="189"/>
-      <c r="N24" s="184"/>
-      <c r="O24" s="185"/>
-      <c r="P24" s="186"/>
-      <c r="Q24" s="177"/>
-      <c r="R24" s="183"/>
-      <c r="S24" s="183"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="160"/>
+      <c r="D24" s="160"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="162"/>
+      <c r="K24" s="162"/>
+      <c r="L24" s="162"/>
+      <c r="M24" s="163"/>
+      <c r="N24" s="164"/>
+      <c r="O24" s="165"/>
+      <c r="P24" s="166"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="167"/>
+      <c r="S24" s="167"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
-      <c r="A25" s="177"/>
-      <c r="B25" s="177"/>
-      <c r="C25" s="178"/>
-      <c r="D25" s="178"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="178"/>
-      <c r="G25" s="178"/>
-      <c r="H25" s="187"/>
-      <c r="I25" s="188"/>
-      <c r="J25" s="188"/>
-      <c r="K25" s="188"/>
-      <c r="L25" s="188"/>
-      <c r="M25" s="189"/>
-      <c r="N25" s="184"/>
-      <c r="O25" s="185"/>
-      <c r="P25" s="186"/>
-      <c r="Q25" s="177"/>
-      <c r="R25" s="183"/>
-      <c r="S25" s="183"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="160"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="160"/>
+      <c r="F25" s="160"/>
+      <c r="G25" s="160"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="162"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="162"/>
+      <c r="M25" s="163"/>
+      <c r="N25" s="164"/>
+      <c r="O25" s="165"/>
+      <c r="P25" s="166"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="167"/>
+      <c r="S25" s="167"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
-      <c r="A26" s="177"/>
-      <c r="B26" s="177"/>
-      <c r="C26" s="178"/>
-      <c r="D26" s="178"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="178"/>
-      <c r="G26" s="178"/>
-      <c r="H26" s="187"/>
-      <c r="I26" s="188"/>
-      <c r="J26" s="188"/>
-      <c r="K26" s="188"/>
-      <c r="L26" s="188"/>
-      <c r="M26" s="189"/>
-      <c r="N26" s="184"/>
-      <c r="O26" s="185"/>
-      <c r="P26" s="186"/>
-      <c r="Q26" s="177"/>
-      <c r="R26" s="183"/>
-      <c r="S26" s="183"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="160"/>
+      <c r="D26" s="160"/>
+      <c r="E26" s="160"/>
+      <c r="F26" s="160"/>
+      <c r="G26" s="160"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="162"/>
+      <c r="K26" s="162"/>
+      <c r="L26" s="162"/>
+      <c r="M26" s="163"/>
+      <c r="N26" s="164"/>
+      <c r="O26" s="165"/>
+      <c r="P26" s="166"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="167"/>
+      <c r="S26" s="167"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
-      <c r="A27" s="177"/>
-      <c r="B27" s="177"/>
-      <c r="C27" s="178"/>
-      <c r="D27" s="178"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="178"/>
-      <c r="G27" s="178"/>
-      <c r="H27" s="187"/>
-      <c r="I27" s="188"/>
-      <c r="J27" s="188"/>
-      <c r="K27" s="188"/>
-      <c r="L27" s="188"/>
-      <c r="M27" s="189"/>
-      <c r="N27" s="184"/>
-      <c r="O27" s="185"/>
-      <c r="P27" s="186"/>
-      <c r="Q27" s="177"/>
-      <c r="R27" s="183"/>
-      <c r="S27" s="183"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="160"/>
+      <c r="E27" s="160"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="160"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="162"/>
+      <c r="K27" s="162"/>
+      <c r="L27" s="162"/>
+      <c r="M27" s="163"/>
+      <c r="N27" s="164"/>
+      <c r="O27" s="165"/>
+      <c r="P27" s="166"/>
+      <c r="Q27" s="57"/>
+      <c r="R27" s="167"/>
+      <c r="S27" s="167"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
-      <c r="A28" s="177"/>
-      <c r="B28" s="177"/>
-      <c r="C28" s="178"/>
-      <c r="D28" s="178"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="178"/>
-      <c r="G28" s="178"/>
-      <c r="H28" s="187"/>
-      <c r="I28" s="188"/>
-      <c r="J28" s="188"/>
-      <c r="K28" s="188"/>
-      <c r="L28" s="188"/>
-      <c r="M28" s="189"/>
-      <c r="N28" s="184"/>
-      <c r="O28" s="185"/>
-      <c r="P28" s="186"/>
-      <c r="Q28" s="177"/>
-      <c r="R28" s="183"/>
-      <c r="S28" s="183"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="160"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="160"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="162"/>
+      <c r="K28" s="162"/>
+      <c r="L28" s="162"/>
+      <c r="M28" s="163"/>
+      <c r="N28" s="164"/>
+      <c r="O28" s="165"/>
+      <c r="P28" s="166"/>
+      <c r="Q28" s="57"/>
+      <c r="R28" s="167"/>
+      <c r="S28" s="167"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
-      <c r="A29" s="177"/>
-      <c r="B29" s="177"/>
-      <c r="C29" s="178"/>
-      <c r="D29" s="178"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="178"/>
-      <c r="G29" s="178"/>
-      <c r="H29" s="187"/>
-      <c r="I29" s="188"/>
-      <c r="J29" s="188"/>
-      <c r="K29" s="188"/>
-      <c r="L29" s="188"/>
-      <c r="M29" s="189"/>
-      <c r="N29" s="184"/>
-      <c r="O29" s="185"/>
-      <c r="P29" s="186"/>
-      <c r="Q29" s="177"/>
-      <c r="R29" s="183"/>
-      <c r="S29" s="183"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="160"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="162"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="162"/>
+      <c r="M29" s="163"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="165"/>
+      <c r="P29" s="166"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="167"/>
+      <c r="S29" s="167"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
-      <c r="A30" s="177"/>
-      <c r="B30" s="177"/>
-      <c r="C30" s="178"/>
-      <c r="D30" s="178"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="178"/>
-      <c r="G30" s="178"/>
-      <c r="H30" s="187"/>
-      <c r="I30" s="188"/>
-      <c r="J30" s="188"/>
-      <c r="K30" s="188"/>
-      <c r="L30" s="188"/>
-      <c r="M30" s="189"/>
-      <c r="N30" s="184"/>
-      <c r="O30" s="185"/>
-      <c r="P30" s="186"/>
-      <c r="Q30" s="177"/>
-      <c r="R30" s="183"/>
-      <c r="S30" s="183"/>
+      <c r="A30" s="57"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="160"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="162"/>
+      <c r="K30" s="162"/>
+      <c r="L30" s="162"/>
+      <c r="M30" s="163"/>
+      <c r="N30" s="164"/>
+      <c r="O30" s="165"/>
+      <c r="P30" s="166"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="167"/>
+      <c r="S30" s="167"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
-      <c r="A31" s="177"/>
-      <c r="B31" s="177"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="178"/>
-      <c r="G31" s="178"/>
-      <c r="H31" s="187"/>
-      <c r="I31" s="188"/>
-      <c r="J31" s="188"/>
-      <c r="K31" s="188"/>
-      <c r="L31" s="188"/>
-      <c r="M31" s="189"/>
-      <c r="N31" s="184"/>
-      <c r="O31" s="185"/>
-      <c r="P31" s="186"/>
-      <c r="Q31" s="177"/>
-      <c r="R31" s="183"/>
-      <c r="S31" s="183"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="160"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="162"/>
+      <c r="J31" s="162"/>
+      <c r="K31" s="162"/>
+      <c r="L31" s="162"/>
+      <c r="M31" s="163"/>
+      <c r="N31" s="164"/>
+      <c r="O31" s="165"/>
+      <c r="P31" s="166"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="167"/>
+      <c r="S31" s="167"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
-      <c r="A32" s="177"/>
-      <c r="B32" s="177"/>
-      <c r="C32" s="178"/>
-      <c r="D32" s="178"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="178"/>
-      <c r="G32" s="178"/>
-      <c r="H32" s="187"/>
-      <c r="I32" s="188"/>
-      <c r="J32" s="188"/>
-      <c r="K32" s="188"/>
-      <c r="L32" s="188"/>
-      <c r="M32" s="189"/>
-      <c r="N32" s="184"/>
-      <c r="O32" s="185"/>
-      <c r="P32" s="186"/>
-      <c r="Q32" s="177"/>
-      <c r="R32" s="183"/>
-      <c r="S32" s="183"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="161"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="162"/>
+      <c r="K32" s="162"/>
+      <c r="L32" s="162"/>
+      <c r="M32" s="163"/>
+      <c r="N32" s="164"/>
+      <c r="O32" s="165"/>
+      <c r="P32" s="166"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="167"/>
+      <c r="S32" s="167"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
-      <c r="A33" s="177"/>
-      <c r="B33" s="177"/>
-      <c r="C33" s="178"/>
-      <c r="D33" s="178"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="178"/>
-      <c r="G33" s="178"/>
-      <c r="H33" s="187"/>
-      <c r="I33" s="188"/>
-      <c r="J33" s="188"/>
-      <c r="K33" s="188"/>
-      <c r="L33" s="188"/>
-      <c r="M33" s="189"/>
-      <c r="N33" s="184"/>
-      <c r="O33" s="185"/>
-      <c r="P33" s="186"/>
-      <c r="Q33" s="177"/>
-      <c r="R33" s="183"/>
-      <c r="S33" s="183"/>
+      <c r="A33" s="57"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="162"/>
+      <c r="K33" s="162"/>
+      <c r="L33" s="162"/>
+      <c r="M33" s="163"/>
+      <c r="N33" s="164"/>
+      <c r="O33" s="165"/>
+      <c r="P33" s="166"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="167"/>
+      <c r="S33" s="167"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
-      <c r="A34" s="177"/>
-      <c r="B34" s="177"/>
-      <c r="C34" s="178"/>
-      <c r="D34" s="178"/>
-      <c r="E34" s="178"/>
-      <c r="F34" s="178"/>
-      <c r="G34" s="178"/>
-      <c r="H34" s="187"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="188"/>
-      <c r="M34" s="189"/>
-      <c r="N34" s="184"/>
-      <c r="O34" s="185"/>
-      <c r="P34" s="186"/>
-      <c r="Q34" s="177"/>
-      <c r="R34" s="183"/>
-      <c r="S34" s="183"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="160"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="161"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="164"/>
+      <c r="O34" s="165"/>
+      <c r="P34" s="166"/>
+      <c r="Q34" s="57"/>
+      <c r="R34" s="167"/>
+      <c r="S34" s="167"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
-      <c r="A35" s="177"/>
-      <c r="B35" s="177"/>
-      <c r="C35" s="178"/>
-      <c r="D35" s="178"/>
-      <c r="E35" s="178"/>
-      <c r="F35" s="178"/>
-      <c r="G35" s="178"/>
-      <c r="H35" s="187"/>
-      <c r="I35" s="188"/>
-      <c r="J35" s="188"/>
-      <c r="K35" s="188"/>
-      <c r="L35" s="188"/>
-      <c r="M35" s="189"/>
-      <c r="N35" s="184"/>
-      <c r="O35" s="185"/>
-      <c r="P35" s="186"/>
-      <c r="Q35" s="177"/>
-      <c r="R35" s="183"/>
-      <c r="S35" s="183"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="160"/>
+      <c r="F35" s="160"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="162"/>
+      <c r="K35" s="162"/>
+      <c r="L35" s="162"/>
+      <c r="M35" s="163"/>
+      <c r="N35" s="164"/>
+      <c r="O35" s="165"/>
+      <c r="P35" s="166"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="167"/>
+      <c r="S35" s="167"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
-      <c r="A36" s="177"/>
-      <c r="B36" s="177"/>
-      <c r="C36" s="178"/>
-      <c r="D36" s="178"/>
-      <c r="E36" s="178"/>
-      <c r="F36" s="178"/>
-      <c r="G36" s="178"/>
-      <c r="H36" s="187"/>
-      <c r="I36" s="188"/>
-      <c r="J36" s="188"/>
-      <c r="K36" s="188"/>
-      <c r="L36" s="188"/>
-      <c r="M36" s="189"/>
-      <c r="N36" s="184"/>
-      <c r="O36" s="185"/>
-      <c r="P36" s="186"/>
-      <c r="Q36" s="177"/>
-      <c r="R36" s="183"/>
-      <c r="S36" s="183"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="160"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="160"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="161"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="162"/>
+      <c r="K36" s="162"/>
+      <c r="L36" s="162"/>
+      <c r="M36" s="163"/>
+      <c r="N36" s="164"/>
+      <c r="O36" s="165"/>
+      <c r="P36" s="166"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="167"/>
+      <c r="S36" s="167"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
-      <c r="A37" s="177"/>
-      <c r="B37" s="177"/>
-      <c r="C37" s="178"/>
-      <c r="D37" s="178"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="178"/>
-      <c r="G37" s="178"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="188"/>
-      <c r="J37" s="188"/>
-      <c r="K37" s="188"/>
-      <c r="L37" s="188"/>
-      <c r="M37" s="189"/>
-      <c r="N37" s="184"/>
-      <c r="O37" s="185"/>
-      <c r="P37" s="186"/>
-      <c r="Q37" s="177"/>
-      <c r="R37" s="183"/>
-      <c r="S37" s="183"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="162"/>
+      <c r="K37" s="162"/>
+      <c r="L37" s="162"/>
+      <c r="M37" s="163"/>
+      <c r="N37" s="164"/>
+      <c r="O37" s="165"/>
+      <c r="P37" s="166"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="167"/>
+      <c r="S37" s="167"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
-      <c r="A38" s="177"/>
-      <c r="B38" s="177"/>
-      <c r="C38" s="178"/>
-      <c r="D38" s="178"/>
-      <c r="E38" s="178"/>
-      <c r="F38" s="178"/>
-      <c r="G38" s="178"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="188"/>
-      <c r="J38" s="188"/>
-      <c r="K38" s="188"/>
-      <c r="L38" s="188"/>
-      <c r="M38" s="189"/>
-      <c r="N38" s="184"/>
-      <c r="O38" s="185"/>
-      <c r="P38" s="186"/>
-      <c r="Q38" s="177"/>
-      <c r="R38" s="183"/>
-      <c r="S38" s="183"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="162"/>
+      <c r="L38" s="162"/>
+      <c r="M38" s="163"/>
+      <c r="N38" s="164"/>
+      <c r="O38" s="165"/>
+      <c r="P38" s="166"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="167"/>
+      <c r="S38" s="167"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
-      <c r="A39" s="177"/>
-      <c r="B39" s="177"/>
-      <c r="C39" s="178"/>
-      <c r="D39" s="178"/>
-      <c r="E39" s="178"/>
-      <c r="F39" s="178"/>
-      <c r="G39" s="178"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
-      <c r="L39" s="188"/>
-      <c r="M39" s="189"/>
-      <c r="N39" s="184"/>
-      <c r="O39" s="185"/>
-      <c r="P39" s="186"/>
-      <c r="Q39" s="177"/>
-      <c r="R39" s="183"/>
-      <c r="S39" s="183"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="160"/>
+      <c r="D39" s="160"/>
+      <c r="E39" s="160"/>
+      <c r="F39" s="160"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="161"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+      <c r="M39" s="163"/>
+      <c r="N39" s="164"/>
+      <c r="O39" s="165"/>
+      <c r="P39" s="166"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="167"/>
+      <c r="S39" s="167"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
-      <c r="A40" s="177"/>
-      <c r="B40" s="177"/>
-      <c r="C40" s="178"/>
-      <c r="D40" s="178"/>
-      <c r="E40" s="178"/>
-      <c r="F40" s="178"/>
-      <c r="G40" s="178"/>
-      <c r="H40" s="187"/>
-      <c r="I40" s="188"/>
-      <c r="J40" s="188"/>
-      <c r="K40" s="188"/>
-      <c r="L40" s="188"/>
-      <c r="M40" s="189"/>
-      <c r="N40" s="184"/>
-      <c r="O40" s="185"/>
-      <c r="P40" s="186"/>
-      <c r="Q40" s="177"/>
-      <c r="R40" s="183"/>
-      <c r="S40" s="183"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="160"/>
+      <c r="D40" s="160"/>
+      <c r="E40" s="160"/>
+      <c r="F40" s="160"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="161"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="162"/>
+      <c r="K40" s="162"/>
+      <c r="L40" s="162"/>
+      <c r="M40" s="163"/>
+      <c r="N40" s="164"/>
+      <c r="O40" s="165"/>
+      <c r="P40" s="166"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="167"/>
+      <c r="S40" s="167"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
-      <c r="A41" s="177"/>
-      <c r="B41" s="177"/>
-      <c r="C41" s="178"/>
-      <c r="D41" s="178"/>
-      <c r="E41" s="178"/>
-      <c r="F41" s="178"/>
-      <c r="G41" s="178"/>
-      <c r="H41" s="187"/>
-      <c r="I41" s="188"/>
-      <c r="J41" s="188"/>
-      <c r="K41" s="188"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="189"/>
-      <c r="N41" s="184"/>
-      <c r="O41" s="185"/>
-      <c r="P41" s="186"/>
-      <c r="Q41" s="177"/>
-      <c r="R41" s="183"/>
-      <c r="S41" s="183"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="160"/>
+      <c r="D41" s="160"/>
+      <c r="E41" s="160"/>
+      <c r="F41" s="160"/>
+      <c r="G41" s="160"/>
+      <c r="H41" s="161"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="164"/>
+      <c r="O41" s="165"/>
+      <c r="P41" s="166"/>
+      <c r="Q41" s="57"/>
+      <c r="R41" s="167"/>
+      <c r="S41" s="167"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
-      <c r="A42" s="177"/>
-      <c r="B42" s="177"/>
-      <c r="C42" s="178"/>
-      <c r="D42" s="178"/>
-      <c r="E42" s="178"/>
-      <c r="F42" s="178"/>
-      <c r="G42" s="178"/>
-      <c r="H42" s="187"/>
-      <c r="I42" s="188"/>
-      <c r="J42" s="188"/>
-      <c r="K42" s="188"/>
-      <c r="L42" s="188"/>
-      <c r="M42" s="189"/>
-      <c r="N42" s="184"/>
-      <c r="O42" s="185"/>
-      <c r="P42" s="186"/>
-      <c r="Q42" s="177"/>
-      <c r="R42" s="183"/>
-      <c r="S42" s="183"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="160"/>
+      <c r="D42" s="160"/>
+      <c r="E42" s="160"/>
+      <c r="F42" s="160"/>
+      <c r="G42" s="160"/>
+      <c r="H42" s="161"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="162"/>
+      <c r="K42" s="162"/>
+      <c r="L42" s="162"/>
+      <c r="M42" s="163"/>
+      <c r="N42" s="164"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="166"/>
+      <c r="Q42" s="57"/>
+      <c r="R42" s="167"/>
+      <c r="S42" s="167"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
-      <c r="A43" s="177"/>
-      <c r="B43" s="177"/>
-      <c r="C43" s="178"/>
-      <c r="D43" s="178"/>
-      <c r="E43" s="178"/>
-      <c r="F43" s="178"/>
-      <c r="G43" s="178"/>
-      <c r="H43" s="187"/>
-      <c r="I43" s="188"/>
-      <c r="J43" s="188"/>
-      <c r="K43" s="188"/>
-      <c r="L43" s="188"/>
-      <c r="M43" s="189"/>
-      <c r="N43" s="184"/>
-      <c r="O43" s="185"/>
-      <c r="P43" s="186"/>
-      <c r="Q43" s="177"/>
-      <c r="R43" s="183"/>
-      <c r="S43" s="183"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="160"/>
+      <c r="D43" s="160"/>
+      <c r="E43" s="160"/>
+      <c r="F43" s="160"/>
+      <c r="G43" s="160"/>
+      <c r="H43" s="161"/>
+      <c r="I43" s="162"/>
+      <c r="J43" s="162"/>
+      <c r="K43" s="162"/>
+      <c r="L43" s="162"/>
+      <c r="M43" s="163"/>
+      <c r="N43" s="164"/>
+      <c r="O43" s="165"/>
+      <c r="P43" s="166"/>
+      <c r="Q43" s="57"/>
+      <c r="R43" s="167"/>
+      <c r="S43" s="167"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
-      <c r="A44" s="177"/>
-      <c r="B44" s="177"/>
-      <c r="C44" s="178"/>
-      <c r="D44" s="178"/>
-      <c r="E44" s="178"/>
-      <c r="F44" s="178"/>
-      <c r="G44" s="178"/>
-      <c r="H44" s="187"/>
-      <c r="I44" s="188"/>
-      <c r="J44" s="188"/>
-      <c r="K44" s="188"/>
-      <c r="L44" s="188"/>
-      <c r="M44" s="189"/>
-      <c r="N44" s="184"/>
-      <c r="O44" s="185"/>
-      <c r="P44" s="186"/>
-      <c r="Q44" s="177"/>
-      <c r="R44" s="183"/>
-      <c r="S44" s="183"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="160"/>
+      <c r="D44" s="160"/>
+      <c r="E44" s="160"/>
+      <c r="F44" s="160"/>
+      <c r="G44" s="160"/>
+      <c r="H44" s="161"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="162"/>
+      <c r="K44" s="162"/>
+      <c r="L44" s="162"/>
+      <c r="M44" s="163"/>
+      <c r="N44" s="164"/>
+      <c r="O44" s="165"/>
+      <c r="P44" s="166"/>
+      <c r="Q44" s="57"/>
+      <c r="R44" s="167"/>
+      <c r="S44" s="167"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
-      <c r="A45" s="177"/>
-      <c r="B45" s="177"/>
-      <c r="C45" s="178"/>
-      <c r="D45" s="178"/>
-      <c r="E45" s="178"/>
-      <c r="F45" s="178"/>
-      <c r="G45" s="178"/>
-      <c r="H45" s="187"/>
-      <c r="I45" s="188"/>
-      <c r="J45" s="188"/>
-      <c r="K45" s="188"/>
-      <c r="L45" s="188"/>
-      <c r="M45" s="189"/>
-      <c r="N45" s="184"/>
-      <c r="O45" s="185"/>
-      <c r="P45" s="186"/>
-      <c r="Q45" s="177"/>
-      <c r="R45" s="183"/>
-      <c r="S45" s="183"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="160"/>
+      <c r="D45" s="160"/>
+      <c r="E45" s="160"/>
+      <c r="F45" s="160"/>
+      <c r="G45" s="160"/>
+      <c r="H45" s="161"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="162"/>
+      <c r="L45" s="162"/>
+      <c r="M45" s="163"/>
+      <c r="N45" s="164"/>
+      <c r="O45" s="165"/>
+      <c r="P45" s="166"/>
+      <c r="Q45" s="57"/>
+      <c r="R45" s="167"/>
+      <c r="S45" s="167"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
-      <c r="A46" s="177"/>
-      <c r="B46" s="177"/>
-      <c r="C46" s="178"/>
-      <c r="D46" s="178"/>
-      <c r="E46" s="178"/>
-      <c r="F46" s="178"/>
-      <c r="G46" s="178"/>
-      <c r="H46" s="187"/>
-      <c r="I46" s="188"/>
-      <c r="J46" s="188"/>
-      <c r="K46" s="188"/>
-      <c r="L46" s="188"/>
-      <c r="M46" s="189"/>
-      <c r="N46" s="184"/>
-      <c r="O46" s="185"/>
-      <c r="P46" s="186"/>
-      <c r="Q46" s="177"/>
-      <c r="R46" s="183"/>
-      <c r="S46" s="183"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="160"/>
+      <c r="D46" s="160"/>
+      <c r="E46" s="160"/>
+      <c r="F46" s="160"/>
+      <c r="G46" s="160"/>
+      <c r="H46" s="161"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="162"/>
+      <c r="K46" s="162"/>
+      <c r="L46" s="162"/>
+      <c r="M46" s="163"/>
+      <c r="N46" s="164"/>
+      <c r="O46" s="165"/>
+      <c r="P46" s="166"/>
+      <c r="Q46" s="57"/>
+      <c r="R46" s="167"/>
+      <c r="S46" s="167"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
-      <c r="A47" s="177"/>
-      <c r="B47" s="177"/>
-      <c r="C47" s="178"/>
-      <c r="D47" s="178"/>
-      <c r="E47" s="178"/>
-      <c r="F47" s="178"/>
-      <c r="G47" s="178"/>
-      <c r="H47" s="187"/>
-      <c r="I47" s="188"/>
-      <c r="J47" s="188"/>
-      <c r="K47" s="188"/>
-      <c r="L47" s="188"/>
-      <c r="M47" s="189"/>
-      <c r="N47" s="184"/>
-      <c r="O47" s="185"/>
-      <c r="P47" s="186"/>
-      <c r="Q47" s="177"/>
-      <c r="R47" s="183"/>
-      <c r="S47" s="183"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="160"/>
+      <c r="D47" s="160"/>
+      <c r="E47" s="160"/>
+      <c r="F47" s="160"/>
+      <c r="G47" s="160"/>
+      <c r="H47" s="161"/>
+      <c r="I47" s="162"/>
+      <c r="J47" s="162"/>
+      <c r="K47" s="162"/>
+      <c r="L47" s="162"/>
+      <c r="M47" s="163"/>
+      <c r="N47" s="164"/>
+      <c r="O47" s="165"/>
+      <c r="P47" s="166"/>
+      <c r="Q47" s="57"/>
+      <c r="R47" s="167"/>
+      <c r="S47" s="167"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
-      <c r="A48" s="177"/>
-      <c r="B48" s="177"/>
-      <c r="C48" s="178"/>
-      <c r="D48" s="178"/>
-      <c r="E48" s="178"/>
-      <c r="F48" s="178"/>
-      <c r="G48" s="178"/>
-      <c r="H48" s="187"/>
-      <c r="I48" s="188"/>
-      <c r="J48" s="188"/>
-      <c r="K48" s="188"/>
-      <c r="L48" s="188"/>
-      <c r="M48" s="189"/>
-      <c r="N48" s="184"/>
-      <c r="O48" s="185"/>
-      <c r="P48" s="186"/>
-      <c r="Q48" s="177"/>
-      <c r="R48" s="183"/>
-      <c r="S48" s="183"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="160"/>
+      <c r="D48" s="160"/>
+      <c r="E48" s="160"/>
+      <c r="F48" s="160"/>
+      <c r="G48" s="160"/>
+      <c r="H48" s="161"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="162"/>
+      <c r="L48" s="162"/>
+      <c r="M48" s="163"/>
+      <c r="N48" s="164"/>
+      <c r="O48" s="165"/>
+      <c r="P48" s="166"/>
+      <c r="Q48" s="57"/>
+      <c r="R48" s="167"/>
+      <c r="S48" s="167"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
-      <c r="A49" s="177"/>
-      <c r="B49" s="177"/>
-      <c r="C49" s="178"/>
-      <c r="D49" s="178"/>
-      <c r="E49" s="178"/>
-      <c r="F49" s="178"/>
-      <c r="G49" s="178"/>
-      <c r="H49" s="187"/>
-      <c r="I49" s="188"/>
-      <c r="J49" s="188"/>
-      <c r="K49" s="188"/>
-      <c r="L49" s="188"/>
-      <c r="M49" s="189"/>
-      <c r="N49" s="184"/>
-      <c r="O49" s="185"/>
-      <c r="P49" s="186"/>
-      <c r="Q49" s="177"/>
-      <c r="R49" s="183"/>
-      <c r="S49" s="183"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="160"/>
+      <c r="D49" s="160"/>
+      <c r="E49" s="160"/>
+      <c r="F49" s="160"/>
+      <c r="G49" s="160"/>
+      <c r="H49" s="161"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="162"/>
+      <c r="K49" s="162"/>
+      <c r="L49" s="162"/>
+      <c r="M49" s="163"/>
+      <c r="N49" s="164"/>
+      <c r="O49" s="165"/>
+      <c r="P49" s="166"/>
+      <c r="Q49" s="57"/>
+      <c r="R49" s="167"/>
+      <c r="S49" s="167"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
-      <c r="A50" s="177"/>
-      <c r="B50" s="177"/>
-      <c r="C50" s="178"/>
-      <c r="D50" s="178"/>
-      <c r="E50" s="178"/>
-      <c r="F50" s="178"/>
-      <c r="G50" s="178"/>
-      <c r="H50" s="187"/>
-      <c r="I50" s="188"/>
-      <c r="J50" s="188"/>
-      <c r="K50" s="188"/>
-      <c r="L50" s="188"/>
-      <c r="M50" s="189"/>
-      <c r="N50" s="184"/>
-      <c r="O50" s="185"/>
-      <c r="P50" s="186"/>
-      <c r="Q50" s="177"/>
-      <c r="R50" s="183"/>
-      <c r="S50" s="183"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="160"/>
+      <c r="D50" s="160"/>
+      <c r="E50" s="160"/>
+      <c r="F50" s="160"/>
+      <c r="G50" s="160"/>
+      <c r="H50" s="161"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="162"/>
+      <c r="K50" s="162"/>
+      <c r="L50" s="162"/>
+      <c r="M50" s="163"/>
+      <c r="N50" s="164"/>
+      <c r="O50" s="165"/>
+      <c r="P50" s="166"/>
+      <c r="Q50" s="57"/>
+      <c r="R50" s="167"/>
+      <c r="S50" s="167"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
-      <c r="A51" s="177"/>
-      <c r="B51" s="177"/>
-      <c r="C51" s="178"/>
-      <c r="D51" s="178"/>
-      <c r="E51" s="178"/>
-      <c r="F51" s="178"/>
-      <c r="G51" s="178"/>
-      <c r="H51" s="187"/>
-      <c r="I51" s="188"/>
-      <c r="J51" s="188"/>
-      <c r="K51" s="188"/>
-      <c r="L51" s="188"/>
-      <c r="M51" s="189"/>
-      <c r="N51" s="184"/>
-      <c r="O51" s="185"/>
-      <c r="P51" s="186"/>
-      <c r="Q51" s="177"/>
-      <c r="R51" s="183"/>
-      <c r="S51" s="183"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="160"/>
+      <c r="D51" s="160"/>
+      <c r="E51" s="160"/>
+      <c r="F51" s="160"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="162"/>
+      <c r="J51" s="162"/>
+      <c r="K51" s="162"/>
+      <c r="L51" s="162"/>
+      <c r="M51" s="163"/>
+      <c r="N51" s="164"/>
+      <c r="O51" s="165"/>
+      <c r="P51" s="166"/>
+      <c r="Q51" s="57"/>
+      <c r="R51" s="167"/>
+      <c r="S51" s="167"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
-      <c r="A52" s="177"/>
-      <c r="B52" s="177"/>
-      <c r="C52" s="178"/>
-      <c r="D52" s="178"/>
-      <c r="E52" s="178"/>
-      <c r="F52" s="178"/>
-      <c r="G52" s="178"/>
-      <c r="H52" s="187"/>
-      <c r="I52" s="188"/>
-      <c r="J52" s="188"/>
-      <c r="K52" s="188"/>
-      <c r="L52" s="188"/>
-      <c r="M52" s="189"/>
-      <c r="N52" s="184"/>
-      <c r="O52" s="185"/>
-      <c r="P52" s="186"/>
-      <c r="Q52" s="177"/>
-      <c r="R52" s="183"/>
-      <c r="S52" s="183"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="160"/>
+      <c r="D52" s="160"/>
+      <c r="E52" s="160"/>
+      <c r="F52" s="160"/>
+      <c r="G52" s="160"/>
+      <c r="H52" s="161"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="162"/>
+      <c r="K52" s="162"/>
+      <c r="L52" s="162"/>
+      <c r="M52" s="163"/>
+      <c r="N52" s="164"/>
+      <c r="O52" s="165"/>
+      <c r="P52" s="166"/>
+      <c r="Q52" s="57"/>
+      <c r="R52" s="167"/>
+      <c r="S52" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13214,6 +13005,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク編集設計書.xlsx
+++ b/Documents/タスク編集設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FEFF19-9658-495A-9BEE-A79274493329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09BD721-694D-47F9-B2DF-666067DA8F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1889,6 +1889,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1904,6 +1937,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1934,84 +2012,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2078,15 +2078,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2096,9 +2102,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2111,9 +2114,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2126,49 +2126,130 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2176,87 +2257,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2337,23 +2337,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>61176</xdr:rowOff>
+      <xdr:colOff>979372</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DF87EDC-3920-874D-81D8-273272731798}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1780B02E-2916-9863-16CA-A1BAC86FBBB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2375,8 +2375,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="390525" y="1200150"/>
-          <a:ext cx="7772400" cy="3337776"/>
+          <a:off x="152399" y="1390650"/>
+          <a:ext cx="8542223" cy="3314700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4329,19 +4329,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="91"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="76"/>
+      <c r="F1" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="91"/>
+      <c r="G1" s="76"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4353,190 +4353,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>45806</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="86"/>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="87"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="88"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="73"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="92" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="93"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="71" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="72"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="83"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="71" t="s">
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="72"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="83"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71" t="s">
+      <c r="B8" s="80"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="72"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="82" t="s">
+      <c r="C9" s="81"/>
+      <c r="D9" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="72"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="83"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="81" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="72"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="83"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81" t="s">
+      <c r="A11" s="106"/>
+      <c r="B11" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="82" t="s">
+      <c r="C11" s="81"/>
+      <c r="D11" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="72"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="83"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71" t="s">
+      <c r="B12" s="80"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="72"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="77"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="103"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5527,18 +5527,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5554,6 +5542,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5576,16 +5576,16 @@
       <c r="A1" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="91"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="76"/>
+      <c r="F1" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="91"/>
+      <c r="G1" s="76"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -5597,48 +5597,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>45806</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="86"/>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="87"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="88"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="73"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -8479,23 +8479,23 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="132"/>
+      <c r="B5" s="135"/>
       <c r="C5" s="126"/>
-      <c r="D5" s="135" t="s">
+      <c r="D5" s="137" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="136"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="138"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="136" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="61"/>
@@ -8506,19 +8506,19 @@
       <c r="G6" s="61"/>
       <c r="H6" s="61"/>
       <c r="I6" s="61"/>
-      <c r="J6" s="137"/>
+      <c r="J6" s="132"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="138"/>
-      <c r="B7" s="139"/>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="140"/>
+      <c r="A7" s="139"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="141"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="120"/>
@@ -8530,7 +8530,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
-      <c r="J8" s="141"/>
+      <c r="J8" s="142"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="120"/>
@@ -8542,7 +8542,7 @@
       <c r="G9" s="64"/>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
-      <c r="J9" s="141"/>
+      <c r="J9" s="142"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="120"/>
@@ -8554,7 +8554,7 @@
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
-      <c r="J10" s="141"/>
+      <c r="J10" s="142"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="120"/>
@@ -8566,7 +8566,7 @@
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
-      <c r="J11" s="141"/>
+      <c r="J11" s="142"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="120"/>
@@ -8578,7 +8578,7 @@
       <c r="G12" s="64"/>
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
-      <c r="J12" s="141"/>
+      <c r="J12" s="142"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="120"/>
@@ -8590,10 +8590,10 @@
       <c r="G13" s="64"/>
       <c r="H13" s="64"/>
       <c r="I13" s="64"/>
-      <c r="J13" s="141"/>
+      <c r="J13" s="142"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="134" t="s">
+      <c r="A14" s="136" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="61"/>
@@ -8604,15 +8604,15 @@
       <c r="G14" s="61"/>
       <c r="H14" s="61"/>
       <c r="I14" s="61"/>
-      <c r="J14" s="137"/>
+      <c r="J14" s="132"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="136" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="61"/>
       <c r="C15" s="62"/>
-      <c r="D15" s="142" t="s">
+      <c r="D15" s="131" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="61"/>
@@ -8627,7 +8627,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="134" t="s">
+      <c r="A16" s="136" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="61"/>
@@ -8648,7 +8648,7 @@
         <v>18</v>
       </c>
       <c r="I16" s="61"/>
-      <c r="J16" s="137"/>
+      <c r="J16" s="132"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="133">
@@ -8668,9 +8668,9 @@
       <c r="G17" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="142"/>
+      <c r="H17" s="131"/>
       <c r="I17" s="61"/>
-      <c r="J17" s="137"/>
+      <c r="J17" s="132"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="133">
@@ -8690,9 +8690,9 @@
       <c r="G18" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H18" s="142"/>
+      <c r="H18" s="131"/>
       <c r="I18" s="61"/>
-      <c r="J18" s="137"/>
+      <c r="J18" s="132"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="133">
@@ -8712,9 +8712,9 @@
       <c r="G19" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="142"/>
+      <c r="H19" s="131"/>
       <c r="I19" s="61"/>
-      <c r="J19" s="137"/>
+      <c r="J19" s="132"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="133">
@@ -8734,9 +8734,9 @@
       <c r="G20" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="142"/>
+      <c r="H20" s="131"/>
       <c r="I20" s="61"/>
-      <c r="J20" s="137"/>
+      <c r="J20" s="132"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="133">
@@ -8756,9 +8756,9 @@
       <c r="G21" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="142"/>
+      <c r="H21" s="131"/>
       <c r="I21" s="61"/>
-      <c r="J21" s="137"/>
+      <c r="J21" s="132"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="133">
@@ -8778,9 +8778,9 @@
       <c r="G22" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H22" s="142"/>
+      <c r="H22" s="131"/>
       <c r="I22" s="61"/>
-      <c r="J22" s="137"/>
+      <c r="J22" s="132"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="133">
@@ -9783,16 +9783,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9809,11 +9804,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9833,7 +9833,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="158" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="118"/>
@@ -9844,14 +9844,14 @@
       <c r="G1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
       <c r="J1" s="126"/>
       <c r="K1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
       <c r="N1" s="126"/>
       <c r="O1" s="125" t="s">
         <v>7</v>
@@ -9864,7 +9864,7 @@
       <c r="S1" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="136"/>
+      <c r="T1" s="138"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="120"/>
@@ -9876,21 +9876,21 @@
       <c r="G2" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
       <c r="J2" s="128"/>
       <c r="K2" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="139"/>
-      <c r="M2" s="139"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
       <c r="N2" s="128"/>
       <c r="O2" s="127"/>
       <c r="P2" s="128"/>
       <c r="Q2" s="127"/>
       <c r="R2" s="128"/>
       <c r="S2" s="127"/>
-      <c r="T2" s="140"/>
+      <c r="T2" s="141"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="120"/>
@@ -9912,7 +9912,7 @@
       <c r="Q3" s="129"/>
       <c r="R3" s="121"/>
       <c r="S3" s="129"/>
-      <c r="T3" s="141"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="122"/>
@@ -9934,36 +9934,36 @@
       <c r="Q4" s="130"/>
       <c r="R4" s="124"/>
       <c r="S4" s="130"/>
-      <c r="T4" s="152"/>
+      <c r="T4" s="157"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="132"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
       <c r="F5" s="126"/>
       <c r="G5" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="132"/>
-      <c r="R5" s="132"/>
-      <c r="S5" s="132"/>
-      <c r="T5" s="136"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="135"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
+      <c r="M5" s="135"/>
+      <c r="N5" s="135"/>
+      <c r="O5" s="135"/>
+      <c r="P5" s="135"/>
+      <c r="Q5" s="135"/>
+      <c r="R5" s="135"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="138"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="136" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="61"/>
@@ -9971,7 +9971,7 @@
       <c r="D6" s="61"/>
       <c r="E6" s="61"/>
       <c r="F6" s="62"/>
-      <c r="G6" s="142" t="s">
+      <c r="G6" s="131" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="61"/>
@@ -9986,10 +9986,10 @@
       <c r="Q6" s="61"/>
       <c r="R6" s="61"/>
       <c r="S6" s="61"/>
-      <c r="T6" s="137"/>
+      <c r="T6" s="132"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="136" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="61"/>
@@ -9997,7 +9997,7 @@
       <c r="D7" s="61"/>
       <c r="E7" s="61"/>
       <c r="F7" s="62"/>
-      <c r="G7" s="142" t="s">
+      <c r="G7" s="131" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="61"/>
@@ -10012,7 +10012,7 @@
       <c r="Q7" s="61"/>
       <c r="R7" s="61"/>
       <c r="S7" s="61"/>
-      <c r="T7" s="137"/>
+      <c r="T7" s="132"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -10211,11 +10211,11 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="136" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="62"/>
-      <c r="C15" s="157" t="s">
+      <c r="C15" s="156" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="62"/>
@@ -10253,31 +10253,31 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="56.25" customHeight="1">
-      <c r="A16" s="155">
+      <c r="A16" s="147">
         <v>1</v>
       </c>
       <c r="B16" s="62"/>
-      <c r="C16" s="156" t="s">
+      <c r="C16" s="148" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="156" t="s">
+      <c r="E16" s="148" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="62"/>
-      <c r="G16" s="147" t="s">
+      <c r="G16" s="155" t="s">
         <v>107</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="62"/>
-      <c r="J16" s="147"/>
+      <c r="J16" s="155"/>
       <c r="K16" s="62"/>
-      <c r="L16" s="150" t="s">
+      <c r="L16" s="152" t="s">
         <v>108</v>
       </c>
       <c r="M16" s="61"/>
       <c r="N16" s="62"/>
-      <c r="O16" s="150" t="s">
+      <c r="O16" s="152" t="s">
         <v>109</v>
       </c>
       <c r="P16" s="61"/>
@@ -10293,27 +10293,27 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="147">
         <v>2</v>
       </c>
       <c r="B17" s="62"/>
-      <c r="C17" s="156" t="s">
+      <c r="C17" s="148" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="62"/>
-      <c r="E17" s="156" t="s">
+      <c r="E17" s="148" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="62"/>
-      <c r="G17" s="147"/>
+      <c r="G17" s="155"/>
       <c r="H17" s="61"/>
       <c r="I17" s="62"/>
-      <c r="J17" s="147"/>
+      <c r="J17" s="155"/>
       <c r="K17" s="62"/>
-      <c r="L17" s="150"/>
+      <c r="L17" s="152"/>
       <c r="M17" s="61"/>
       <c r="N17" s="62"/>
-      <c r="O17" s="150"/>
+      <c r="O17" s="152"/>
       <c r="P17" s="61"/>
       <c r="Q17" s="62"/>
       <c r="R17" s="32"/>
@@ -10327,21 +10327,21 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="155"/>
+      <c r="A18" s="147"/>
       <c r="B18" s="62"/>
-      <c r="C18" s="156"/>
+      <c r="C18" s="148"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="156"/>
+      <c r="E18" s="148"/>
       <c r="F18" s="62"/>
-      <c r="G18" s="147"/>
+      <c r="G18" s="155"/>
       <c r="H18" s="61"/>
       <c r="I18" s="62"/>
-      <c r="J18" s="147"/>
+      <c r="J18" s="155"/>
       <c r="K18" s="62"/>
-      <c r="L18" s="150"/>
+      <c r="L18" s="152"/>
       <c r="M18" s="61"/>
       <c r="N18" s="62"/>
-      <c r="O18" s="150"/>
+      <c r="O18" s="152"/>
       <c r="P18" s="61"/>
       <c r="Q18" s="62"/>
       <c r="R18" s="32"/>
@@ -10355,21 +10355,21 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="155"/>
+      <c r="A19" s="147"/>
       <c r="B19" s="62"/>
-      <c r="C19" s="156"/>
+      <c r="C19" s="148"/>
       <c r="D19" s="62"/>
-      <c r="E19" s="156"/>
+      <c r="E19" s="148"/>
       <c r="F19" s="62"/>
-      <c r="G19" s="147"/>
+      <c r="G19" s="155"/>
       <c r="H19" s="61"/>
       <c r="I19" s="62"/>
-      <c r="J19" s="147"/>
+      <c r="J19" s="155"/>
       <c r="K19" s="62"/>
-      <c r="L19" s="150"/>
+      <c r="L19" s="152"/>
       <c r="M19" s="61"/>
       <c r="N19" s="62"/>
-      <c r="O19" s="150"/>
+      <c r="O19" s="152"/>
       <c r="P19" s="61"/>
       <c r="Q19" s="62"/>
       <c r="R19" s="32"/>
@@ -10383,21 +10383,21 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="155"/>
+      <c r="A20" s="147"/>
       <c r="B20" s="62"/>
-      <c r="C20" s="156"/>
+      <c r="C20" s="148"/>
       <c r="D20" s="62"/>
-      <c r="E20" s="156"/>
+      <c r="E20" s="148"/>
       <c r="F20" s="62"/>
-      <c r="G20" s="147"/>
+      <c r="G20" s="155"/>
       <c r="H20" s="61"/>
       <c r="I20" s="62"/>
-      <c r="J20" s="147"/>
+      <c r="J20" s="155"/>
       <c r="K20" s="62"/>
-      <c r="L20" s="150"/>
+      <c r="L20" s="152"/>
       <c r="M20" s="61"/>
       <c r="N20" s="62"/>
-      <c r="O20" s="150"/>
+      <c r="O20" s="152"/>
       <c r="P20" s="61"/>
       <c r="Q20" s="62"/>
       <c r="R20" s="32"/>
@@ -10411,21 +10411,21 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="155"/>
+      <c r="A21" s="147"/>
       <c r="B21" s="62"/>
-      <c r="C21" s="156"/>
+      <c r="C21" s="148"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="156"/>
+      <c r="E21" s="148"/>
       <c r="F21" s="62"/>
-      <c r="G21" s="147"/>
+      <c r="G21" s="155"/>
       <c r="H21" s="61"/>
       <c r="I21" s="62"/>
-      <c r="J21" s="147"/>
+      <c r="J21" s="155"/>
       <c r="K21" s="62"/>
-      <c r="L21" s="150"/>
+      <c r="L21" s="152"/>
       <c r="M21" s="61"/>
       <c r="N21" s="62"/>
-      <c r="O21" s="150"/>
+      <c r="O21" s="152"/>
       <c r="P21" s="61"/>
       <c r="Q21" s="62"/>
       <c r="R21" s="32"/>
@@ -10439,21 +10439,21 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="155"/>
+      <c r="A22" s="147"/>
       <c r="B22" s="62"/>
-      <c r="C22" s="156"/>
+      <c r="C22" s="148"/>
       <c r="D22" s="62"/>
-      <c r="E22" s="156"/>
+      <c r="E22" s="148"/>
       <c r="F22" s="62"/>
-      <c r="G22" s="147"/>
+      <c r="G22" s="155"/>
       <c r="H22" s="61"/>
       <c r="I22" s="62"/>
-      <c r="J22" s="147"/>
+      <c r="J22" s="155"/>
       <c r="K22" s="62"/>
-      <c r="L22" s="150"/>
+      <c r="L22" s="152"/>
       <c r="M22" s="61"/>
       <c r="N22" s="62"/>
-      <c r="O22" s="150"/>
+      <c r="O22" s="152"/>
       <c r="P22" s="61"/>
       <c r="Q22" s="62"/>
       <c r="R22" s="32"/>
@@ -10467,21 +10467,21 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="155"/>
+      <c r="A23" s="147"/>
       <c r="B23" s="62"/>
-      <c r="C23" s="156"/>
+      <c r="C23" s="148"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="156"/>
+      <c r="E23" s="148"/>
       <c r="F23" s="62"/>
-      <c r="G23" s="147"/>
+      <c r="G23" s="155"/>
       <c r="H23" s="61"/>
       <c r="I23" s="62"/>
-      <c r="J23" s="147"/>
+      <c r="J23" s="155"/>
       <c r="K23" s="62"/>
-      <c r="L23" s="150"/>
+      <c r="L23" s="152"/>
       <c r="M23" s="61"/>
       <c r="N23" s="62"/>
-      <c r="O23" s="150"/>
+      <c r="O23" s="152"/>
       <c r="P23" s="61"/>
       <c r="Q23" s="62"/>
       <c r="R23" s="32"/>
@@ -10495,21 +10495,21 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="155"/>
+      <c r="A24" s="147"/>
       <c r="B24" s="62"/>
-      <c r="C24" s="156"/>
+      <c r="C24" s="148"/>
       <c r="D24" s="62"/>
-      <c r="E24" s="156"/>
+      <c r="E24" s="148"/>
       <c r="F24" s="62"/>
-      <c r="G24" s="147"/>
+      <c r="G24" s="155"/>
       <c r="H24" s="61"/>
       <c r="I24" s="62"/>
-      <c r="J24" s="147"/>
+      <c r="J24" s="155"/>
       <c r="K24" s="62"/>
-      <c r="L24" s="150"/>
+      <c r="L24" s="152"/>
       <c r="M24" s="61"/>
       <c r="N24" s="62"/>
-      <c r="O24" s="150"/>
+      <c r="O24" s="152"/>
       <c r="P24" s="61"/>
       <c r="Q24" s="62"/>
       <c r="R24" s="32"/>
@@ -10523,21 +10523,21 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="155"/>
+      <c r="A25" s="147"/>
       <c r="B25" s="62"/>
-      <c r="C25" s="156"/>
+      <c r="C25" s="148"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="156"/>
+      <c r="E25" s="148"/>
       <c r="F25" s="62"/>
-      <c r="G25" s="147"/>
+      <c r="G25" s="155"/>
       <c r="H25" s="61"/>
       <c r="I25" s="62"/>
-      <c r="J25" s="147"/>
+      <c r="J25" s="155"/>
       <c r="K25" s="62"/>
-      <c r="L25" s="150"/>
+      <c r="L25" s="152"/>
       <c r="M25" s="61"/>
       <c r="N25" s="62"/>
-      <c r="O25" s="150"/>
+      <c r="O25" s="152"/>
       <c r="P25" s="61"/>
       <c r="Q25" s="62"/>
       <c r="R25" s="32"/>
@@ -10551,21 +10551,21 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="155"/>
+      <c r="A26" s="147"/>
       <c r="B26" s="62"/>
-      <c r="C26" s="156"/>
+      <c r="C26" s="148"/>
       <c r="D26" s="62"/>
-      <c r="E26" s="156"/>
+      <c r="E26" s="148"/>
       <c r="F26" s="62"/>
-      <c r="G26" s="147"/>
+      <c r="G26" s="155"/>
       <c r="H26" s="61"/>
       <c r="I26" s="62"/>
-      <c r="J26" s="147"/>
+      <c r="J26" s="155"/>
       <c r="K26" s="62"/>
-      <c r="L26" s="150"/>
+      <c r="L26" s="152"/>
       <c r="M26" s="61"/>
       <c r="N26" s="62"/>
-      <c r="O26" s="150"/>
+      <c r="O26" s="152"/>
       <c r="P26" s="61"/>
       <c r="Q26" s="62"/>
       <c r="R26" s="32"/>
@@ -10579,21 +10579,21 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="155"/>
+      <c r="A27" s="147"/>
       <c r="B27" s="62"/>
-      <c r="C27" s="156"/>
+      <c r="C27" s="148"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="156"/>
+      <c r="E27" s="148"/>
       <c r="F27" s="62"/>
-      <c r="G27" s="147"/>
+      <c r="G27" s="155"/>
       <c r="H27" s="61"/>
       <c r="I27" s="62"/>
-      <c r="J27" s="147"/>
+      <c r="J27" s="155"/>
       <c r="K27" s="62"/>
-      <c r="L27" s="150"/>
+      <c r="L27" s="152"/>
       <c r="M27" s="61"/>
       <c r="N27" s="62"/>
-      <c r="O27" s="150"/>
+      <c r="O27" s="152"/>
       <c r="P27" s="61"/>
       <c r="Q27" s="62"/>
       <c r="R27" s="32"/>
@@ -10607,21 +10607,21 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="155"/>
+      <c r="A28" s="147"/>
       <c r="B28" s="62"/>
-      <c r="C28" s="156"/>
+      <c r="C28" s="148"/>
       <c r="D28" s="62"/>
-      <c r="E28" s="156"/>
+      <c r="E28" s="148"/>
       <c r="F28" s="62"/>
-      <c r="G28" s="147"/>
+      <c r="G28" s="155"/>
       <c r="H28" s="61"/>
       <c r="I28" s="62"/>
-      <c r="J28" s="147"/>
+      <c r="J28" s="155"/>
       <c r="K28" s="62"/>
-      <c r="L28" s="150"/>
+      <c r="L28" s="152"/>
       <c r="M28" s="61"/>
       <c r="N28" s="62"/>
-      <c r="O28" s="150"/>
+      <c r="O28" s="152"/>
       <c r="P28" s="61"/>
       <c r="Q28" s="62"/>
       <c r="R28" s="32"/>
@@ -10635,21 +10635,21 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="155"/>
+      <c r="A29" s="147"/>
       <c r="B29" s="62"/>
-      <c r="C29" s="156"/>
+      <c r="C29" s="148"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="156"/>
+      <c r="E29" s="148"/>
       <c r="F29" s="62"/>
-      <c r="G29" s="147"/>
+      <c r="G29" s="155"/>
       <c r="H29" s="61"/>
       <c r="I29" s="62"/>
-      <c r="J29" s="147"/>
+      <c r="J29" s="155"/>
       <c r="K29" s="62"/>
-      <c r="L29" s="150"/>
+      <c r="L29" s="152"/>
       <c r="M29" s="61"/>
       <c r="N29" s="62"/>
-      <c r="O29" s="150"/>
+      <c r="O29" s="152"/>
       <c r="P29" s="61"/>
       <c r="Q29" s="62"/>
       <c r="R29" s="32"/>
@@ -10663,21 +10663,21 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="155"/>
+      <c r="A30" s="147"/>
       <c r="B30" s="62"/>
-      <c r="C30" s="156"/>
+      <c r="C30" s="148"/>
       <c r="D30" s="62"/>
-      <c r="E30" s="156"/>
+      <c r="E30" s="148"/>
       <c r="F30" s="62"/>
-      <c r="G30" s="147"/>
+      <c r="G30" s="155"/>
       <c r="H30" s="61"/>
       <c r="I30" s="62"/>
-      <c r="J30" s="147"/>
+      <c r="J30" s="155"/>
       <c r="K30" s="62"/>
-      <c r="L30" s="150"/>
+      <c r="L30" s="152"/>
       <c r="M30" s="61"/>
       <c r="N30" s="62"/>
-      <c r="O30" s="150"/>
+      <c r="O30" s="152"/>
       <c r="P30" s="61"/>
       <c r="Q30" s="62"/>
       <c r="R30" s="32"/>
@@ -10691,23 +10691,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="158"/>
-      <c r="B31" s="149"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="148"/>
+      <c r="A31" s="149"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="150"/>
+      <c r="E31" s="151"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="159"/>
       <c r="H31" s="145"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="148"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="151"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="153"/>
       <c r="M31" s="145"/>
-      <c r="N31" s="149"/>
-      <c r="O31" s="151"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="153"/>
       <c r="P31" s="145"/>
-      <c r="Q31" s="149"/>
+      <c r="Q31" s="150"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -11705,6 +11705,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11729,118 +11841,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11863,64 +11863,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="169" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="181" t="s">
+      <c r="B1" s="169"/>
+      <c r="C1" s="170" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="182"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="186"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="184"/>
-      <c r="P1" s="186"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="175"/>
       <c r="Q1" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="184" t="s">
+      <c r="R1" s="173" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="186"/>
+      <c r="S1" s="175"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="180"/>
-      <c r="B2" s="180"/>
-      <c r="C2" s="181" t="s">
+      <c r="A2" s="169"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="170" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="182"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="186"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="175"/>
       <c r="N2" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="187"/>
-      <c r="P2" s="188"/>
+      <c r="O2" s="176"/>
+      <c r="P2" s="177"/>
       <c r="Q2" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="R2" s="189">
+      <c r="R2" s="178">
         <v>44771</v>
       </c>
-      <c r="S2" s="190"/>
+      <c r="S2" s="179"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="51"/>
@@ -11950,1044 +11950,1232 @@
       <c r="B4" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="171" t="s">
+      <c r="C4" s="160" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="172"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="172"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="171" t="s">
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="172"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="172"/>
-      <c r="L4" s="172"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="171" t="s">
+      <c r="I4" s="161"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="160" t="s">
         <v>104</v>
       </c>
-      <c r="O4" s="172"/>
-      <c r="P4" s="173"/>
+      <c r="O4" s="161"/>
+      <c r="P4" s="162"/>
       <c r="Q4" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="171" t="s">
+      <c r="R4" s="160" t="s">
         <v>106</v>
       </c>
-      <c r="S4" s="173"/>
+      <c r="S4" s="162"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="55"/>
       <c r="B5" s="56"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="174"/>
-      <c r="K5" s="174"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="175"/>
-      <c r="O5" s="176"/>
-      <c r="P5" s="177"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="163"/>
+      <c r="J5" s="163"/>
+      <c r="K5" s="163"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="163"/>
+      <c r="N5" s="164"/>
+      <c r="O5" s="165"/>
+      <c r="P5" s="166"/>
       <c r="Q5" s="55"/>
-      <c r="R5" s="178"/>
-      <c r="S5" s="179"/>
+      <c r="R5" s="167"/>
+      <c r="S5" s="168"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="57"/>
       <c r="B6" s="57"/>
-      <c r="C6" s="160"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="160"/>
-      <c r="J6" s="160"/>
-      <c r="K6" s="160"/>
-      <c r="L6" s="160"/>
-      <c r="M6" s="160"/>
-      <c r="N6" s="168"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="170"/>
+      <c r="C6" s="180"/>
+      <c r="D6" s="180"/>
+      <c r="E6" s="180"/>
+      <c r="F6" s="180"/>
+      <c r="G6" s="180"/>
+      <c r="H6" s="180"/>
+      <c r="I6" s="180"/>
+      <c r="J6" s="180"/>
+      <c r="K6" s="180"/>
+      <c r="L6" s="180"/>
+      <c r="M6" s="180"/>
+      <c r="N6" s="185"/>
+      <c r="O6" s="186"/>
+      <c r="P6" s="187"/>
       <c r="Q6" s="58"/>
-      <c r="R6" s="167"/>
-      <c r="S6" s="167"/>
+      <c r="R6" s="184"/>
+      <c r="S6" s="184"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="57"/>
       <c r="B7" s="57"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="160"/>
-      <c r="K7" s="160"/>
-      <c r="L7" s="160"/>
-      <c r="M7" s="160"/>
-      <c r="N7" s="164"/>
-      <c r="O7" s="165"/>
-      <c r="P7" s="166"/>
+      <c r="C7" s="180"/>
+      <c r="D7" s="180"/>
+      <c r="E7" s="180"/>
+      <c r="F7" s="180"/>
+      <c r="G7" s="180"/>
+      <c r="H7" s="180"/>
+      <c r="I7" s="180"/>
+      <c r="J7" s="180"/>
+      <c r="K7" s="180"/>
+      <c r="L7" s="180"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="181"/>
+      <c r="O7" s="182"/>
+      <c r="P7" s="183"/>
       <c r="Q7" s="58"/>
-      <c r="R7" s="167"/>
-      <c r="S7" s="167"/>
+      <c r="R7" s="184"/>
+      <c r="S7" s="184"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="57"/>
       <c r="B8" s="57"/>
-      <c r="C8" s="160"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="160"/>
-      <c r="I8" s="160"/>
-      <c r="J8" s="160"/>
-      <c r="K8" s="160"/>
-      <c r="L8" s="160"/>
-      <c r="M8" s="160"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="165"/>
-      <c r="P8" s="166"/>
+      <c r="C8" s="180"/>
+      <c r="D8" s="180"/>
+      <c r="E8" s="180"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="180"/>
+      <c r="H8" s="180"/>
+      <c r="I8" s="180"/>
+      <c r="J8" s="180"/>
+      <c r="K8" s="180"/>
+      <c r="L8" s="180"/>
+      <c r="M8" s="180"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="182"/>
+      <c r="P8" s="183"/>
       <c r="Q8" s="58"/>
-      <c r="R8" s="167"/>
-      <c r="S8" s="167"/>
+      <c r="R8" s="184"/>
+      <c r="S8" s="184"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="57"/>
       <c r="B9" s="57"/>
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160"/>
-      <c r="J9" s="160"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="160"/>
-      <c r="M9" s="160"/>
-      <c r="N9" s="164"/>
-      <c r="O9" s="165"/>
-      <c r="P9" s="166"/>
+      <c r="C9" s="180"/>
+      <c r="D9" s="180"/>
+      <c r="E9" s="180"/>
+      <c r="F9" s="180"/>
+      <c r="G9" s="180"/>
+      <c r="H9" s="180"/>
+      <c r="I9" s="180"/>
+      <c r="J9" s="180"/>
+      <c r="K9" s="180"/>
+      <c r="L9" s="180"/>
+      <c r="M9" s="180"/>
+      <c r="N9" s="181"/>
+      <c r="O9" s="182"/>
+      <c r="P9" s="183"/>
       <c r="Q9" s="57"/>
-      <c r="R9" s="167"/>
-      <c r="S9" s="167"/>
+      <c r="R9" s="184"/>
+      <c r="S9" s="184"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="57"/>
       <c r="B10" s="57"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="161"/>
-      <c r="I10" s="162"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="162"/>
-      <c r="L10" s="162"/>
-      <c r="M10" s="163"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="165"/>
-      <c r="P10" s="166"/>
+      <c r="C10" s="180"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="180"/>
+      <c r="F10" s="180"/>
+      <c r="G10" s="180"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="189"/>
+      <c r="J10" s="189"/>
+      <c r="K10" s="189"/>
+      <c r="L10" s="189"/>
+      <c r="M10" s="190"/>
+      <c r="N10" s="181"/>
+      <c r="O10" s="182"/>
+      <c r="P10" s="183"/>
       <c r="Q10" s="58"/>
-      <c r="R10" s="167"/>
-      <c r="S10" s="167"/>
+      <c r="R10" s="184"/>
+      <c r="S10" s="184"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="57"/>
       <c r="B11" s="57"/>
-      <c r="C11" s="160"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="160"/>
-      <c r="F11" s="160"/>
-      <c r="G11" s="160"/>
-      <c r="H11" s="161"/>
-      <c r="I11" s="162"/>
-      <c r="J11" s="162"/>
-      <c r="K11" s="162"/>
-      <c r="L11" s="162"/>
-      <c r="M11" s="163"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="165"/>
-      <c r="P11" s="166"/>
+      <c r="C11" s="180"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="180"/>
+      <c r="F11" s="180"/>
+      <c r="G11" s="180"/>
+      <c r="H11" s="188"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="189"/>
+      <c r="K11" s="189"/>
+      <c r="L11" s="189"/>
+      <c r="M11" s="190"/>
+      <c r="N11" s="181"/>
+      <c r="O11" s="182"/>
+      <c r="P11" s="183"/>
       <c r="Q11" s="57"/>
-      <c r="R11" s="167"/>
-      <c r="S11" s="167"/>
+      <c r="R11" s="184"/>
+      <c r="S11" s="184"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="57"/>
       <c r="B12" s="57"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="160"/>
-      <c r="E12" s="160"/>
-      <c r="F12" s="160"/>
-      <c r="G12" s="160"/>
-      <c r="H12" s="161"/>
-      <c r="I12" s="162"/>
-      <c r="J12" s="162"/>
-      <c r="K12" s="162"/>
-      <c r="L12" s="162"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="164"/>
-      <c r="O12" s="165"/>
-      <c r="P12" s="166"/>
+      <c r="C12" s="180"/>
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="180"/>
+      <c r="G12" s="180"/>
+      <c r="H12" s="188"/>
+      <c r="I12" s="189"/>
+      <c r="J12" s="189"/>
+      <c r="K12" s="189"/>
+      <c r="L12" s="189"/>
+      <c r="M12" s="190"/>
+      <c r="N12" s="181"/>
+      <c r="O12" s="182"/>
+      <c r="P12" s="183"/>
       <c r="Q12" s="57"/>
-      <c r="R12" s="167"/>
-      <c r="S12" s="167"/>
+      <c r="R12" s="184"/>
+      <c r="S12" s="184"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="57"/>
       <c r="B13" s="57"/>
-      <c r="C13" s="160"/>
-      <c r="D13" s="160"/>
-      <c r="E13" s="160"/>
-      <c r="F13" s="160"/>
-      <c r="G13" s="160"/>
-      <c r="H13" s="161"/>
-      <c r="I13" s="162"/>
-      <c r="J13" s="162"/>
-      <c r="K13" s="162"/>
-      <c r="L13" s="162"/>
-      <c r="M13" s="163"/>
-      <c r="N13" s="164"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="166"/>
+      <c r="C13" s="180"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="180"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="180"/>
+      <c r="H13" s="188"/>
+      <c r="I13" s="189"/>
+      <c r="J13" s="189"/>
+      <c r="K13" s="189"/>
+      <c r="L13" s="189"/>
+      <c r="M13" s="190"/>
+      <c r="N13" s="181"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="183"/>
       <c r="Q13" s="57"/>
-      <c r="R13" s="167"/>
-      <c r="S13" s="167"/>
+      <c r="R13" s="184"/>
+      <c r="S13" s="184"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="57"/>
       <c r="B14" s="57"/>
-      <c r="C14" s="160"/>
-      <c r="D14" s="160"/>
-      <c r="E14" s="160"/>
-      <c r="F14" s="160"/>
-      <c r="G14" s="160"/>
-      <c r="H14" s="161"/>
-      <c r="I14" s="162"/>
-      <c r="J14" s="162"/>
-      <c r="K14" s="162"/>
-      <c r="L14" s="162"/>
-      <c r="M14" s="163"/>
-      <c r="N14" s="164"/>
-      <c r="O14" s="165"/>
-      <c r="P14" s="166"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="180"/>
+      <c r="F14" s="180"/>
+      <c r="G14" s="180"/>
+      <c r="H14" s="188"/>
+      <c r="I14" s="189"/>
+      <c r="J14" s="189"/>
+      <c r="K14" s="189"/>
+      <c r="L14" s="189"/>
+      <c r="M14" s="190"/>
+      <c r="N14" s="181"/>
+      <c r="O14" s="182"/>
+      <c r="P14" s="183"/>
       <c r="Q14" s="57"/>
-      <c r="R14" s="167"/>
-      <c r="S14" s="167"/>
+      <c r="R14" s="184"/>
+      <c r="S14" s="184"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="57"/>
       <c r="B15" s="57"/>
-      <c r="C15" s="160"/>
-      <c r="D15" s="160"/>
-      <c r="E15" s="160"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="160"/>
-      <c r="H15" s="161"/>
-      <c r="I15" s="162"/>
-      <c r="J15" s="162"/>
-      <c r="K15" s="162"/>
-      <c r="L15" s="162"/>
-      <c r="M15" s="163"/>
-      <c r="N15" s="164"/>
-      <c r="O15" s="165"/>
-      <c r="P15" s="166"/>
+      <c r="C15" s="180"/>
+      <c r="D15" s="180"/>
+      <c r="E15" s="180"/>
+      <c r="F15" s="180"/>
+      <c r="G15" s="180"/>
+      <c r="H15" s="188"/>
+      <c r="I15" s="189"/>
+      <c r="J15" s="189"/>
+      <c r="K15" s="189"/>
+      <c r="L15" s="189"/>
+      <c r="M15" s="190"/>
+      <c r="N15" s="181"/>
+      <c r="O15" s="182"/>
+      <c r="P15" s="183"/>
       <c r="Q15" s="57"/>
-      <c r="R15" s="167"/>
-      <c r="S15" s="167"/>
+      <c r="R15" s="184"/>
+      <c r="S15" s="184"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="57"/>
       <c r="B16" s="57"/>
-      <c r="C16" s="160"/>
-      <c r="D16" s="160"/>
-      <c r="E16" s="160"/>
-      <c r="F16" s="160"/>
-      <c r="G16" s="160"/>
-      <c r="H16" s="161"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="162"/>
-      <c r="K16" s="162"/>
-      <c r="L16" s="162"/>
-      <c r="M16" s="163"/>
-      <c r="N16" s="164"/>
-      <c r="O16" s="165"/>
-      <c r="P16" s="166"/>
+      <c r="C16" s="180"/>
+      <c r="D16" s="180"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="180"/>
+      <c r="G16" s="180"/>
+      <c r="H16" s="188"/>
+      <c r="I16" s="189"/>
+      <c r="J16" s="189"/>
+      <c r="K16" s="189"/>
+      <c r="L16" s="189"/>
+      <c r="M16" s="190"/>
+      <c r="N16" s="181"/>
+      <c r="O16" s="182"/>
+      <c r="P16" s="183"/>
       <c r="Q16" s="57"/>
-      <c r="R16" s="167"/>
-      <c r="S16" s="167"/>
+      <c r="R16" s="184"/>
+      <c r="S16" s="184"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="57"/>
       <c r="B17" s="57"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="160"/>
-      <c r="E17" s="160"/>
-      <c r="F17" s="160"/>
-      <c r="G17" s="160"/>
-      <c r="H17" s="161"/>
-      <c r="I17" s="162"/>
-      <c r="J17" s="162"/>
-      <c r="K17" s="162"/>
-      <c r="L17" s="162"/>
-      <c r="M17" s="163"/>
-      <c r="N17" s="164"/>
-      <c r="O17" s="165"/>
-      <c r="P17" s="166"/>
+      <c r="C17" s="180"/>
+      <c r="D17" s="180"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="180"/>
+      <c r="G17" s="180"/>
+      <c r="H17" s="188"/>
+      <c r="I17" s="189"/>
+      <c r="J17" s="189"/>
+      <c r="K17" s="189"/>
+      <c r="L17" s="189"/>
+      <c r="M17" s="190"/>
+      <c r="N17" s="181"/>
+      <c r="O17" s="182"/>
+      <c r="P17" s="183"/>
       <c r="Q17" s="57"/>
-      <c r="R17" s="167"/>
-      <c r="S17" s="167"/>
+      <c r="R17" s="184"/>
+      <c r="S17" s="184"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="57"/>
       <c r="B18" s="57"/>
-      <c r="C18" s="160"/>
-      <c r="D18" s="160"/>
-      <c r="E18" s="160"/>
-      <c r="F18" s="160"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="161"/>
-      <c r="I18" s="162"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="162"/>
-      <c r="L18" s="162"/>
-      <c r="M18" s="163"/>
-      <c r="N18" s="164"/>
-      <c r="O18" s="165"/>
-      <c r="P18" s="166"/>
+      <c r="C18" s="180"/>
+      <c r="D18" s="180"/>
+      <c r="E18" s="180"/>
+      <c r="F18" s="180"/>
+      <c r="G18" s="180"/>
+      <c r="H18" s="188"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="189"/>
+      <c r="K18" s="189"/>
+      <c r="L18" s="189"/>
+      <c r="M18" s="190"/>
+      <c r="N18" s="181"/>
+      <c r="O18" s="182"/>
+      <c r="P18" s="183"/>
       <c r="Q18" s="57"/>
-      <c r="R18" s="167"/>
-      <c r="S18" s="167"/>
+      <c r="R18" s="184"/>
+      <c r="S18" s="184"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
-      <c r="C19" s="160"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="160"/>
-      <c r="F19" s="160"/>
-      <c r="G19" s="160"/>
-      <c r="H19" s="161"/>
-      <c r="I19" s="162"/>
-      <c r="J19" s="162"/>
-      <c r="K19" s="162"/>
-      <c r="L19" s="162"/>
-      <c r="M19" s="163"/>
-      <c r="N19" s="164"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="166"/>
+      <c r="C19" s="180"/>
+      <c r="D19" s="180"/>
+      <c r="E19" s="180"/>
+      <c r="F19" s="180"/>
+      <c r="G19" s="180"/>
+      <c r="H19" s="188"/>
+      <c r="I19" s="189"/>
+      <c r="J19" s="189"/>
+      <c r="K19" s="189"/>
+      <c r="L19" s="189"/>
+      <c r="M19" s="190"/>
+      <c r="N19" s="181"/>
+      <c r="O19" s="182"/>
+      <c r="P19" s="183"/>
       <c r="Q19" s="57"/>
-      <c r="R19" s="167"/>
-      <c r="S19" s="167"/>
+      <c r="R19" s="184"/>
+      <c r="S19" s="184"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="57"/>
       <c r="B20" s="57"/>
-      <c r="C20" s="160"/>
-      <c r="D20" s="160"/>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="161"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="162"/>
-      <c r="K20" s="162"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="163"/>
-      <c r="N20" s="164"/>
-      <c r="O20" s="165"/>
-      <c r="P20" s="166"/>
+      <c r="C20" s="180"/>
+      <c r="D20" s="180"/>
+      <c r="E20" s="180"/>
+      <c r="F20" s="180"/>
+      <c r="G20" s="180"/>
+      <c r="H20" s="188"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="189"/>
+      <c r="K20" s="189"/>
+      <c r="L20" s="189"/>
+      <c r="M20" s="190"/>
+      <c r="N20" s="181"/>
+      <c r="O20" s="182"/>
+      <c r="P20" s="183"/>
       <c r="Q20" s="57"/>
-      <c r="R20" s="167"/>
-      <c r="S20" s="167"/>
+      <c r="R20" s="184"/>
+      <c r="S20" s="184"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="57"/>
       <c r="B21" s="57"/>
-      <c r="C21" s="160"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="160"/>
-      <c r="F21" s="160"/>
-      <c r="G21" s="160"/>
-      <c r="H21" s="161"/>
-      <c r="I21" s="162"/>
-      <c r="J21" s="162"/>
-      <c r="K21" s="162"/>
-      <c r="L21" s="162"/>
-      <c r="M21" s="163"/>
-      <c r="N21" s="164"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="166"/>
+      <c r="C21" s="180"/>
+      <c r="D21" s="180"/>
+      <c r="E21" s="180"/>
+      <c r="F21" s="180"/>
+      <c r="G21" s="180"/>
+      <c r="H21" s="188"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="189"/>
+      <c r="K21" s="189"/>
+      <c r="L21" s="189"/>
+      <c r="M21" s="190"/>
+      <c r="N21" s="181"/>
+      <c r="O21" s="182"/>
+      <c r="P21" s="183"/>
       <c r="Q21" s="57"/>
-      <c r="R21" s="167"/>
-      <c r="S21" s="167"/>
+      <c r="R21" s="184"/>
+      <c r="S21" s="184"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="57"/>
       <c r="B22" s="57"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="160"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="161"/>
-      <c r="I22" s="162"/>
-      <c r="J22" s="162"/>
-      <c r="K22" s="162"/>
-      <c r="L22" s="162"/>
-      <c r="M22" s="163"/>
-      <c r="N22" s="164"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="166"/>
+      <c r="C22" s="180"/>
+      <c r="D22" s="180"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="180"/>
+      <c r="G22" s="180"/>
+      <c r="H22" s="188"/>
+      <c r="I22" s="189"/>
+      <c r="J22" s="189"/>
+      <c r="K22" s="189"/>
+      <c r="L22" s="189"/>
+      <c r="M22" s="190"/>
+      <c r="N22" s="181"/>
+      <c r="O22" s="182"/>
+      <c r="P22" s="183"/>
       <c r="Q22" s="57"/>
-      <c r="R22" s="167"/>
-      <c r="S22" s="167"/>
+      <c r="R22" s="184"/>
+      <c r="S22" s="184"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="57"/>
       <c r="B23" s="57"/>
-      <c r="C23" s="160"/>
-      <c r="D23" s="160"/>
-      <c r="E23" s="160"/>
-      <c r="F23" s="160"/>
-      <c r="G23" s="160"/>
-      <c r="H23" s="161"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="162"/>
-      <c r="K23" s="162"/>
-      <c r="L23" s="162"/>
-      <c r="M23" s="163"/>
-      <c r="N23" s="164"/>
-      <c r="O23" s="165"/>
-      <c r="P23" s="166"/>
+      <c r="C23" s="180"/>
+      <c r="D23" s="180"/>
+      <c r="E23" s="180"/>
+      <c r="F23" s="180"/>
+      <c r="G23" s="180"/>
+      <c r="H23" s="188"/>
+      <c r="I23" s="189"/>
+      <c r="J23" s="189"/>
+      <c r="K23" s="189"/>
+      <c r="L23" s="189"/>
+      <c r="M23" s="190"/>
+      <c r="N23" s="181"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
       <c r="Q23" s="57"/>
-      <c r="R23" s="167"/>
-      <c r="S23" s="167"/>
+      <c r="R23" s="184"/>
+      <c r="S23" s="184"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="57"/>
       <c r="B24" s="57"/>
-      <c r="C24" s="160"/>
-      <c r="D24" s="160"/>
-      <c r="E24" s="160"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="161"/>
-      <c r="I24" s="162"/>
-      <c r="J24" s="162"/>
-      <c r="K24" s="162"/>
-      <c r="L24" s="162"/>
-      <c r="M24" s="163"/>
-      <c r="N24" s="164"/>
-      <c r="O24" s="165"/>
-      <c r="P24" s="166"/>
+      <c r="C24" s="180"/>
+      <c r="D24" s="180"/>
+      <c r="E24" s="180"/>
+      <c r="F24" s="180"/>
+      <c r="G24" s="180"/>
+      <c r="H24" s="188"/>
+      <c r="I24" s="189"/>
+      <c r="J24" s="189"/>
+      <c r="K24" s="189"/>
+      <c r="L24" s="189"/>
+      <c r="M24" s="190"/>
+      <c r="N24" s="181"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
       <c r="Q24" s="57"/>
-      <c r="R24" s="167"/>
-      <c r="S24" s="167"/>
+      <c r="R24" s="184"/>
+      <c r="S24" s="184"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="57"/>
       <c r="B25" s="57"/>
-      <c r="C25" s="160"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="161"/>
-      <c r="I25" s="162"/>
-      <c r="J25" s="162"/>
-      <c r="K25" s="162"/>
-      <c r="L25" s="162"/>
-      <c r="M25" s="163"/>
-      <c r="N25" s="164"/>
-      <c r="O25" s="165"/>
-      <c r="P25" s="166"/>
+      <c r="C25" s="180"/>
+      <c r="D25" s="180"/>
+      <c r="E25" s="180"/>
+      <c r="F25" s="180"/>
+      <c r="G25" s="180"/>
+      <c r="H25" s="188"/>
+      <c r="I25" s="189"/>
+      <c r="J25" s="189"/>
+      <c r="K25" s="189"/>
+      <c r="L25" s="189"/>
+      <c r="M25" s="190"/>
+      <c r="N25" s="181"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
       <c r="Q25" s="57"/>
-      <c r="R25" s="167"/>
-      <c r="S25" s="167"/>
+      <c r="R25" s="184"/>
+      <c r="S25" s="184"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="57"/>
       <c r="B26" s="57"/>
-      <c r="C26" s="160"/>
-      <c r="D26" s="160"/>
-      <c r="E26" s="160"/>
-      <c r="F26" s="160"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="161"/>
-      <c r="I26" s="162"/>
-      <c r="J26" s="162"/>
-      <c r="K26" s="162"/>
-      <c r="L26" s="162"/>
-      <c r="M26" s="163"/>
-      <c r="N26" s="164"/>
-      <c r="O26" s="165"/>
-      <c r="P26" s="166"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="180"/>
+      <c r="E26" s="180"/>
+      <c r="F26" s="180"/>
+      <c r="G26" s="180"/>
+      <c r="H26" s="188"/>
+      <c r="I26" s="189"/>
+      <c r="J26" s="189"/>
+      <c r="K26" s="189"/>
+      <c r="L26" s="189"/>
+      <c r="M26" s="190"/>
+      <c r="N26" s="181"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
       <c r="Q26" s="57"/>
-      <c r="R26" s="167"/>
-      <c r="S26" s="167"/>
+      <c r="R26" s="184"/>
+      <c r="S26" s="184"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="57"/>
       <c r="B27" s="57"/>
-      <c r="C27" s="160"/>
-      <c r="D27" s="160"/>
-      <c r="E27" s="160"/>
-      <c r="F27" s="160"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="161"/>
-      <c r="I27" s="162"/>
-      <c r="J27" s="162"/>
-      <c r="K27" s="162"/>
-      <c r="L27" s="162"/>
-      <c r="M27" s="163"/>
-      <c r="N27" s="164"/>
-      <c r="O27" s="165"/>
-      <c r="P27" s="166"/>
+      <c r="C27" s="180"/>
+      <c r="D27" s="180"/>
+      <c r="E27" s="180"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="180"/>
+      <c r="H27" s="188"/>
+      <c r="I27" s="189"/>
+      <c r="J27" s="189"/>
+      <c r="K27" s="189"/>
+      <c r="L27" s="189"/>
+      <c r="M27" s="190"/>
+      <c r="N27" s="181"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
       <c r="Q27" s="57"/>
-      <c r="R27" s="167"/>
-      <c r="S27" s="167"/>
+      <c r="R27" s="184"/>
+      <c r="S27" s="184"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="57"/>
       <c r="B28" s="57"/>
-      <c r="C28" s="160"/>
-      <c r="D28" s="160"/>
-      <c r="E28" s="160"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="160"/>
-      <c r="H28" s="161"/>
-      <c r="I28" s="162"/>
-      <c r="J28" s="162"/>
-      <c r="K28" s="162"/>
-      <c r="L28" s="162"/>
-      <c r="M28" s="163"/>
-      <c r="N28" s="164"/>
-      <c r="O28" s="165"/>
-      <c r="P28" s="166"/>
+      <c r="C28" s="180"/>
+      <c r="D28" s="180"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="180"/>
+      <c r="G28" s="180"/>
+      <c r="H28" s="188"/>
+      <c r="I28" s="189"/>
+      <c r="J28" s="189"/>
+      <c r="K28" s="189"/>
+      <c r="L28" s="189"/>
+      <c r="M28" s="190"/>
+      <c r="N28" s="181"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
       <c r="Q28" s="57"/>
-      <c r="R28" s="167"/>
-      <c r="S28" s="167"/>
+      <c r="R28" s="184"/>
+      <c r="S28" s="184"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="57"/>
       <c r="B29" s="57"/>
-      <c r="C29" s="160"/>
-      <c r="D29" s="160"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="161"/>
-      <c r="I29" s="162"/>
-      <c r="J29" s="162"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="162"/>
-      <c r="M29" s="163"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="165"/>
-      <c r="P29" s="166"/>
+      <c r="C29" s="180"/>
+      <c r="D29" s="180"/>
+      <c r="E29" s="180"/>
+      <c r="F29" s="180"/>
+      <c r="G29" s="180"/>
+      <c r="H29" s="188"/>
+      <c r="I29" s="189"/>
+      <c r="J29" s="189"/>
+      <c r="K29" s="189"/>
+      <c r="L29" s="189"/>
+      <c r="M29" s="190"/>
+      <c r="N29" s="181"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
       <c r="Q29" s="57"/>
-      <c r="R29" s="167"/>
-      <c r="S29" s="167"/>
+      <c r="R29" s="184"/>
+      <c r="S29" s="184"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="57"/>
       <c r="B30" s="57"/>
-      <c r="C30" s="160"/>
-      <c r="D30" s="160"/>
-      <c r="E30" s="160"/>
-      <c r="F30" s="160"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="161"/>
-      <c r="I30" s="162"/>
-      <c r="J30" s="162"/>
-      <c r="K30" s="162"/>
-      <c r="L30" s="162"/>
-      <c r="M30" s="163"/>
-      <c r="N30" s="164"/>
-      <c r="O30" s="165"/>
-      <c r="P30" s="166"/>
+      <c r="C30" s="180"/>
+      <c r="D30" s="180"/>
+      <c r="E30" s="180"/>
+      <c r="F30" s="180"/>
+      <c r="G30" s="180"/>
+      <c r="H30" s="188"/>
+      <c r="I30" s="189"/>
+      <c r="J30" s="189"/>
+      <c r="K30" s="189"/>
+      <c r="L30" s="189"/>
+      <c r="M30" s="190"/>
+      <c r="N30" s="181"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
       <c r="Q30" s="57"/>
-      <c r="R30" s="167"/>
-      <c r="S30" s="167"/>
+      <c r="R30" s="184"/>
+      <c r="S30" s="184"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="57"/>
       <c r="B31" s="57"/>
-      <c r="C31" s="160"/>
-      <c r="D31" s="160"/>
-      <c r="E31" s="160"/>
-      <c r="F31" s="160"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="161"/>
-      <c r="I31" s="162"/>
-      <c r="J31" s="162"/>
-      <c r="K31" s="162"/>
-      <c r="L31" s="162"/>
-      <c r="M31" s="163"/>
-      <c r="N31" s="164"/>
-      <c r="O31" s="165"/>
-      <c r="P31" s="166"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="180"/>
+      <c r="E31" s="180"/>
+      <c r="F31" s="180"/>
+      <c r="G31" s="180"/>
+      <c r="H31" s="188"/>
+      <c r="I31" s="189"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="189"/>
+      <c r="L31" s="189"/>
+      <c r="M31" s="190"/>
+      <c r="N31" s="181"/>
+      <c r="O31" s="182"/>
+      <c r="P31" s="183"/>
       <c r="Q31" s="57"/>
-      <c r="R31" s="167"/>
-      <c r="S31" s="167"/>
+      <c r="R31" s="184"/>
+      <c r="S31" s="184"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="57"/>
       <c r="B32" s="57"/>
-      <c r="C32" s="160"/>
-      <c r="D32" s="160"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="160"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="161"/>
-      <c r="I32" s="162"/>
-      <c r="J32" s="162"/>
-      <c r="K32" s="162"/>
-      <c r="L32" s="162"/>
-      <c r="M32" s="163"/>
-      <c r="N32" s="164"/>
-      <c r="O32" s="165"/>
-      <c r="P32" s="166"/>
+      <c r="C32" s="180"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="180"/>
+      <c r="G32" s="180"/>
+      <c r="H32" s="188"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="189"/>
+      <c r="L32" s="189"/>
+      <c r="M32" s="190"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="183"/>
       <c r="Q32" s="57"/>
-      <c r="R32" s="167"/>
-      <c r="S32" s="167"/>
+      <c r="R32" s="184"/>
+      <c r="S32" s="184"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="57"/>
       <c r="B33" s="57"/>
-      <c r="C33" s="160"/>
-      <c r="D33" s="160"/>
-      <c r="E33" s="160"/>
-      <c r="F33" s="160"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="161"/>
-      <c r="I33" s="162"/>
-      <c r="J33" s="162"/>
-      <c r="K33" s="162"/>
-      <c r="L33" s="162"/>
-      <c r="M33" s="163"/>
-      <c r="N33" s="164"/>
-      <c r="O33" s="165"/>
-      <c r="P33" s="166"/>
+      <c r="C33" s="180"/>
+      <c r="D33" s="180"/>
+      <c r="E33" s="180"/>
+      <c r="F33" s="180"/>
+      <c r="G33" s="180"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="189"/>
+      <c r="K33" s="189"/>
+      <c r="L33" s="189"/>
+      <c r="M33" s="190"/>
+      <c r="N33" s="181"/>
+      <c r="O33" s="182"/>
+      <c r="P33" s="183"/>
       <c r="Q33" s="57"/>
-      <c r="R33" s="167"/>
-      <c r="S33" s="167"/>
+      <c r="R33" s="184"/>
+      <c r="S33" s="184"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="57"/>
       <c r="B34" s="57"/>
-      <c r="C34" s="160"/>
-      <c r="D34" s="160"/>
-      <c r="E34" s="160"/>
-      <c r="F34" s="160"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="161"/>
-      <c r="I34" s="162"/>
-      <c r="J34" s="162"/>
-      <c r="K34" s="162"/>
-      <c r="L34" s="162"/>
-      <c r="M34" s="163"/>
-      <c r="N34" s="164"/>
-      <c r="O34" s="165"/>
-      <c r="P34" s="166"/>
+      <c r="C34" s="180"/>
+      <c r="D34" s="180"/>
+      <c r="E34" s="180"/>
+      <c r="F34" s="180"/>
+      <c r="G34" s="180"/>
+      <c r="H34" s="188"/>
+      <c r="I34" s="189"/>
+      <c r="J34" s="189"/>
+      <c r="K34" s="189"/>
+      <c r="L34" s="189"/>
+      <c r="M34" s="190"/>
+      <c r="N34" s="181"/>
+      <c r="O34" s="182"/>
+      <c r="P34" s="183"/>
       <c r="Q34" s="57"/>
-      <c r="R34" s="167"/>
-      <c r="S34" s="167"/>
+      <c r="R34" s="184"/>
+      <c r="S34" s="184"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="57"/>
       <c r="B35" s="57"/>
-      <c r="C35" s="160"/>
-      <c r="D35" s="160"/>
-      <c r="E35" s="160"/>
-      <c r="F35" s="160"/>
-      <c r="G35" s="160"/>
-      <c r="H35" s="161"/>
-      <c r="I35" s="162"/>
-      <c r="J35" s="162"/>
-      <c r="K35" s="162"/>
-      <c r="L35" s="162"/>
-      <c r="M35" s="163"/>
-      <c r="N35" s="164"/>
-      <c r="O35" s="165"/>
-      <c r="P35" s="166"/>
+      <c r="C35" s="180"/>
+      <c r="D35" s="180"/>
+      <c r="E35" s="180"/>
+      <c r="F35" s="180"/>
+      <c r="G35" s="180"/>
+      <c r="H35" s="188"/>
+      <c r="I35" s="189"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="189"/>
+      <c r="L35" s="189"/>
+      <c r="M35" s="190"/>
+      <c r="N35" s="181"/>
+      <c r="O35" s="182"/>
+      <c r="P35" s="183"/>
       <c r="Q35" s="57"/>
-      <c r="R35" s="167"/>
-      <c r="S35" s="167"/>
+      <c r="R35" s="184"/>
+      <c r="S35" s="184"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="57"/>
       <c r="B36" s="57"/>
-      <c r="C36" s="160"/>
-      <c r="D36" s="160"/>
-      <c r="E36" s="160"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="161"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="162"/>
-      <c r="K36" s="162"/>
-      <c r="L36" s="162"/>
-      <c r="M36" s="163"/>
-      <c r="N36" s="164"/>
-      <c r="O36" s="165"/>
-      <c r="P36" s="166"/>
+      <c r="C36" s="180"/>
+      <c r="D36" s="180"/>
+      <c r="E36" s="180"/>
+      <c r="F36" s="180"/>
+      <c r="G36" s="180"/>
+      <c r="H36" s="188"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="189"/>
+      <c r="K36" s="189"/>
+      <c r="L36" s="189"/>
+      <c r="M36" s="190"/>
+      <c r="N36" s="181"/>
+      <c r="O36" s="182"/>
+      <c r="P36" s="183"/>
       <c r="Q36" s="57"/>
-      <c r="R36" s="167"/>
-      <c r="S36" s="167"/>
+      <c r="R36" s="184"/>
+      <c r="S36" s="184"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="57"/>
       <c r="B37" s="57"/>
-      <c r="C37" s="160"/>
-      <c r="D37" s="160"/>
-      <c r="E37" s="160"/>
-      <c r="F37" s="160"/>
-      <c r="G37" s="160"/>
-      <c r="H37" s="161"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
-      <c r="K37" s="162"/>
-      <c r="L37" s="162"/>
-      <c r="M37" s="163"/>
-      <c r="N37" s="164"/>
-      <c r="O37" s="165"/>
-      <c r="P37" s="166"/>
+      <c r="C37" s="180"/>
+      <c r="D37" s="180"/>
+      <c r="E37" s="180"/>
+      <c r="F37" s="180"/>
+      <c r="G37" s="180"/>
+      <c r="H37" s="188"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="189"/>
+      <c r="K37" s="189"/>
+      <c r="L37" s="189"/>
+      <c r="M37" s="190"/>
+      <c r="N37" s="181"/>
+      <c r="O37" s="182"/>
+      <c r="P37" s="183"/>
       <c r="Q37" s="57"/>
-      <c r="R37" s="167"/>
-      <c r="S37" s="167"/>
+      <c r="R37" s="184"/>
+      <c r="S37" s="184"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="57"/>
       <c r="B38" s="57"/>
-      <c r="C38" s="160"/>
-      <c r="D38" s="160"/>
-      <c r="E38" s="160"/>
-      <c r="F38" s="160"/>
-      <c r="G38" s="160"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="162"/>
-      <c r="L38" s="162"/>
-      <c r="M38" s="163"/>
-      <c r="N38" s="164"/>
-      <c r="O38" s="165"/>
-      <c r="P38" s="166"/>
+      <c r="C38" s="180"/>
+      <c r="D38" s="180"/>
+      <c r="E38" s="180"/>
+      <c r="F38" s="180"/>
+      <c r="G38" s="180"/>
+      <c r="H38" s="188"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="189"/>
+      <c r="K38" s="189"/>
+      <c r="L38" s="189"/>
+      <c r="M38" s="190"/>
+      <c r="N38" s="181"/>
+      <c r="O38" s="182"/>
+      <c r="P38" s="183"/>
       <c r="Q38" s="57"/>
-      <c r="R38" s="167"/>
-      <c r="S38" s="167"/>
+      <c r="R38" s="184"/>
+      <c r="S38" s="184"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="57"/>
       <c r="B39" s="57"/>
-      <c r="C39" s="160"/>
-      <c r="D39" s="160"/>
-      <c r="E39" s="160"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="160"/>
-      <c r="H39" s="161"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="162"/>
-      <c r="K39" s="162"/>
-      <c r="L39" s="162"/>
-      <c r="M39" s="163"/>
-      <c r="N39" s="164"/>
-      <c r="O39" s="165"/>
-      <c r="P39" s="166"/>
+      <c r="C39" s="180"/>
+      <c r="D39" s="180"/>
+      <c r="E39" s="180"/>
+      <c r="F39" s="180"/>
+      <c r="G39" s="180"/>
+      <c r="H39" s="188"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="189"/>
+      <c r="K39" s="189"/>
+      <c r="L39" s="189"/>
+      <c r="M39" s="190"/>
+      <c r="N39" s="181"/>
+      <c r="O39" s="182"/>
+      <c r="P39" s="183"/>
       <c r="Q39" s="57"/>
-      <c r="R39" s="167"/>
-      <c r="S39" s="167"/>
+      <c r="R39" s="184"/>
+      <c r="S39" s="184"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="57"/>
       <c r="B40" s="57"/>
-      <c r="C40" s="160"/>
-      <c r="D40" s="160"/>
-      <c r="E40" s="160"/>
-      <c r="F40" s="160"/>
-      <c r="G40" s="160"/>
-      <c r="H40" s="161"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="162"/>
-      <c r="K40" s="162"/>
-      <c r="L40" s="162"/>
-      <c r="M40" s="163"/>
-      <c r="N40" s="164"/>
-      <c r="O40" s="165"/>
-      <c r="P40" s="166"/>
+      <c r="C40" s="180"/>
+      <c r="D40" s="180"/>
+      <c r="E40" s="180"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="180"/>
+      <c r="H40" s="188"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
+      <c r="L40" s="189"/>
+      <c r="M40" s="190"/>
+      <c r="N40" s="181"/>
+      <c r="O40" s="182"/>
+      <c r="P40" s="183"/>
       <c r="Q40" s="57"/>
-      <c r="R40" s="167"/>
-      <c r="S40" s="167"/>
+      <c r="R40" s="184"/>
+      <c r="S40" s="184"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="57"/>
       <c r="B41" s="57"/>
-      <c r="C41" s="160"/>
-      <c r="D41" s="160"/>
-      <c r="E41" s="160"/>
-      <c r="F41" s="160"/>
-      <c r="G41" s="160"/>
-      <c r="H41" s="161"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="163"/>
-      <c r="N41" s="164"/>
-      <c r="O41" s="165"/>
-      <c r="P41" s="166"/>
+      <c r="C41" s="180"/>
+      <c r="D41" s="180"/>
+      <c r="E41" s="180"/>
+      <c r="F41" s="180"/>
+      <c r="G41" s="180"/>
+      <c r="H41" s="188"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
+      <c r="L41" s="189"/>
+      <c r="M41" s="190"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="182"/>
+      <c r="P41" s="183"/>
       <c r="Q41" s="57"/>
-      <c r="R41" s="167"/>
-      <c r="S41" s="167"/>
+      <c r="R41" s="184"/>
+      <c r="S41" s="184"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="57"/>
       <c r="B42" s="57"/>
-      <c r="C42" s="160"/>
-      <c r="D42" s="160"/>
-      <c r="E42" s="160"/>
-      <c r="F42" s="160"/>
-      <c r="G42" s="160"/>
-      <c r="H42" s="161"/>
-      <c r="I42" s="162"/>
-      <c r="J42" s="162"/>
-      <c r="K42" s="162"/>
-      <c r="L42" s="162"/>
-      <c r="M42" s="163"/>
-      <c r="N42" s="164"/>
-      <c r="O42" s="165"/>
-      <c r="P42" s="166"/>
+      <c r="C42" s="180"/>
+      <c r="D42" s="180"/>
+      <c r="E42" s="180"/>
+      <c r="F42" s="180"/>
+      <c r="G42" s="180"/>
+      <c r="H42" s="188"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
+      <c r="L42" s="189"/>
+      <c r="M42" s="190"/>
+      <c r="N42" s="181"/>
+      <c r="O42" s="182"/>
+      <c r="P42" s="183"/>
       <c r="Q42" s="57"/>
-      <c r="R42" s="167"/>
-      <c r="S42" s="167"/>
+      <c r="R42" s="184"/>
+      <c r="S42" s="184"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="57"/>
       <c r="B43" s="57"/>
-      <c r="C43" s="160"/>
-      <c r="D43" s="160"/>
-      <c r="E43" s="160"/>
-      <c r="F43" s="160"/>
-      <c r="G43" s="160"/>
-      <c r="H43" s="161"/>
-      <c r="I43" s="162"/>
-      <c r="J43" s="162"/>
-      <c r="K43" s="162"/>
-      <c r="L43" s="162"/>
-      <c r="M43" s="163"/>
-      <c r="N43" s="164"/>
-      <c r="O43" s="165"/>
-      <c r="P43" s="166"/>
+      <c r="C43" s="180"/>
+      <c r="D43" s="180"/>
+      <c r="E43" s="180"/>
+      <c r="F43" s="180"/>
+      <c r="G43" s="180"/>
+      <c r="H43" s="188"/>
+      <c r="I43" s="189"/>
+      <c r="J43" s="189"/>
+      <c r="K43" s="189"/>
+      <c r="L43" s="189"/>
+      <c r="M43" s="190"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="182"/>
+      <c r="P43" s="183"/>
       <c r="Q43" s="57"/>
-      <c r="R43" s="167"/>
-      <c r="S43" s="167"/>
+      <c r="R43" s="184"/>
+      <c r="S43" s="184"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="57"/>
       <c r="B44" s="57"/>
-      <c r="C44" s="160"/>
-      <c r="D44" s="160"/>
-      <c r="E44" s="160"/>
-      <c r="F44" s="160"/>
-      <c r="G44" s="160"/>
-      <c r="H44" s="161"/>
-      <c r="I44" s="162"/>
-      <c r="J44" s="162"/>
-      <c r="K44" s="162"/>
-      <c r="L44" s="162"/>
-      <c r="M44" s="163"/>
-      <c r="N44" s="164"/>
-      <c r="O44" s="165"/>
-      <c r="P44" s="166"/>
+      <c r="C44" s="180"/>
+      <c r="D44" s="180"/>
+      <c r="E44" s="180"/>
+      <c r="F44" s="180"/>
+      <c r="G44" s="180"/>
+      <c r="H44" s="188"/>
+      <c r="I44" s="189"/>
+      <c r="J44" s="189"/>
+      <c r="K44" s="189"/>
+      <c r="L44" s="189"/>
+      <c r="M44" s="190"/>
+      <c r="N44" s="181"/>
+      <c r="O44" s="182"/>
+      <c r="P44" s="183"/>
       <c r="Q44" s="57"/>
-      <c r="R44" s="167"/>
-      <c r="S44" s="167"/>
+      <c r="R44" s="184"/>
+      <c r="S44" s="184"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="57"/>
       <c r="B45" s="57"/>
-      <c r="C45" s="160"/>
-      <c r="D45" s="160"/>
-      <c r="E45" s="160"/>
-      <c r="F45" s="160"/>
-      <c r="G45" s="160"/>
-      <c r="H45" s="161"/>
-      <c r="I45" s="162"/>
-      <c r="J45" s="162"/>
-      <c r="K45" s="162"/>
-      <c r="L45" s="162"/>
-      <c r="M45" s="163"/>
-      <c r="N45" s="164"/>
-      <c r="O45" s="165"/>
-      <c r="P45" s="166"/>
+      <c r="C45" s="180"/>
+      <c r="D45" s="180"/>
+      <c r="E45" s="180"/>
+      <c r="F45" s="180"/>
+      <c r="G45" s="180"/>
+      <c r="H45" s="188"/>
+      <c r="I45" s="189"/>
+      <c r="J45" s="189"/>
+      <c r="K45" s="189"/>
+      <c r="L45" s="189"/>
+      <c r="M45" s="190"/>
+      <c r="N45" s="181"/>
+      <c r="O45" s="182"/>
+      <c r="P45" s="183"/>
       <c r="Q45" s="57"/>
-      <c r="R45" s="167"/>
-      <c r="S45" s="167"/>
+      <c r="R45" s="184"/>
+      <c r="S45" s="184"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="57"/>
       <c r="B46" s="57"/>
-      <c r="C46" s="160"/>
-      <c r="D46" s="160"/>
-      <c r="E46" s="160"/>
-      <c r="F46" s="160"/>
-      <c r="G46" s="160"/>
-      <c r="H46" s="161"/>
-      <c r="I46" s="162"/>
-      <c r="J46" s="162"/>
-      <c r="K46" s="162"/>
-      <c r="L46" s="162"/>
-      <c r="M46" s="163"/>
-      <c r="N46" s="164"/>
-      <c r="O46" s="165"/>
-      <c r="P46" s="166"/>
+      <c r="C46" s="180"/>
+      <c r="D46" s="180"/>
+      <c r="E46" s="180"/>
+      <c r="F46" s="180"/>
+      <c r="G46" s="180"/>
+      <c r="H46" s="188"/>
+      <c r="I46" s="189"/>
+      <c r="J46" s="189"/>
+      <c r="K46" s="189"/>
+      <c r="L46" s="189"/>
+      <c r="M46" s="190"/>
+      <c r="N46" s="181"/>
+      <c r="O46" s="182"/>
+      <c r="P46" s="183"/>
       <c r="Q46" s="57"/>
-      <c r="R46" s="167"/>
-      <c r="S46" s="167"/>
+      <c r="R46" s="184"/>
+      <c r="S46" s="184"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="57"/>
       <c r="B47" s="57"/>
-      <c r="C47" s="160"/>
-      <c r="D47" s="160"/>
-      <c r="E47" s="160"/>
-      <c r="F47" s="160"/>
-      <c r="G47" s="160"/>
-      <c r="H47" s="161"/>
-      <c r="I47" s="162"/>
-      <c r="J47" s="162"/>
-      <c r="K47" s="162"/>
-      <c r="L47" s="162"/>
-      <c r="M47" s="163"/>
-      <c r="N47" s="164"/>
-      <c r="O47" s="165"/>
-      <c r="P47" s="166"/>
+      <c r="C47" s="180"/>
+      <c r="D47" s="180"/>
+      <c r="E47" s="180"/>
+      <c r="F47" s="180"/>
+      <c r="G47" s="180"/>
+      <c r="H47" s="188"/>
+      <c r="I47" s="189"/>
+      <c r="J47" s="189"/>
+      <c r="K47" s="189"/>
+      <c r="L47" s="189"/>
+      <c r="M47" s="190"/>
+      <c r="N47" s="181"/>
+      <c r="O47" s="182"/>
+      <c r="P47" s="183"/>
       <c r="Q47" s="57"/>
-      <c r="R47" s="167"/>
-      <c r="S47" s="167"/>
+      <c r="R47" s="184"/>
+      <c r="S47" s="184"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="57"/>
       <c r="B48" s="57"/>
-      <c r="C48" s="160"/>
-      <c r="D48" s="160"/>
-      <c r="E48" s="160"/>
-      <c r="F48" s="160"/>
-      <c r="G48" s="160"/>
-      <c r="H48" s="161"/>
-      <c r="I48" s="162"/>
-      <c r="J48" s="162"/>
-      <c r="K48" s="162"/>
-      <c r="L48" s="162"/>
-      <c r="M48" s="163"/>
-      <c r="N48" s="164"/>
-      <c r="O48" s="165"/>
-      <c r="P48" s="166"/>
+      <c r="C48" s="180"/>
+      <c r="D48" s="180"/>
+      <c r="E48" s="180"/>
+      <c r="F48" s="180"/>
+      <c r="G48" s="180"/>
+      <c r="H48" s="188"/>
+      <c r="I48" s="189"/>
+      <c r="J48" s="189"/>
+      <c r="K48" s="189"/>
+      <c r="L48" s="189"/>
+      <c r="M48" s="190"/>
+      <c r="N48" s="181"/>
+      <c r="O48" s="182"/>
+      <c r="P48" s="183"/>
       <c r="Q48" s="57"/>
-      <c r="R48" s="167"/>
-      <c r="S48" s="167"/>
+      <c r="R48" s="184"/>
+      <c r="S48" s="184"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="57"/>
       <c r="B49" s="57"/>
-      <c r="C49" s="160"/>
-      <c r="D49" s="160"/>
-      <c r="E49" s="160"/>
-      <c r="F49" s="160"/>
-      <c r="G49" s="160"/>
-      <c r="H49" s="161"/>
-      <c r="I49" s="162"/>
-      <c r="J49" s="162"/>
-      <c r="K49" s="162"/>
-      <c r="L49" s="162"/>
-      <c r="M49" s="163"/>
-      <c r="N49" s="164"/>
-      <c r="O49" s="165"/>
-      <c r="P49" s="166"/>
+      <c r="C49" s="180"/>
+      <c r="D49" s="180"/>
+      <c r="E49" s="180"/>
+      <c r="F49" s="180"/>
+      <c r="G49" s="180"/>
+      <c r="H49" s="188"/>
+      <c r="I49" s="189"/>
+      <c r="J49" s="189"/>
+      <c r="K49" s="189"/>
+      <c r="L49" s="189"/>
+      <c r="M49" s="190"/>
+      <c r="N49" s="181"/>
+      <c r="O49" s="182"/>
+      <c r="P49" s="183"/>
       <c r="Q49" s="57"/>
-      <c r="R49" s="167"/>
-      <c r="S49" s="167"/>
+      <c r="R49" s="184"/>
+      <c r="S49" s="184"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="57"/>
       <c r="B50" s="57"/>
-      <c r="C50" s="160"/>
-      <c r="D50" s="160"/>
-      <c r="E50" s="160"/>
-      <c r="F50" s="160"/>
-      <c r="G50" s="160"/>
-      <c r="H50" s="161"/>
-      <c r="I50" s="162"/>
-      <c r="J50" s="162"/>
-      <c r="K50" s="162"/>
-      <c r="L50" s="162"/>
-      <c r="M50" s="163"/>
-      <c r="N50" s="164"/>
-      <c r="O50" s="165"/>
-      <c r="P50" s="166"/>
+      <c r="C50" s="180"/>
+      <c r="D50" s="180"/>
+      <c r="E50" s="180"/>
+      <c r="F50" s="180"/>
+      <c r="G50" s="180"/>
+      <c r="H50" s="188"/>
+      <c r="I50" s="189"/>
+      <c r="J50" s="189"/>
+      <c r="K50" s="189"/>
+      <c r="L50" s="189"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="181"/>
+      <c r="O50" s="182"/>
+      <c r="P50" s="183"/>
       <c r="Q50" s="57"/>
-      <c r="R50" s="167"/>
-      <c r="S50" s="167"/>
+      <c r="R50" s="184"/>
+      <c r="S50" s="184"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="57"/>
       <c r="B51" s="57"/>
-      <c r="C51" s="160"/>
-      <c r="D51" s="160"/>
-      <c r="E51" s="160"/>
-      <c r="F51" s="160"/>
-      <c r="G51" s="160"/>
-      <c r="H51" s="161"/>
-      <c r="I51" s="162"/>
-      <c r="J51" s="162"/>
-      <c r="K51" s="162"/>
-      <c r="L51" s="162"/>
-      <c r="M51" s="163"/>
-      <c r="N51" s="164"/>
-      <c r="O51" s="165"/>
-      <c r="P51" s="166"/>
+      <c r="C51" s="180"/>
+      <c r="D51" s="180"/>
+      <c r="E51" s="180"/>
+      <c r="F51" s="180"/>
+      <c r="G51" s="180"/>
+      <c r="H51" s="188"/>
+      <c r="I51" s="189"/>
+      <c r="J51" s="189"/>
+      <c r="K51" s="189"/>
+      <c r="L51" s="189"/>
+      <c r="M51" s="190"/>
+      <c r="N51" s="181"/>
+      <c r="O51" s="182"/>
+      <c r="P51" s="183"/>
       <c r="Q51" s="57"/>
-      <c r="R51" s="167"/>
-      <c r="S51" s="167"/>
+      <c r="R51" s="184"/>
+      <c r="S51" s="184"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="57"/>
       <c r="B52" s="57"/>
-      <c r="C52" s="160"/>
-      <c r="D52" s="160"/>
-      <c r="E52" s="160"/>
-      <c r="F52" s="160"/>
-      <c r="G52" s="160"/>
-      <c r="H52" s="161"/>
-      <c r="I52" s="162"/>
-      <c r="J52" s="162"/>
-      <c r="K52" s="162"/>
-      <c r="L52" s="162"/>
-      <c r="M52" s="163"/>
-      <c r="N52" s="164"/>
-      <c r="O52" s="165"/>
-      <c r="P52" s="166"/>
+      <c r="C52" s="180"/>
+      <c r="D52" s="180"/>
+      <c r="E52" s="180"/>
+      <c r="F52" s="180"/>
+      <c r="G52" s="180"/>
+      <c r="H52" s="188"/>
+      <c r="I52" s="189"/>
+      <c r="J52" s="189"/>
+      <c r="K52" s="189"/>
+      <c r="L52" s="189"/>
+      <c r="M52" s="190"/>
+      <c r="N52" s="181"/>
+      <c r="O52" s="182"/>
+      <c r="P52" s="183"/>
       <c r="Q52" s="57"/>
-      <c r="R52" s="167"/>
-      <c r="S52" s="167"/>
+      <c r="R52" s="184"/>
+      <c r="S52" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -13005,194 +13193,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/タスク編集設計書.xlsx
+++ b/Documents/タスク編集設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-24\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09BD721-694D-47F9-B2DF-666067DA8F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6902E74-FD13-44C6-AA82-95324A94C380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -19,18 +19,14 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
-    <sheet name="JUnitテスト仕様書兼報告書" sheetId="9" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="範囲１" localSheetId="6">#REF!</definedName>
-    <definedName name="範囲１">#REF!</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -194,12 +190,6 @@
   <si>
     <t xml:space="preserve">正常系
 </t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>異常系</t>
   </si>
   <si>
     <t>taskUN</t>
@@ -450,7 +440,7 @@
 ②変更したいカラムに対応したフォームを入力し"確認"ボタンを押下
 ③①に記載されたカラムの変更後のデータが表示され"実行"ボタン、"戻る"ボタンが表示される。
 ④❶"実行"ボタンを押下した場合、データベース上のレコードに編集がかけられ、編集完了画面に遷移する。
-　❷"戻る"ボタンを押下した場合、フォームに遷移する。</t>
+　❷"戻る"ボタンを押下した場合、編集画面に遷移する。</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
     </rPh>
@@ -541,165 +531,235 @@
     <rPh sb="252" eb="254">
       <t>バアイ</t>
     </rPh>
+    <rPh sb="255" eb="259">
+      <t>ヘンシュウガメン</t>
+    </rPh>
     <rPh sb="260" eb="262">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>JUnitテスト仕様書兼報告書</t>
-    <rPh sb="8" eb="11">
-      <t>シヨウショ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ホウコクショ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>システム名</t>
-    <rPh sb="4" eb="5">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>作成者</t>
-  </si>
-  <si>
-    <t>会社名</t>
-    <rPh sb="0" eb="3">
-      <t>カイシャメイ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>コンサイズ</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>サブシステム名</t>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>作成日</t>
-    <rPh sb="0" eb="3">
-      <t>サクセイビ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>実施者</t>
+    <t>詳細ページから編集ページへページ遷移</t>
     <rPh sb="0" eb="2">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>No</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>分類</t>
-    <rPh sb="0" eb="2">
-      <t>ブンルイ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>テストクラス</t>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>検証するメソッド</t>
-    <rPh sb="0" eb="2">
-      <t>ケンショウ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>期待する結果</t>
-    <rPh sb="0" eb="2">
-      <t>キタイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>実施日</t>
-    <rPh sb="0" eb="3">
-      <t>ジッシビ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>備考・特記事項</t>
-    <rPh sb="0" eb="2">
-      <t>ビコウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トッキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジコウ</t>
-    </rPh>
-    <phoneticPr fontId="12"/>
-  </si>
-  <si>
-    <t>タスク詳細画面からタスク編集画面へページ遷移</t>
-    <rPh sb="3" eb="5">
       <t>ショウサイ</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
+    <rPh sb="7" eb="9">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="14" eb="16">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="16" eb="18">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集ボタンを押下する</t>
-    <rPh sb="0" eb="2">
+    <t>詳細画面のレコードのユーザーIDとログインしているユーザーIDが一致していること</t>
+    <rPh sb="0" eb="4">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>イッチ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>詳細画面の編集ボタンを押下</t>
+    <rPh sb="0" eb="4">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh sb="11" eb="13">
       <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク編集画面が表示される</t>
-    <rPh sb="3" eb="7">
-      <t>ヘンシュウガメン</t>
+    <t>タスク編集画面に遷移する。</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
     </rPh>
     <rPh sb="8" eb="10">
-      <t>ヒョウジ</t>
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>山形</t>
-    <rPh sb="0" eb="2">
-      <t>ヤマガタ</t>
+    <t>◎</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系
+</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名,カテゴリ名,期限,ステータス,メモを入力し、確認画面で入力したデータが出力される。</t>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
     </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名:テスト
+カテゴリ名:1
+期限:6/20
+ステータス:50
+メモ:テスト</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集画面の確認ボタンを押下</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集確認画面に遷移する。</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>確認画面にて登録ボタンを押下し、編集登録成功画面へ遷移する。</t>
+    <rPh sb="0" eb="4">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ヘンシュウトウロク</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>セイコウガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2のテストにてタスク確認画面が表示されている。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>確認画面の登録ボタンを押下</t>
+    <rPh sb="0" eb="4">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集成功画面に遷移する。</t>
+    <rPh sb="3" eb="9">
+      <t>ヘンシュウセイコウガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名,期限,メモを空欄状態にして確認画面に遷移し、変更前のデータが入ることを確認する。</t>
+    <rPh sb="11" eb="15">
+      <t>クウランジョウタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ヘンコウマエ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名:空欄
+カテゴリ名:2
+期限:空欄
+ステータス:99
+メモ:空欄</t>
+    <rPh sb="5" eb="7">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名:テスト
+カテゴリ名:既存商品B～
+期限:6/20
+ステータス:完了
+メモ:テスト</t>
+    <rPh sb="15" eb="19">
+      <t>キゾンショウヒン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面遷移図</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -710,7 +770,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -781,45 +841,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <sz val="10"/>
+      <name val="MS PGothic"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -832,14 +868,8 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="71">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1499,192 +1529,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1829,42 +1680,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="62" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="67" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2165,105 +1980,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{6C10B5B7-E36B-40F5-9E99-A4A9558B5B5A}"/>
-    <cellStyle name="標準_生産計画ED書" xfId="2" xr:uid="{B379AC83-C2C5-4CC3-93BC-2F95CC4D6933}"/>
-    <cellStyle name="標準_東京理科大DBレイアウト" xfId="3" xr:uid="{F2C8EDF1-C230-4C71-B560-56D5DE10D912}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2282,23 +2015,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>149925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8F6EE0E-7F6F-405F-FBF7-DFB48C7A6F6E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3524B28-42EB-4DB5-9EEB-4C43AB95C204}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2320,8 +2053,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="581025" y="1009650"/>
-          <a:ext cx="7772400" cy="4295775"/>
+          <a:off x="247650" y="1028700"/>
+          <a:ext cx="8267700" cy="4569525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2337,23 +2070,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>152399</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>979372</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1780B02E-2916-9863-16CA-A1BAC86FBBB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E50DE7E-6A27-61A4-EA4A-43806E766AEA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2375,8 +2108,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="152399" y="1390650"/>
-          <a:ext cx="8542223" cy="3314700"/>
+          <a:off x="381000" y="923925"/>
+          <a:ext cx="7772400" cy="4648200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3162,85 +2895,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3260,46 +2993,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
+      <c r="E8" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="60" t="s">
+      <c r="H13" s="50"/>
+      <c r="I13" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="60"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="50"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="60"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3308,13 +3041,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="63" t="s">
+      <c r="G17" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4329,19 +4062,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="76"/>
+      <c r="G1" s="64"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4353,190 +4086,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="94" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
+        <v>45806</v>
+      </c>
+      <c r="I2" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="J2" s="59"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="60"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="61"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
-        <v>45806</v>
-      </c>
-      <c r="I2" s="68" t="s">
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="66"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="71"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="73"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="77" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="71"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="79" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="82" t="s">
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="71"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="83"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="79" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="82" t="s">
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="71"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="69"/>
+      <c r="D9" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="71"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="93"/>
+      <c r="B10" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="69"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="71"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="69"/>
+      <c r="D11" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="83"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="82" t="s">
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="71"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="83"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="104" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="107" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="108" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="83"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="83"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="107" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="108" t="s">
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="83"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="79" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="83"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="71"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="99" t="s">
+      <c r="A13" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="103"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="91"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5573,19 +5306,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="76"/>
+      <c r="G1" s="64"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -5597,48 +5330,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>45806</v>
       </c>
-      <c r="I2" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="J2" s="71"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="73"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -6995,19 +6726,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="125" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="126"/>
-      <c r="F1" s="125" t="s">
+      <c r="E1" s="114"/>
+      <c r="F1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="126"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7019,48 +6750,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="120"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="127" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="128"/>
-      <c r="F2" s="127" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="110">
+      <c r="A2" s="108"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="115" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="116"/>
+      <c r="F2" s="115" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="116"/>
+      <c r="H2" s="98">
         <v>45810</v>
       </c>
-      <c r="I2" s="113" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="114"/>
+      <c r="I2" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="115"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="122"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="116"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -8411,19 +8142,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="125" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="126"/>
-      <c r="F1" s="125" t="s">
+      <c r="E1" s="114"/>
+      <c r="F1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="126"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -8435,203 +8166,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="120"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="127" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="115" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="116"/>
+      <c r="F2" s="115">
         <v>56</v>
       </c>
-      <c r="E2" s="128"/>
-      <c r="F2" s="127">
-        <v>56</v>
-      </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="110">
+      <c r="G2" s="116"/>
+      <c r="H2" s="98">
         <v>45810</v>
       </c>
-      <c r="I2" s="113" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="114"/>
+      <c r="I2" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="115"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="120"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="115"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="103"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="137" t="s">
+      <c r="B5" s="123"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="125" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="126"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="124" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="120"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="127"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="129"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="108"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="130"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="108"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="130"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="108"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="130"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="108"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="130"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="108"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="130"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="108"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="130"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="124" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="120"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="138"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="136" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="132"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="139"/>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="141"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="142"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="142"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="142"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="142"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="120"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="142"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="120"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="142"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="136" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="132"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="136" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="131" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="136" t="s">
+      <c r="A16" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -8644,165 +8375,165 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="143" t="s">
+      <c r="H16" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="132"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="133">
+      <c r="A17" s="121">
         <v>1</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="62"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="119"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="120"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="121">
+        <v>2</v>
+      </c>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="119"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="120"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="121">
+        <v>3</v>
+      </c>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="119"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="120"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="121">
+        <v>4</v>
+      </c>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="119"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="120"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="121">
+        <v>5</v>
+      </c>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="119"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="120"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="121">
+        <v>6</v>
+      </c>
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="131"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="132"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="133">
-        <v>2</v>
-      </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="131"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="132"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="133">
-        <v>3</v>
-      </c>
-      <c r="B19" s="61"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="131"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="132"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="133">
-        <v>4</v>
-      </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="16" t="s">
+      <c r="E22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="131"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="132"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="133">
-        <v>5</v>
-      </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="16" t="s">
+      <c r="F22" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="119"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="120"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="121">
+        <v>7</v>
+      </c>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" s="131"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="132"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="133">
-        <v>6</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="16" t="s">
+      <c r="F23" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="131"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="132"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="133">
-        <v>7</v>
-      </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="144"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="146"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9833,186 +9564,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="125" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="125" t="s">
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="125" t="s">
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="125" t="s">
+      <c r="P1" s="114"/>
+      <c r="Q1" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="126"/>
-      <c r="S1" s="125" t="s">
+      <c r="R1" s="114"/>
+      <c r="S1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="138"/>
+      <c r="T1" s="126"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="120"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="127" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="115" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="115" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="151">
+        <v>45821</v>
+      </c>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="127" t="s">
+      <c r="R2" s="116"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="129"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="108"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="130"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="145"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="142" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="126"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="120"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="124" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="128"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="141"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="129"/>
-      <c r="R3" s="121"/>
-      <c r="S3" s="129"/>
-      <c r="T3" s="142"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="122"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="123"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="130"/>
-      <c r="T4" s="157"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="134" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="154" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
-      <c r="O5" s="135"/>
-      <c r="P5" s="135"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="135"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="138"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="136" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="131" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="132"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="136" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="131" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="61"/>
-      <c r="T7" s="132"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="120"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -10211,37 +9946,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="136" t="s">
+      <c r="A15" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="156" t="s">
+      <c r="B15" s="50"/>
+      <c r="C15" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="143" t="s">
+      <c r="D15" s="50"/>
+      <c r="E15" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="143" t="s">
+      <c r="F15" s="50"/>
+      <c r="G15" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="143" t="s">
+      <c r="H15" s="49"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="143" t="s">
+      <c r="K15" s="50"/>
+      <c r="L15" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="143" t="s">
+      <c r="M15" s="49"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="131" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="50"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -10252,36 +9987,38 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="56.25" customHeight="1">
-      <c r="A16" s="147">
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="135">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="148" t="s">
+      <c r="B16" s="50"/>
+      <c r="C16" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="148" t="s">
+      <c r="D16" s="50"/>
+      <c r="E16" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="155" t="s">
-        <v>107</v>
-      </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="155"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="152" t="s">
-        <v>108</v>
-      </c>
-      <c r="M16" s="61"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="152" t="s">
-        <v>109</v>
-      </c>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="143" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="49"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="143" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="50"/>
+      <c r="L16" s="150" t="s">
+        <v>92</v>
+      </c>
+      <c r="M16" s="148"/>
+      <c r="N16" s="149"/>
+      <c r="O16" s="140" t="s">
+        <v>93</v>
+      </c>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="50"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -10292,30 +10029,38 @@
       <c r="Y16" s="34"/>
       <c r="Z16" s="34"/>
     </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="147">
+    <row r="17" spans="1:26" ht="62.25" customHeight="1">
+      <c r="A17" s="135">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="148" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="148" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="155"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="152"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="152"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="136" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="50"/>
+      <c r="E17" s="136" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="50"/>
+      <c r="G17" s="143" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="49"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="143" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" s="50"/>
+      <c r="L17" s="140" t="s">
+        <v>98</v>
+      </c>
+      <c r="M17" s="49"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="140" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="50"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -10326,24 +10071,38 @@
       <c r="Y17" s="34"/>
       <c r="Z17" s="34"/>
     </row>
-    <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="147"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="155"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="152"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="152"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="62"/>
+    <row r="18" spans="1:26" ht="54" customHeight="1">
+      <c r="A18" s="135">
+        <v>3</v>
+      </c>
+      <c r="B18" s="50"/>
+      <c r="C18" s="136" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="50"/>
+      <c r="E18" s="136" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="50"/>
+      <c r="G18" s="143" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="49"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="143" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="50"/>
+      <c r="L18" s="140" t="s">
+        <v>102</v>
+      </c>
+      <c r="M18" s="49"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="140" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="50"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -10354,24 +10113,38 @@
       <c r="Y18" s="34"/>
       <c r="Z18" s="34"/>
     </row>
-    <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="147"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="148"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="148"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="152"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="152"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="62"/>
+    <row r="19" spans="1:26" ht="69.75" customHeight="1">
+      <c r="A19" s="135">
+        <v>4</v>
+      </c>
+      <c r="B19" s="50"/>
+      <c r="C19" s="136" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="50"/>
+      <c r="E19" s="136" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="50"/>
+      <c r="G19" s="143" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="49"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="143" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="50"/>
+      <c r="L19" s="140" t="s">
+        <v>102</v>
+      </c>
+      <c r="M19" s="49"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="140" t="s">
+        <v>106</v>
+      </c>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="50"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -10382,24 +10155,24 @@
       <c r="Y19" s="34"/>
       <c r="Z19" s="34"/>
     </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="147"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="148"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="155"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="152"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="152"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="62"/>
+    <row r="20" spans="1:26" ht="57" customHeight="1">
+      <c r="A20" s="135"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="140"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="50"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -10411,23 +10184,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="147"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="155"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="152"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="152"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="62"/>
+      <c r="A21" s="135"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="140"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="50"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -10439,23 +10212,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="147"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="148"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="152"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="152"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="62"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="50"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -10467,23 +10240,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="147"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="155"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="155"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="152"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="152"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
+      <c r="A23" s="135"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="136"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="140"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="50"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -10495,23 +10268,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="147"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="155"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="152"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="152"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="62"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="140"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="50"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -10523,23 +10296,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="147"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="155"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="152"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="152"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="62"/>
+      <c r="A25" s="135"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="140"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="50"/>
+      <c r="O25" s="140"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="50"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -10551,23 +10324,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="147"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="155"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="155"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="152"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="152"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="62"/>
+      <c r="A26" s="135"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="140"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="50"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -10579,23 +10352,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="147"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="155"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="152"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="62"/>
+      <c r="A27" s="135"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="140"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="50"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -10607,23 +10380,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="147"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="148"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="152"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="152"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="62"/>
+      <c r="A28" s="135"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="143"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="50"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -10635,23 +10408,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="147"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="148"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="152"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="152"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="62"/>
+      <c r="A29" s="135"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="143"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="140"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="50"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -10663,23 +10436,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="147"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="148"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="155"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="152"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="152"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="62"/>
+      <c r="A30" s="135"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="140"/>
+      <c r="M30" s="49"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="140"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="50"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -10691,23 +10464,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="149"/>
-      <c r="B31" s="150"/>
-      <c r="C31" s="151"/>
-      <c r="D31" s="150"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="150"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="150"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="150"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="145"/>
-      <c r="N31" s="150"/>
-      <c r="O31" s="153"/>
-      <c r="P31" s="145"/>
-      <c r="Q31" s="150"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="133"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="147"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="133"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="141"/>
+      <c r="P31" s="133"/>
+      <c r="Q31" s="138"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -11846,1357 +11619,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{813620BE-5D85-43CD-A82F-469E5B53D58D}">
-  <dimension ref="A1:S52"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" style="49" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="59" customWidth="1"/>
-    <col min="3" max="6" width="8.140625" style="49" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="59" customWidth="1"/>
-    <col min="8" max="13" width="8.140625" style="49" customWidth="1"/>
-    <col min="14" max="19" width="12.140625" style="49" customWidth="1"/>
-    <col min="20" max="16384" width="8" style="49"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="169" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="170" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="171"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="175"/>
-      <c r="N1" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="O1" s="173"/>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" s="173" t="s">
-        <v>96</v>
-      </c>
-      <c r="S1" s="175"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="169"/>
-      <c r="B2" s="169"/>
-      <c r="C2" s="170" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
-      <c r="L2" s="174"/>
-      <c r="M2" s="175"/>
-      <c r="N2" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="O2" s="176"/>
-      <c r="P2" s="177"/>
-      <c r="Q2" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="R2" s="178">
-        <v>44771</v>
-      </c>
-      <c r="S2" s="179"/>
-    </row>
-    <row r="3" spans="1:19" ht="11.25" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-    </row>
-    <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="160" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="160" t="s">
-        <v>103</v>
-      </c>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="O4" s="161"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="R4" s="160" t="s">
-        <v>106</v>
-      </c>
-      <c r="S4" s="162"/>
-    </row>
-    <row r="5" spans="1:19" ht="30" customHeight="1">
-      <c r="A5" s="55"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="163"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="163"/>
-      <c r="G5" s="163"/>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
-      <c r="J5" s="163"/>
-      <c r="K5" s="163"/>
-      <c r="L5" s="163"/>
-      <c r="M5" s="163"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="165"/>
-      <c r="P5" s="166"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="167"/>
-      <c r="S5" s="168"/>
-    </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="180"/>
-      <c r="D6" s="180"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="180"/>
-      <c r="G6" s="180"/>
-      <c r="H6" s="180"/>
-      <c r="I6" s="180"/>
-      <c r="J6" s="180"/>
-      <c r="K6" s="180"/>
-      <c r="L6" s="180"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="185"/>
-      <c r="O6" s="186"/>
-      <c r="P6" s="187"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="184"/>
-      <c r="S6" s="184"/>
-    </row>
-    <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="180"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
-      <c r="G7" s="180"/>
-      <c r="H7" s="180"/>
-      <c r="I7" s="180"/>
-      <c r="J7" s="180"/>
-      <c r="K7" s="180"/>
-      <c r="L7" s="180"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="182"/>
-      <c r="P7" s="183"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="184"/>
-      <c r="S7" s="184"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
-      <c r="H8" s="180"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="180"/>
-      <c r="M8" s="180"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="182"/>
-      <c r="P8" s="183"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="184"/>
-      <c r="S8" s="184"/>
-    </row>
-    <row r="9" spans="1:19" ht="30" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="180"/>
-      <c r="D9" s="180"/>
-      <c r="E9" s="180"/>
-      <c r="F9" s="180"/>
-      <c r="G9" s="180"/>
-      <c r="H9" s="180"/>
-      <c r="I9" s="180"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="180"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="181"/>
-      <c r="O9" s="182"/>
-      <c r="P9" s="183"/>
-      <c r="Q9" s="57"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-    </row>
-    <row r="10" spans="1:19" ht="30" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="180"/>
-      <c r="D10" s="180"/>
-      <c r="E10" s="180"/>
-      <c r="F10" s="180"/>
-      <c r="G10" s="180"/>
-      <c r="H10" s="188"/>
-      <c r="I10" s="189"/>
-      <c r="J10" s="189"/>
-      <c r="K10" s="189"/>
-      <c r="L10" s="189"/>
-      <c r="M10" s="190"/>
-      <c r="N10" s="181"/>
-      <c r="O10" s="182"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="184"/>
-      <c r="S10" s="184"/>
-    </row>
-    <row r="11" spans="1:19" ht="30" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="180"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="180"/>
-      <c r="G11" s="180"/>
-      <c r="H11" s="188"/>
-      <c r="I11" s="189"/>
-      <c r="J11" s="189"/>
-      <c r="K11" s="189"/>
-      <c r="L11" s="189"/>
-      <c r="M11" s="190"/>
-      <c r="N11" s="181"/>
-      <c r="O11" s="182"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="57"/>
-      <c r="R11" s="184"/>
-      <c r="S11" s="184"/>
-    </row>
-    <row r="12" spans="1:19" ht="30" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="180"/>
-      <c r="D12" s="180"/>
-      <c r="E12" s="180"/>
-      <c r="F12" s="180"/>
-      <c r="G12" s="180"/>
-      <c r="H12" s="188"/>
-      <c r="I12" s="189"/>
-      <c r="J12" s="189"/>
-      <c r="K12" s="189"/>
-      <c r="L12" s="189"/>
-      <c r="M12" s="190"/>
-      <c r="N12" s="181"/>
-      <c r="O12" s="182"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="57"/>
-      <c r="R12" s="184"/>
-      <c r="S12" s="184"/>
-    </row>
-    <row r="13" spans="1:19" ht="30" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="180"/>
-      <c r="D13" s="180"/>
-      <c r="E13" s="180"/>
-      <c r="F13" s="180"/>
-      <c r="G13" s="180"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="189"/>
-      <c r="J13" s="189"/>
-      <c r="K13" s="189"/>
-      <c r="L13" s="189"/>
-      <c r="M13" s="190"/>
-      <c r="N13" s="181"/>
-      <c r="O13" s="182"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="57"/>
-      <c r="R13" s="184"/>
-      <c r="S13" s="184"/>
-    </row>
-    <row r="14" spans="1:19" ht="30" customHeight="1">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="180"/>
-      <c r="E14" s="180"/>
-      <c r="F14" s="180"/>
-      <c r="G14" s="180"/>
-      <c r="H14" s="188"/>
-      <c r="I14" s="189"/>
-      <c r="J14" s="189"/>
-      <c r="K14" s="189"/>
-      <c r="L14" s="189"/>
-      <c r="M14" s="190"/>
-      <c r="N14" s="181"/>
-      <c r="O14" s="182"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="184"/>
-      <c r="S14" s="184"/>
-    </row>
-    <row r="15" spans="1:19" ht="30" customHeight="1">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="180"/>
-      <c r="E15" s="180"/>
-      <c r="F15" s="180"/>
-      <c r="G15" s="180"/>
-      <c r="H15" s="188"/>
-      <c r="I15" s="189"/>
-      <c r="J15" s="189"/>
-      <c r="K15" s="189"/>
-      <c r="L15" s="189"/>
-      <c r="M15" s="190"/>
-      <c r="N15" s="181"/>
-      <c r="O15" s="182"/>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="57"/>
-      <c r="R15" s="184"/>
-      <c r="S15" s="184"/>
-    </row>
-    <row r="16" spans="1:19" ht="30" customHeight="1">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="180"/>
-      <c r="D16" s="180"/>
-      <c r="E16" s="180"/>
-      <c r="F16" s="180"/>
-      <c r="G16" s="180"/>
-      <c r="H16" s="188"/>
-      <c r="I16" s="189"/>
-      <c r="J16" s="189"/>
-      <c r="K16" s="189"/>
-      <c r="L16" s="189"/>
-      <c r="M16" s="190"/>
-      <c r="N16" s="181"/>
-      <c r="O16" s="182"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="184"/>
-      <c r="S16" s="184"/>
-    </row>
-    <row r="17" spans="1:19" ht="30" customHeight="1">
-      <c r="A17" s="57"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="180"/>
-      <c r="D17" s="180"/>
-      <c r="E17" s="180"/>
-      <c r="F17" s="180"/>
-      <c r="G17" s="180"/>
-      <c r="H17" s="188"/>
-      <c r="I17" s="189"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="189"/>
-      <c r="L17" s="189"/>
-      <c r="M17" s="190"/>
-      <c r="N17" s="181"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="57"/>
-      <c r="R17" s="184"/>
-      <c r="S17" s="184"/>
-    </row>
-    <row r="18" spans="1:19" ht="30" customHeight="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="180"/>
-      <c r="D18" s="180"/>
-      <c r="E18" s="180"/>
-      <c r="F18" s="180"/>
-      <c r="G18" s="180"/>
-      <c r="H18" s="188"/>
-      <c r="I18" s="189"/>
-      <c r="J18" s="189"/>
-      <c r="K18" s="189"/>
-      <c r="L18" s="189"/>
-      <c r="M18" s="190"/>
-      <c r="N18" s="181"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="184"/>
-      <c r="S18" s="184"/>
-    </row>
-    <row r="19" spans="1:19" ht="30" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="180"/>
-      <c r="D19" s="180"/>
-      <c r="E19" s="180"/>
-      <c r="F19" s="180"/>
-      <c r="G19" s="180"/>
-      <c r="H19" s="188"/>
-      <c r="I19" s="189"/>
-      <c r="J19" s="189"/>
-      <c r="K19" s="189"/>
-      <c r="L19" s="189"/>
-      <c r="M19" s="190"/>
-      <c r="N19" s="181"/>
-      <c r="O19" s="182"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="184"/>
-      <c r="S19" s="184"/>
-    </row>
-    <row r="20" spans="1:19" ht="30" customHeight="1">
-      <c r="A20" s="57"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="180"/>
-      <c r="D20" s="180"/>
-      <c r="E20" s="180"/>
-      <c r="F20" s="180"/>
-      <c r="G20" s="180"/>
-      <c r="H20" s="188"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="189"/>
-      <c r="L20" s="189"/>
-      <c r="M20" s="190"/>
-      <c r="N20" s="181"/>
-      <c r="O20" s="182"/>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="184"/>
-      <c r="S20" s="184"/>
-    </row>
-    <row r="21" spans="1:19" ht="30" customHeight="1">
-      <c r="A21" s="57"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="180"/>
-      <c r="D21" s="180"/>
-      <c r="E21" s="180"/>
-      <c r="F21" s="180"/>
-      <c r="G21" s="180"/>
-      <c r="H21" s="188"/>
-      <c r="I21" s="189"/>
-      <c r="J21" s="189"/>
-      <c r="K21" s="189"/>
-      <c r="L21" s="189"/>
-      <c r="M21" s="190"/>
-      <c r="N21" s="181"/>
-      <c r="O21" s="182"/>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="184"/>
-      <c r="S21" s="184"/>
-    </row>
-    <row r="22" spans="1:19" ht="30" customHeight="1">
-      <c r="A22" s="57"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="180"/>
-      <c r="D22" s="180"/>
-      <c r="E22" s="180"/>
-      <c r="F22" s="180"/>
-      <c r="G22" s="180"/>
-      <c r="H22" s="188"/>
-      <c r="I22" s="189"/>
-      <c r="J22" s="189"/>
-      <c r="K22" s="189"/>
-      <c r="L22" s="189"/>
-      <c r="M22" s="190"/>
-      <c r="N22" s="181"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="57"/>
-      <c r="R22" s="184"/>
-      <c r="S22" s="184"/>
-    </row>
-    <row r="23" spans="1:19" ht="30" customHeight="1">
-      <c r="A23" s="57"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="180"/>
-      <c r="D23" s="180"/>
-      <c r="E23" s="180"/>
-      <c r="F23" s="180"/>
-      <c r="G23" s="180"/>
-      <c r="H23" s="188"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="189"/>
-      <c r="K23" s="189"/>
-      <c r="L23" s="189"/>
-      <c r="M23" s="190"/>
-      <c r="N23" s="181"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="57"/>
-      <c r="R23" s="184"/>
-      <c r="S23" s="184"/>
-    </row>
-    <row r="24" spans="1:19" ht="30" customHeight="1">
-      <c r="A24" s="57"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="180"/>
-      <c r="D24" s="180"/>
-      <c r="E24" s="180"/>
-      <c r="F24" s="180"/>
-      <c r="G24" s="180"/>
-      <c r="H24" s="188"/>
-      <c r="I24" s="189"/>
-      <c r="J24" s="189"/>
-      <c r="K24" s="189"/>
-      <c r="L24" s="189"/>
-      <c r="M24" s="190"/>
-      <c r="N24" s="181"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="57"/>
-      <c r="R24" s="184"/>
-      <c r="S24" s="184"/>
-    </row>
-    <row r="25" spans="1:19" ht="30" customHeight="1">
-      <c r="A25" s="57"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="180"/>
-      <c r="D25" s="180"/>
-      <c r="E25" s="180"/>
-      <c r="F25" s="180"/>
-      <c r="G25" s="180"/>
-      <c r="H25" s="188"/>
-      <c r="I25" s="189"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="189"/>
-      <c r="L25" s="189"/>
-      <c r="M25" s="190"/>
-      <c r="N25" s="181"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="184"/>
-      <c r="S25" s="184"/>
-    </row>
-    <row r="26" spans="1:19" ht="30" customHeight="1">
-      <c r="A26" s="57"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="180"/>
-      <c r="D26" s="180"/>
-      <c r="E26" s="180"/>
-      <c r="F26" s="180"/>
-      <c r="G26" s="180"/>
-      <c r="H26" s="188"/>
-      <c r="I26" s="189"/>
-      <c r="J26" s="189"/>
-      <c r="K26" s="189"/>
-      <c r="L26" s="189"/>
-      <c r="M26" s="190"/>
-      <c r="N26" s="181"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="184"/>
-      <c r="S26" s="184"/>
-    </row>
-    <row r="27" spans="1:19" ht="30" customHeight="1">
-      <c r="A27" s="57"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="180"/>
-      <c r="D27" s="180"/>
-      <c r="E27" s="180"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="180"/>
-      <c r="H27" s="188"/>
-      <c r="I27" s="189"/>
-      <c r="J27" s="189"/>
-      <c r="K27" s="189"/>
-      <c r="L27" s="189"/>
-      <c r="M27" s="190"/>
-      <c r="N27" s="181"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="57"/>
-      <c r="R27" s="184"/>
-      <c r="S27" s="184"/>
-    </row>
-    <row r="28" spans="1:19" ht="30" customHeight="1">
-      <c r="A28" s="57"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="180"/>
-      <c r="D28" s="180"/>
-      <c r="E28" s="180"/>
-      <c r="F28" s="180"/>
-      <c r="G28" s="180"/>
-      <c r="H28" s="188"/>
-      <c r="I28" s="189"/>
-      <c r="J28" s="189"/>
-      <c r="K28" s="189"/>
-      <c r="L28" s="189"/>
-      <c r="M28" s="190"/>
-      <c r="N28" s="181"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="57"/>
-      <c r="R28" s="184"/>
-      <c r="S28" s="184"/>
-    </row>
-    <row r="29" spans="1:19" ht="30" customHeight="1">
-      <c r="A29" s="57"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="180"/>
-      <c r="D29" s="180"/>
-      <c r="E29" s="180"/>
-      <c r="F29" s="180"/>
-      <c r="G29" s="180"/>
-      <c r="H29" s="188"/>
-      <c r="I29" s="189"/>
-      <c r="J29" s="189"/>
-      <c r="K29" s="189"/>
-      <c r="L29" s="189"/>
-      <c r="M29" s="190"/>
-      <c r="N29" s="181"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="57"/>
-      <c r="R29" s="184"/>
-      <c r="S29" s="184"/>
-    </row>
-    <row r="30" spans="1:19" ht="30" customHeight="1">
-      <c r="A30" s="57"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="180"/>
-      <c r="D30" s="180"/>
-      <c r="E30" s="180"/>
-      <c r="F30" s="180"/>
-      <c r="G30" s="180"/>
-      <c r="H30" s="188"/>
-      <c r="I30" s="189"/>
-      <c r="J30" s="189"/>
-      <c r="K30" s="189"/>
-      <c r="L30" s="189"/>
-      <c r="M30" s="190"/>
-      <c r="N30" s="181"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="57"/>
-      <c r="R30" s="184"/>
-      <c r="S30" s="184"/>
-    </row>
-    <row r="31" spans="1:19" ht="30" customHeight="1">
-      <c r="A31" s="57"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="180"/>
-      <c r="D31" s="180"/>
-      <c r="E31" s="180"/>
-      <c r="F31" s="180"/>
-      <c r="G31" s="180"/>
-      <c r="H31" s="188"/>
-      <c r="I31" s="189"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="189"/>
-      <c r="L31" s="189"/>
-      <c r="M31" s="190"/>
-      <c r="N31" s="181"/>
-      <c r="O31" s="182"/>
-      <c r="P31" s="183"/>
-      <c r="Q31" s="57"/>
-      <c r="R31" s="184"/>
-      <c r="S31" s="184"/>
-    </row>
-    <row r="32" spans="1:19" ht="30" customHeight="1">
-      <c r="A32" s="57"/>
-      <c r="B32" s="57"/>
-      <c r="C32" s="180"/>
-      <c r="D32" s="180"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="180"/>
-      <c r="G32" s="180"/>
-      <c r="H32" s="188"/>
-      <c r="I32" s="189"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="189"/>
-      <c r="L32" s="189"/>
-      <c r="M32" s="190"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="183"/>
-      <c r="Q32" s="57"/>
-      <c r="R32" s="184"/>
-      <c r="S32" s="184"/>
-    </row>
-    <row r="33" spans="1:19" ht="30" customHeight="1">
-      <c r="A33" s="57"/>
-      <c r="B33" s="57"/>
-      <c r="C33" s="180"/>
-      <c r="D33" s="180"/>
-      <c r="E33" s="180"/>
-      <c r="F33" s="180"/>
-      <c r="G33" s="180"/>
-      <c r="H33" s="188"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="189"/>
-      <c r="L33" s="189"/>
-      <c r="M33" s="190"/>
-      <c r="N33" s="181"/>
-      <c r="O33" s="182"/>
-      <c r="P33" s="183"/>
-      <c r="Q33" s="57"/>
-      <c r="R33" s="184"/>
-      <c r="S33" s="184"/>
-    </row>
-    <row r="34" spans="1:19" ht="30" customHeight="1">
-      <c r="A34" s="57"/>
-      <c r="B34" s="57"/>
-      <c r="C34" s="180"/>
-      <c r="D34" s="180"/>
-      <c r="E34" s="180"/>
-      <c r="F34" s="180"/>
-      <c r="G34" s="180"/>
-      <c r="H34" s="188"/>
-      <c r="I34" s="189"/>
-      <c r="J34" s="189"/>
-      <c r="K34" s="189"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="190"/>
-      <c r="N34" s="181"/>
-      <c r="O34" s="182"/>
-      <c r="P34" s="183"/>
-      <c r="Q34" s="57"/>
-      <c r="R34" s="184"/>
-      <c r="S34" s="184"/>
-    </row>
-    <row r="35" spans="1:19" ht="30" customHeight="1">
-      <c r="A35" s="57"/>
-      <c r="B35" s="57"/>
-      <c r="C35" s="180"/>
-      <c r="D35" s="180"/>
-      <c r="E35" s="180"/>
-      <c r="F35" s="180"/>
-      <c r="G35" s="180"/>
-      <c r="H35" s="188"/>
-      <c r="I35" s="189"/>
-      <c r="J35" s="189"/>
-      <c r="K35" s="189"/>
-      <c r="L35" s="189"/>
-      <c r="M35" s="190"/>
-      <c r="N35" s="181"/>
-      <c r="O35" s="182"/>
-      <c r="P35" s="183"/>
-      <c r="Q35" s="57"/>
-      <c r="R35" s="184"/>
-      <c r="S35" s="184"/>
-    </row>
-    <row r="36" spans="1:19" ht="30" customHeight="1">
-      <c r="A36" s="57"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="180"/>
-      <c r="D36" s="180"/>
-      <c r="E36" s="180"/>
-      <c r="F36" s="180"/>
-      <c r="G36" s="180"/>
-      <c r="H36" s="188"/>
-      <c r="I36" s="189"/>
-      <c r="J36" s="189"/>
-      <c r="K36" s="189"/>
-      <c r="L36" s="189"/>
-      <c r="M36" s="190"/>
-      <c r="N36" s="181"/>
-      <c r="O36" s="182"/>
-      <c r="P36" s="183"/>
-      <c r="Q36" s="57"/>
-      <c r="R36" s="184"/>
-      <c r="S36" s="184"/>
-    </row>
-    <row r="37" spans="1:19" ht="30" customHeight="1">
-      <c r="A37" s="57"/>
-      <c r="B37" s="57"/>
-      <c r="C37" s="180"/>
-      <c r="D37" s="180"/>
-      <c r="E37" s="180"/>
-      <c r="F37" s="180"/>
-      <c r="G37" s="180"/>
-      <c r="H37" s="188"/>
-      <c r="I37" s="189"/>
-      <c r="J37" s="189"/>
-      <c r="K37" s="189"/>
-      <c r="L37" s="189"/>
-      <c r="M37" s="190"/>
-      <c r="N37" s="181"/>
-      <c r="O37" s="182"/>
-      <c r="P37" s="183"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="184"/>
-      <c r="S37" s="184"/>
-    </row>
-    <row r="38" spans="1:19" ht="30" customHeight="1">
-      <c r="A38" s="57"/>
-      <c r="B38" s="57"/>
-      <c r="C38" s="180"/>
-      <c r="D38" s="180"/>
-      <c r="E38" s="180"/>
-      <c r="F38" s="180"/>
-      <c r="G38" s="180"/>
-      <c r="H38" s="188"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="189"/>
-      <c r="K38" s="189"/>
-      <c r="L38" s="189"/>
-      <c r="M38" s="190"/>
-      <c r="N38" s="181"/>
-      <c r="O38" s="182"/>
-      <c r="P38" s="183"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="184"/>
-      <c r="S38" s="184"/>
-    </row>
-    <row r="39" spans="1:19" ht="30" customHeight="1">
-      <c r="A39" s="57"/>
-      <c r="B39" s="57"/>
-      <c r="C39" s="180"/>
-      <c r="D39" s="180"/>
-      <c r="E39" s="180"/>
-      <c r="F39" s="180"/>
-      <c r="G39" s="180"/>
-      <c r="H39" s="188"/>
-      <c r="I39" s="189"/>
-      <c r="J39" s="189"/>
-      <c r="K39" s="189"/>
-      <c r="L39" s="189"/>
-      <c r="M39" s="190"/>
-      <c r="N39" s="181"/>
-      <c r="O39" s="182"/>
-      <c r="P39" s="183"/>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="184"/>
-      <c r="S39" s="184"/>
-    </row>
-    <row r="40" spans="1:19" ht="30" customHeight="1">
-      <c r="A40" s="57"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="180"/>
-      <c r="D40" s="180"/>
-      <c r="E40" s="180"/>
-      <c r="F40" s="180"/>
-      <c r="G40" s="180"/>
-      <c r="H40" s="188"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
-      <c r="L40" s="189"/>
-      <c r="M40" s="190"/>
-      <c r="N40" s="181"/>
-      <c r="O40" s="182"/>
-      <c r="P40" s="183"/>
-      <c r="Q40" s="57"/>
-      <c r="R40" s="184"/>
-      <c r="S40" s="184"/>
-    </row>
-    <row r="41" spans="1:19" ht="30" customHeight="1">
-      <c r="A41" s="57"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="180"/>
-      <c r="D41" s="180"/>
-      <c r="E41" s="180"/>
-      <c r="F41" s="180"/>
-      <c r="G41" s="180"/>
-      <c r="H41" s="188"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="189"/>
-      <c r="L41" s="189"/>
-      <c r="M41" s="190"/>
-      <c r="N41" s="181"/>
-      <c r="O41" s="182"/>
-      <c r="P41" s="183"/>
-      <c r="Q41" s="57"/>
-      <c r="R41" s="184"/>
-      <c r="S41" s="184"/>
-    </row>
-    <row r="42" spans="1:19" ht="30" customHeight="1">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="180"/>
-      <c r="D42" s="180"/>
-      <c r="E42" s="180"/>
-      <c r="F42" s="180"/>
-      <c r="G42" s="180"/>
-      <c r="H42" s="188"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="189"/>
-      <c r="M42" s="190"/>
-      <c r="N42" s="181"/>
-      <c r="O42" s="182"/>
-      <c r="P42" s="183"/>
-      <c r="Q42" s="57"/>
-      <c r="R42" s="184"/>
-      <c r="S42" s="184"/>
-    </row>
-    <row r="43" spans="1:19" ht="30" customHeight="1">
-      <c r="A43" s="57"/>
-      <c r="B43" s="57"/>
-      <c r="C43" s="180"/>
-      <c r="D43" s="180"/>
-      <c r="E43" s="180"/>
-      <c r="F43" s="180"/>
-      <c r="G43" s="180"/>
-      <c r="H43" s="188"/>
-      <c r="I43" s="189"/>
-      <c r="J43" s="189"/>
-      <c r="K43" s="189"/>
-      <c r="L43" s="189"/>
-      <c r="M43" s="190"/>
-      <c r="N43" s="181"/>
-      <c r="O43" s="182"/>
-      <c r="P43" s="183"/>
-      <c r="Q43" s="57"/>
-      <c r="R43" s="184"/>
-      <c r="S43" s="184"/>
-    </row>
-    <row r="44" spans="1:19" ht="30" customHeight="1">
-      <c r="A44" s="57"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="180"/>
-      <c r="D44" s="180"/>
-      <c r="E44" s="180"/>
-      <c r="F44" s="180"/>
-      <c r="G44" s="180"/>
-      <c r="H44" s="188"/>
-      <c r="I44" s="189"/>
-      <c r="J44" s="189"/>
-      <c r="K44" s="189"/>
-      <c r="L44" s="189"/>
-      <c r="M44" s="190"/>
-      <c r="N44" s="181"/>
-      <c r="O44" s="182"/>
-      <c r="P44" s="183"/>
-      <c r="Q44" s="57"/>
-      <c r="R44" s="184"/>
-      <c r="S44" s="184"/>
-    </row>
-    <row r="45" spans="1:19" ht="30" customHeight="1">
-      <c r="A45" s="57"/>
-      <c r="B45" s="57"/>
-      <c r="C45" s="180"/>
-      <c r="D45" s="180"/>
-      <c r="E45" s="180"/>
-      <c r="F45" s="180"/>
-      <c r="G45" s="180"/>
-      <c r="H45" s="188"/>
-      <c r="I45" s="189"/>
-      <c r="J45" s="189"/>
-      <c r="K45" s="189"/>
-      <c r="L45" s="189"/>
-      <c r="M45" s="190"/>
-      <c r="N45" s="181"/>
-      <c r="O45" s="182"/>
-      <c r="P45" s="183"/>
-      <c r="Q45" s="57"/>
-      <c r="R45" s="184"/>
-      <c r="S45" s="184"/>
-    </row>
-    <row r="46" spans="1:19" ht="30" customHeight="1">
-      <c r="A46" s="57"/>
-      <c r="B46" s="57"/>
-      <c r="C46" s="180"/>
-      <c r="D46" s="180"/>
-      <c r="E46" s="180"/>
-      <c r="F46" s="180"/>
-      <c r="G46" s="180"/>
-      <c r="H46" s="188"/>
-      <c r="I46" s="189"/>
-      <c r="J46" s="189"/>
-      <c r="K46" s="189"/>
-      <c r="L46" s="189"/>
-      <c r="M46" s="190"/>
-      <c r="N46" s="181"/>
-      <c r="O46" s="182"/>
-      <c r="P46" s="183"/>
-      <c r="Q46" s="57"/>
-      <c r="R46" s="184"/>
-      <c r="S46" s="184"/>
-    </row>
-    <row r="47" spans="1:19" ht="30" customHeight="1">
-      <c r="A47" s="57"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="180"/>
-      <c r="D47" s="180"/>
-      <c r="E47" s="180"/>
-      <c r="F47" s="180"/>
-      <c r="G47" s="180"/>
-      <c r="H47" s="188"/>
-      <c r="I47" s="189"/>
-      <c r="J47" s="189"/>
-      <c r="K47" s="189"/>
-      <c r="L47" s="189"/>
-      <c r="M47" s="190"/>
-      <c r="N47" s="181"/>
-      <c r="O47" s="182"/>
-      <c r="P47" s="183"/>
-      <c r="Q47" s="57"/>
-      <c r="R47" s="184"/>
-      <c r="S47" s="184"/>
-    </row>
-    <row r="48" spans="1:19" ht="30" customHeight="1">
-      <c r="A48" s="57"/>
-      <c r="B48" s="57"/>
-      <c r="C48" s="180"/>
-      <c r="D48" s="180"/>
-      <c r="E48" s="180"/>
-      <c r="F48" s="180"/>
-      <c r="G48" s="180"/>
-      <c r="H48" s="188"/>
-      <c r="I48" s="189"/>
-      <c r="J48" s="189"/>
-      <c r="K48" s="189"/>
-      <c r="L48" s="189"/>
-      <c r="M48" s="190"/>
-      <c r="N48" s="181"/>
-      <c r="O48" s="182"/>
-      <c r="P48" s="183"/>
-      <c r="Q48" s="57"/>
-      <c r="R48" s="184"/>
-      <c r="S48" s="184"/>
-    </row>
-    <row r="49" spans="1:19" ht="30" customHeight="1">
-      <c r="A49" s="57"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="180"/>
-      <c r="D49" s="180"/>
-      <c r="E49" s="180"/>
-      <c r="F49" s="180"/>
-      <c r="G49" s="180"/>
-      <c r="H49" s="188"/>
-      <c r="I49" s="189"/>
-      <c r="J49" s="189"/>
-      <c r="K49" s="189"/>
-      <c r="L49" s="189"/>
-      <c r="M49" s="190"/>
-      <c r="N49" s="181"/>
-      <c r="O49" s="182"/>
-      <c r="P49" s="183"/>
-      <c r="Q49" s="57"/>
-      <c r="R49" s="184"/>
-      <c r="S49" s="184"/>
-    </row>
-    <row r="50" spans="1:19" ht="30" customHeight="1">
-      <c r="A50" s="57"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="180"/>
-      <c r="D50" s="180"/>
-      <c r="E50" s="180"/>
-      <c r="F50" s="180"/>
-      <c r="G50" s="180"/>
-      <c r="H50" s="188"/>
-      <c r="I50" s="189"/>
-      <c r="J50" s="189"/>
-      <c r="K50" s="189"/>
-      <c r="L50" s="189"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="181"/>
-      <c r="O50" s="182"/>
-      <c r="P50" s="183"/>
-      <c r="Q50" s="57"/>
-      <c r="R50" s="184"/>
-      <c r="S50" s="184"/>
-    </row>
-    <row r="51" spans="1:19" ht="30" customHeight="1">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="180"/>
-      <c r="D51" s="180"/>
-      <c r="E51" s="180"/>
-      <c r="F51" s="180"/>
-      <c r="G51" s="180"/>
-      <c r="H51" s="188"/>
-      <c r="I51" s="189"/>
-      <c r="J51" s="189"/>
-      <c r="K51" s="189"/>
-      <c r="L51" s="189"/>
-      <c r="M51" s="190"/>
-      <c r="N51" s="181"/>
-      <c r="O51" s="182"/>
-      <c r="P51" s="183"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="184"/>
-      <c r="S51" s="184"/>
-    </row>
-    <row r="52" spans="1:19" ht="30" customHeight="1">
-      <c r="A52" s="57"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="180"/>
-      <c r="D52" s="180"/>
-      <c r="E52" s="180"/>
-      <c r="F52" s="180"/>
-      <c r="G52" s="180"/>
-      <c r="H52" s="188"/>
-      <c r="I52" s="189"/>
-      <c r="J52" s="189"/>
-      <c r="K52" s="189"/>
-      <c r="L52" s="189"/>
-      <c r="M52" s="190"/>
-      <c r="N52" s="181"/>
-      <c r="O52" s="182"/>
-      <c r="P52" s="183"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="184"/>
-      <c r="S52" s="184"/>
-    </row>
-  </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="R2:S2"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Documents/タスク編集設計書.xlsx
+++ b/Documents/タスク編集設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-24\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6902E74-FD13-44C6-AA82-95324A94C380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28168027-0602-435C-8E2D-117614C2D403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6495" yWindow="300" windowWidth="11415" windowHeight="8955" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,11 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -762,6 +761,50 @@
     <t>画面遷移図</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>異常系</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態でのページ表示</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-edit.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1535,7 +1578,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1704,6 +1747,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1737,21 +1825,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1797,36 +1870,6 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1893,42 +1936,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1941,56 +1984,73 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4062,19 +4122,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="64"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4086,190 +4146,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="E2" s="93"/>
+      <c r="F2" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
+      <c r="G2" s="93"/>
+      <c r="H2" s="96">
         <v>45806</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="66"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="81"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="71"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="70" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="71"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70" t="s">
+      <c r="B8" s="57"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="71"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="96" t="s">
+      <c r="C9" s="58"/>
+      <c r="D9" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="71"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="60"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="95" t="s">
+      <c r="A10" s="67"/>
+      <c r="B10" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="71"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95" t="s">
+      <c r="A11" s="68"/>
+      <c r="B11" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="96" t="s">
+      <c r="C11" s="58"/>
+      <c r="D11" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="71"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="70" t="s">
+      <c r="B12" s="57"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="71"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="88"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="91"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5260,6 +5320,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5275,18 +5347,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5309,16 +5369,16 @@
       <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="64"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -5330,46 +5390,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="E2" s="93"/>
+      <c r="F2" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
+      <c r="G2" s="93"/>
+      <c r="H2" s="96">
         <v>45806</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="59"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -8210,23 +8270,23 @@
       <c r="J4" s="103"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="114"/>
-      <c r="D5" s="125" t="s">
+      <c r="D5" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="126"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="122" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="49"/>
@@ -8237,19 +8297,19 @@
       <c r="G6" s="49"/>
       <c r="H6" s="49"/>
       <c r="I6" s="49"/>
-      <c r="J6" s="120"/>
+      <c r="J6" s="125"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="127"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="108"/>
@@ -8261,7 +8321,7 @@
       <c r="G8" s="52"/>
       <c r="H8" s="52"/>
       <c r="I8" s="52"/>
-      <c r="J8" s="130"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="108"/>
@@ -8273,7 +8333,7 @@
       <c r="G9" s="52"/>
       <c r="H9" s="52"/>
       <c r="I9" s="52"/>
-      <c r="J9" s="130"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="108"/>
@@ -8285,7 +8345,7 @@
       <c r="G10" s="52"/>
       <c r="H10" s="52"/>
       <c r="I10" s="52"/>
-      <c r="J10" s="130"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="108"/>
@@ -8297,7 +8357,7 @@
       <c r="G11" s="52"/>
       <c r="H11" s="52"/>
       <c r="I11" s="52"/>
-      <c r="J11" s="130"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="108"/>
@@ -8309,7 +8369,7 @@
       <c r="G12" s="52"/>
       <c r="H12" s="52"/>
       <c r="I12" s="52"/>
-      <c r="J12" s="130"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="108"/>
@@ -8321,10 +8381,10 @@
       <c r="G13" s="52"/>
       <c r="H13" s="52"/>
       <c r="I13" s="52"/>
-      <c r="J13" s="130"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="122" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="49"/>
@@ -8335,15 +8395,15 @@
       <c r="G14" s="49"/>
       <c r="H14" s="49"/>
       <c r="I14" s="49"/>
-      <c r="J14" s="120"/>
+      <c r="J14" s="125"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="122" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="49"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="130" t="s">
         <v>68</v>
       </c>
       <c r="E15" s="49"/>
@@ -8358,7 +8418,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="122" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="49"/>
@@ -8379,7 +8439,7 @@
         <v>18</v>
       </c>
       <c r="I16" s="49"/>
-      <c r="J16" s="120"/>
+      <c r="J16" s="125"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="121">
@@ -8399,9 +8459,9 @@
       <c r="G17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="119"/>
+      <c r="H17" s="130"/>
       <c r="I17" s="49"/>
-      <c r="J17" s="120"/>
+      <c r="J17" s="125"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="121">
@@ -8421,9 +8481,9 @@
       <c r="G18" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="119"/>
+      <c r="H18" s="130"/>
       <c r="I18" s="49"/>
-      <c r="J18" s="120"/>
+      <c r="J18" s="125"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="121">
@@ -8443,9 +8503,9 @@
       <c r="G19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="119"/>
+      <c r="H19" s="130"/>
       <c r="I19" s="49"/>
-      <c r="J19" s="120"/>
+      <c r="J19" s="125"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="121">
@@ -8465,9 +8525,9 @@
       <c r="G20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="119"/>
+      <c r="H20" s="130"/>
       <c r="I20" s="49"/>
-      <c r="J20" s="120"/>
+      <c r="J20" s="125"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="121">
@@ -8487,9 +8547,9 @@
       <c r="G21" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="119"/>
+      <c r="H21" s="130"/>
       <c r="I21" s="49"/>
-      <c r="J21" s="120"/>
+      <c r="J21" s="125"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="121">
@@ -8509,9 +8569,9 @@
       <c r="G22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="119"/>
+      <c r="H22" s="130"/>
       <c r="I22" s="49"/>
-      <c r="J22" s="120"/>
+      <c r="J22" s="125"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="121">
@@ -9514,11 +9574,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9535,16 +9600,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9564,7 +9624,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="142" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="106"/>
@@ -9575,14 +9635,14 @@
       <c r="G1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
       <c r="J1" s="114"/>
       <c r="K1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
       <c r="N1" s="114"/>
       <c r="O1" s="113" t="s">
         <v>7</v>
@@ -9595,7 +9655,7 @@
       <c r="S1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="126"/>
+      <c r="T1" s="124"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="108"/>
@@ -9607,16 +9667,16 @@
       <c r="G2" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
       <c r="J2" s="116"/>
       <c r="K2" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
       <c r="N2" s="116"/>
-      <c r="O2" s="151">
+      <c r="O2" s="140">
         <v>45821</v>
       </c>
       <c r="P2" s="116"/>
@@ -9625,7 +9685,7 @@
       </c>
       <c r="R2" s="116"/>
       <c r="S2" s="115"/>
-      <c r="T2" s="129"/>
+      <c r="T2" s="128"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="108"/>
@@ -9647,7 +9707,7 @@
       <c r="Q3" s="117"/>
       <c r="R3" s="109"/>
       <c r="S3" s="117"/>
-      <c r="T3" s="130"/>
+      <c r="T3" s="129"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="110"/>
@@ -9669,36 +9729,36 @@
       <c r="Q4" s="118"/>
       <c r="R4" s="112"/>
       <c r="S4" s="118"/>
-      <c r="T4" s="145"/>
+      <c r="T4" s="141"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="123"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="114"/>
-      <c r="G5" s="142" t="s">
+      <c r="G5" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="123"/>
-      <c r="N5" s="123"/>
-      <c r="O5" s="123"/>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="126"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="124"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="122" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="49"/>
@@ -9706,7 +9766,7 @@
       <c r="D6" s="49"/>
       <c r="E6" s="49"/>
       <c r="F6" s="50"/>
-      <c r="G6" s="119" t="s">
+      <c r="G6" s="130" t="s">
         <v>107</v>
       </c>
       <c r="H6" s="49"/>
@@ -9721,10 +9781,10 @@
       <c r="Q6" s="49"/>
       <c r="R6" s="49"/>
       <c r="S6" s="49"/>
-      <c r="T6" s="120"/>
+      <c r="T6" s="125"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="122" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="49"/>
@@ -9732,7 +9792,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="50"/>
-      <c r="G7" s="119" t="s">
+      <c r="G7" s="130" t="s">
         <v>57</v>
       </c>
       <c r="H7" s="49"/>
@@ -9747,7 +9807,7 @@
       <c r="Q7" s="49"/>
       <c r="R7" s="49"/>
       <c r="S7" s="49"/>
-      <c r="T7" s="120"/>
+      <c r="T7" s="125"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -9946,11 +10006,11 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="122" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="50"/>
-      <c r="C15" s="144" t="s">
+      <c r="C15" s="149" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="50"/>
@@ -9988,33 +10048,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="135">
+      <c r="A16" s="144">
         <v>1</v>
       </c>
       <c r="B16" s="50"/>
-      <c r="C16" s="136" t="s">
+      <c r="C16" s="145" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="50"/>
-      <c r="E16" s="136" t="s">
+      <c r="E16" s="145" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="50"/>
-      <c r="G16" s="143" t="s">
+      <c r="G16" s="135" t="s">
         <v>90</v>
       </c>
       <c r="H16" s="49"/>
       <c r="I16" s="50"/>
-      <c r="J16" s="143" t="s">
+      <c r="J16" s="135" t="s">
         <v>91</v>
       </c>
       <c r="K16" s="50"/>
-      <c r="L16" s="150" t="s">
+      <c r="L16" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="M16" s="148"/>
-      <c r="N16" s="149"/>
-      <c r="O16" s="140" t="s">
+      <c r="M16" s="147"/>
+      <c r="N16" s="148"/>
+      <c r="O16" s="138" t="s">
         <v>93</v>
       </c>
       <c r="P16" s="49"/>
@@ -10030,33 +10090,33 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="62.25" customHeight="1">
-      <c r="A17" s="135">
+      <c r="A17" s="144">
         <v>2</v>
       </c>
       <c r="B17" s="50"/>
-      <c r="C17" s="136" t="s">
+      <c r="C17" s="145" t="s">
         <v>94</v>
       </c>
       <c r="D17" s="50"/>
-      <c r="E17" s="136" t="s">
+      <c r="E17" s="145" t="s">
         <v>95</v>
       </c>
       <c r="F17" s="50"/>
-      <c r="G17" s="143" t="s">
+      <c r="G17" s="135" t="s">
         <v>96</v>
       </c>
       <c r="H17" s="49"/>
       <c r="I17" s="50"/>
-      <c r="J17" s="143" t="s">
+      <c r="J17" s="135" t="s">
         <v>97</v>
       </c>
       <c r="K17" s="50"/>
-      <c r="L17" s="140" t="s">
+      <c r="L17" s="138" t="s">
         <v>98</v>
       </c>
       <c r="M17" s="49"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="140" t="s">
+      <c r="O17" s="138" t="s">
         <v>99</v>
       </c>
       <c r="P17" s="49"/>
@@ -10072,33 +10132,33 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="54" customHeight="1">
-      <c r="A18" s="135">
+      <c r="A18" s="144">
         <v>3</v>
       </c>
       <c r="B18" s="50"/>
-      <c r="C18" s="136" t="s">
+      <c r="C18" s="145" t="s">
         <v>94</v>
       </c>
       <c r="D18" s="50"/>
-      <c r="E18" s="136" t="s">
+      <c r="E18" s="145" t="s">
         <v>95</v>
       </c>
       <c r="F18" s="50"/>
-      <c r="G18" s="143" t="s">
+      <c r="G18" s="135" t="s">
         <v>100</v>
       </c>
       <c r="H18" s="49"/>
       <c r="I18" s="50"/>
-      <c r="J18" s="143" t="s">
+      <c r="J18" s="135" t="s">
         <v>101</v>
       </c>
       <c r="K18" s="50"/>
-      <c r="L18" s="140" t="s">
+      <c r="L18" s="138" t="s">
         <v>102</v>
       </c>
       <c r="M18" s="49"/>
       <c r="N18" s="50"/>
-      <c r="O18" s="140" t="s">
+      <c r="O18" s="138" t="s">
         <v>103</v>
       </c>
       <c r="P18" s="49"/>
@@ -10114,33 +10174,33 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A19" s="135">
+      <c r="A19" s="144">
         <v>4</v>
       </c>
       <c r="B19" s="50"/>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="145" t="s">
         <v>94</v>
       </c>
       <c r="D19" s="50"/>
-      <c r="E19" s="136" t="s">
+      <c r="E19" s="145" t="s">
         <v>95</v>
       </c>
       <c r="F19" s="50"/>
-      <c r="G19" s="143" t="s">
+      <c r="G19" s="135" t="s">
         <v>104</v>
       </c>
       <c r="H19" s="49"/>
       <c r="I19" s="50"/>
-      <c r="J19" s="143" t="s">
+      <c r="J19" s="135" t="s">
         <v>105</v>
       </c>
       <c r="K19" s="50"/>
-      <c r="L19" s="140" t="s">
+      <c r="L19" s="138" t="s">
         <v>102</v>
       </c>
       <c r="M19" s="49"/>
       <c r="N19" s="50"/>
-      <c r="O19" s="140" t="s">
+      <c r="O19" s="138" t="s">
         <v>106</v>
       </c>
       <c r="P19" s="49"/>
@@ -10156,26 +10216,40 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="57" customHeight="1">
-      <c r="A20" s="135"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="140"/>
+      <c r="A20" s="152">
+        <v>7</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="153" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="58"/>
+      <c r="E20" s="153" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="58"/>
+      <c r="G20" s="154" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="57"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="154" t="s">
+        <v>110</v>
+      </c>
+      <c r="K20" s="58"/>
+      <c r="L20" s="155" t="s">
+        <v>112</v>
+      </c>
+      <c r="M20" s="156"/>
+      <c r="N20" s="156"/>
+      <c r="O20" s="138" t="s">
+        <v>111</v>
+      </c>
       <c r="P20" s="49"/>
       <c r="Q20" s="50"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="33"/>
+      <c r="R20" s="157"/>
+      <c r="S20" s="157"/>
+      <c r="T20" s="158"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -10184,21 +10258,21 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="135"/>
+      <c r="A21" s="144"/>
       <c r="B21" s="50"/>
-      <c r="C21" s="136"/>
+      <c r="C21" s="145"/>
       <c r="D21" s="50"/>
-      <c r="E21" s="136"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="50"/>
-      <c r="G21" s="143"/>
+      <c r="G21" s="135"/>
       <c r="H21" s="49"/>
       <c r="I21" s="50"/>
-      <c r="J21" s="143"/>
+      <c r="J21" s="135"/>
       <c r="K21" s="50"/>
-      <c r="L21" s="140"/>
+      <c r="L21" s="138"/>
       <c r="M21" s="49"/>
       <c r="N21" s="50"/>
-      <c r="O21" s="140"/>
+      <c r="O21" s="138"/>
       <c r="P21" s="49"/>
       <c r="Q21" s="50"/>
       <c r="R21" s="32"/>
@@ -10212,21 +10286,21 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="135"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="50"/>
-      <c r="C22" s="136"/>
+      <c r="C22" s="145"/>
       <c r="D22" s="50"/>
-      <c r="E22" s="136"/>
+      <c r="E22" s="145"/>
       <c r="F22" s="50"/>
-      <c r="G22" s="143"/>
+      <c r="G22" s="135"/>
       <c r="H22" s="49"/>
       <c r="I22" s="50"/>
-      <c r="J22" s="143"/>
+      <c r="J22" s="135"/>
       <c r="K22" s="50"/>
-      <c r="L22" s="140"/>
+      <c r="L22" s="138"/>
       <c r="M22" s="49"/>
       <c r="N22" s="50"/>
-      <c r="O22" s="140"/>
+      <c r="O22" s="138"/>
       <c r="P22" s="49"/>
       <c r="Q22" s="50"/>
       <c r="R22" s="32"/>
@@ -10240,21 +10314,21 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="135"/>
+      <c r="A23" s="144"/>
       <c r="B23" s="50"/>
-      <c r="C23" s="136"/>
+      <c r="C23" s="145"/>
       <c r="D23" s="50"/>
-      <c r="E23" s="136"/>
+      <c r="E23" s="145"/>
       <c r="F23" s="50"/>
-      <c r="G23" s="143"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="49"/>
       <c r="I23" s="50"/>
-      <c r="J23" s="143"/>
+      <c r="J23" s="135"/>
       <c r="K23" s="50"/>
-      <c r="L23" s="140"/>
+      <c r="L23" s="138"/>
       <c r="M23" s="49"/>
       <c r="N23" s="50"/>
-      <c r="O23" s="140"/>
+      <c r="O23" s="138"/>
       <c r="P23" s="49"/>
       <c r="Q23" s="50"/>
       <c r="R23" s="32"/>
@@ -10268,21 +10342,21 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="135"/>
+      <c r="A24" s="144"/>
       <c r="B24" s="50"/>
-      <c r="C24" s="136"/>
+      <c r="C24" s="145"/>
       <c r="D24" s="50"/>
-      <c r="E24" s="136"/>
+      <c r="E24" s="145"/>
       <c r="F24" s="50"/>
-      <c r="G24" s="143"/>
+      <c r="G24" s="135"/>
       <c r="H24" s="49"/>
       <c r="I24" s="50"/>
-      <c r="J24" s="143"/>
+      <c r="J24" s="135"/>
       <c r="K24" s="50"/>
-      <c r="L24" s="140"/>
+      <c r="L24" s="138"/>
       <c r="M24" s="49"/>
       <c r="N24" s="50"/>
-      <c r="O24" s="140"/>
+      <c r="O24" s="138"/>
       <c r="P24" s="49"/>
       <c r="Q24" s="50"/>
       <c r="R24" s="32"/>
@@ -10296,21 +10370,21 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="135"/>
+      <c r="A25" s="144"/>
       <c r="B25" s="50"/>
-      <c r="C25" s="136"/>
+      <c r="C25" s="145"/>
       <c r="D25" s="50"/>
-      <c r="E25" s="136"/>
+      <c r="E25" s="145"/>
       <c r="F25" s="50"/>
-      <c r="G25" s="143"/>
+      <c r="G25" s="135"/>
       <c r="H25" s="49"/>
       <c r="I25" s="50"/>
-      <c r="J25" s="143"/>
+      <c r="J25" s="135"/>
       <c r="K25" s="50"/>
-      <c r="L25" s="140"/>
+      <c r="L25" s="138"/>
       <c r="M25" s="49"/>
       <c r="N25" s="50"/>
-      <c r="O25" s="140"/>
+      <c r="O25" s="138"/>
       <c r="P25" s="49"/>
       <c r="Q25" s="50"/>
       <c r="R25" s="32"/>
@@ -10324,21 +10398,21 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="135"/>
+      <c r="A26" s="144"/>
       <c r="B26" s="50"/>
-      <c r="C26" s="136"/>
+      <c r="C26" s="145"/>
       <c r="D26" s="50"/>
-      <c r="E26" s="136"/>
+      <c r="E26" s="145"/>
       <c r="F26" s="50"/>
-      <c r="G26" s="143"/>
+      <c r="G26" s="135"/>
       <c r="H26" s="49"/>
       <c r="I26" s="50"/>
-      <c r="J26" s="143"/>
+      <c r="J26" s="135"/>
       <c r="K26" s="50"/>
-      <c r="L26" s="140"/>
+      <c r="L26" s="138"/>
       <c r="M26" s="49"/>
       <c r="N26" s="50"/>
-      <c r="O26" s="140"/>
+      <c r="O26" s="138"/>
       <c r="P26" s="49"/>
       <c r="Q26" s="50"/>
       <c r="R26" s="32"/>
@@ -10352,21 +10426,21 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="135"/>
+      <c r="A27" s="144"/>
       <c r="B27" s="50"/>
-      <c r="C27" s="136"/>
+      <c r="C27" s="145"/>
       <c r="D27" s="50"/>
-      <c r="E27" s="136"/>
+      <c r="E27" s="145"/>
       <c r="F27" s="50"/>
-      <c r="G27" s="143"/>
+      <c r="G27" s="135"/>
       <c r="H27" s="49"/>
       <c r="I27" s="50"/>
-      <c r="J27" s="143"/>
+      <c r="J27" s="135"/>
       <c r="K27" s="50"/>
-      <c r="L27" s="140"/>
+      <c r="L27" s="138"/>
       <c r="M27" s="49"/>
       <c r="N27" s="50"/>
-      <c r="O27" s="140"/>
+      <c r="O27" s="138"/>
       <c r="P27" s="49"/>
       <c r="Q27" s="50"/>
       <c r="R27" s="32"/>
@@ -10380,21 +10454,21 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="135"/>
+      <c r="A28" s="144"/>
       <c r="B28" s="50"/>
-      <c r="C28" s="136"/>
+      <c r="C28" s="145"/>
       <c r="D28" s="50"/>
-      <c r="E28" s="136"/>
+      <c r="E28" s="145"/>
       <c r="F28" s="50"/>
-      <c r="G28" s="143"/>
+      <c r="G28" s="135"/>
       <c r="H28" s="49"/>
       <c r="I28" s="50"/>
-      <c r="J28" s="143"/>
+      <c r="J28" s="135"/>
       <c r="K28" s="50"/>
-      <c r="L28" s="140"/>
+      <c r="L28" s="138"/>
       <c r="M28" s="49"/>
       <c r="N28" s="50"/>
-      <c r="O28" s="140"/>
+      <c r="O28" s="138"/>
       <c r="P28" s="49"/>
       <c r="Q28" s="50"/>
       <c r="R28" s="32"/>
@@ -10408,21 +10482,21 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="135"/>
+      <c r="A29" s="144"/>
       <c r="B29" s="50"/>
-      <c r="C29" s="136"/>
+      <c r="C29" s="145"/>
       <c r="D29" s="50"/>
-      <c r="E29" s="136"/>
+      <c r="E29" s="145"/>
       <c r="F29" s="50"/>
-      <c r="G29" s="143"/>
+      <c r="G29" s="135"/>
       <c r="H29" s="49"/>
       <c r="I29" s="50"/>
-      <c r="J29" s="143"/>
+      <c r="J29" s="135"/>
       <c r="K29" s="50"/>
-      <c r="L29" s="140"/>
+      <c r="L29" s="138"/>
       <c r="M29" s="49"/>
       <c r="N29" s="50"/>
-      <c r="O29" s="140"/>
+      <c r="O29" s="138"/>
       <c r="P29" s="49"/>
       <c r="Q29" s="50"/>
       <c r="R29" s="32"/>
@@ -10436,21 +10510,21 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="135"/>
+      <c r="A30" s="144"/>
       <c r="B30" s="50"/>
-      <c r="C30" s="136"/>
+      <c r="C30" s="145"/>
       <c r="D30" s="50"/>
-      <c r="E30" s="136"/>
+      <c r="E30" s="145"/>
       <c r="F30" s="50"/>
-      <c r="G30" s="143"/>
+      <c r="G30" s="135"/>
       <c r="H30" s="49"/>
       <c r="I30" s="50"/>
-      <c r="J30" s="143"/>
+      <c r="J30" s="135"/>
       <c r="K30" s="50"/>
-      <c r="L30" s="140"/>
+      <c r="L30" s="138"/>
       <c r="M30" s="49"/>
       <c r="N30" s="50"/>
-      <c r="O30" s="140"/>
+      <c r="O30" s="138"/>
       <c r="P30" s="49"/>
       <c r="Q30" s="50"/>
       <c r="R30" s="32"/>
@@ -10464,23 +10538,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="147"/>
+      <c r="A31" s="150"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="151"/>
+      <c r="F31" s="137"/>
+      <c r="G31" s="136"/>
       <c r="H31" s="133"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="147"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="141"/>
+      <c r="I31" s="137"/>
+      <c r="J31" s="136"/>
+      <c r="K31" s="137"/>
+      <c r="L31" s="139"/>
       <c r="M31" s="133"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="141"/>
+      <c r="N31" s="137"/>
+      <c r="O31" s="139"/>
       <c r="P31" s="133"/>
-      <c r="Q31" s="138"/>
+      <c r="Q31" s="137"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -11478,62 +11552,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11558,64 +11632,67 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="L20" r:id="rId1" xr:uid="{29959F9C-D2C5-4624-BB77-C32F70D08F79}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>

--- a/Documents/タスク編集設計書.xlsx
+++ b/Documents/タスク編集設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28168027-0602-435C-8E2D-117614C2D403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477E75AA-1030-4729-8A2E-AD07214BB930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="300" windowWidth="11415" windowHeight="8955" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,20 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="JUnitテスト仕様書兼報告書 (2)" sheetId="10" r:id="rId7"/>
+    <sheet name="カバレッジレポート" sheetId="11" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="ああ">#REF!</definedName>
+    <definedName name="範囲１" localSheetId="6">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="139">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -762,48 +769,220 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>異常系</t>
-    <phoneticPr fontId="8"/>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>ログアウト状態でのページ表示</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウタイ</t>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
     </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヒョウジ</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>タスク一覧</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログアウト状態であること</t>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
     <rPh sb="5" eb="7">
-      <t>ジョウタイ</t>
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
-    <rPh sb="20" eb="22">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ユウドウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ヒョウジ</t>
-    </rPh>
+    <t>TaskDAOTest</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>http://localhost:8080/taskUN/task-edit.jsp</t>
+    <t>update()</t>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>count==1</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>カバレッジレポート</t>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>（１）概要</t>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>対象クラス</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>TaskDAO.Java</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>カバレッジ率</t>
+    <rPh sb="5" eb="6">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>（２）報告事項</t>
+    <rPh sb="3" eb="5">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>調査結果</t>
+    <rPh sb="0" eb="2">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>分析・考察</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウサツ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
+  </si>
+  <si>
+    <t>備　考</t>
+    <rPh sb="0" eb="1">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="21"/>
   </si>
 </sst>
 </file>
@@ -813,7 +992,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -897,8 +1076,95 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -911,8 +1177,20 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="77">
     <border>
       <left/>
       <right/>
@@ -1572,13 +1850,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1723,6 +2244,97 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="72" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="73" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="74" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="75" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2035,28 +2647,137 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="71" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="71" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="6">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{6C10B5B7-E36B-40F5-9E99-A4A9558B5B5A}"/>
+    <cellStyle name="標準 2 2" xfId="5" xr:uid="{8FFEA0FA-F7CE-41FE-99C2-37F49EFBDA58}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="3" xr:uid="{4DFE3633-1B59-43CE-8502-06E7AFD138DD}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="4" xr:uid="{ECCD0612-EF6C-4CEE-A273-74138412619D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2748,6 +3469,111 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>68036</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>84365</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{299333A8-2380-54B8-3613-2996A46A4ABE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1292679" y="2245179"/>
+          <a:ext cx="7772400" cy="3646714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>68036</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>163243</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>132482</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>49193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60EC6485-0A9A-3224-BE22-88C70F03FDF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3333750" y="6585814"/>
+          <a:ext cx="3534268" cy="1790950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -2955,85 +3781,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3053,46 +3879,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="48" t="s">
+      <c r="H13" s="81"/>
+      <c r="I13" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="48"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="81"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="48"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="81"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3101,13 +3927,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="83"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4122,19 +4948,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="114"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="110"/>
+      <c r="F1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="79"/>
+      <c r="G1" s="110"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4146,190 +4972,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="92" t="s">
+      <c r="A2" s="116"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="93"/>
-      <c r="F2" s="92" t="s">
+      <c r="E2" s="124"/>
+      <c r="F2" s="123" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="96">
+      <c r="G2" s="124"/>
+      <c r="H2" s="127">
         <v>45806</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="105"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="106"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="107"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="80" t="s">
+      <c r="B5" s="109"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="81"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="112"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="59" t="s">
+      <c r="B6" s="88"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="60"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="91"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="88"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="60"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="91"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="59" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="60"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="91"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="70" t="s">
+      <c r="C9" s="89"/>
+      <c r="D9" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="60"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="91"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="98"/>
+      <c r="B10" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="60"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="91"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69" t="s">
+      <c r="A11" s="99"/>
+      <c r="B11" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="70" t="s">
+      <c r="C11" s="89"/>
+      <c r="D11" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="60"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="91"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="59" t="s">
+      <c r="B12" s="88"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="60"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="91"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="65"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5366,19 +6192,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="114"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="110"/>
+      <c r="F1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="79"/>
+      <c r="G1" s="110"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -5390,46 +6216,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="92" t="s">
+      <c r="A2" s="116"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="93"/>
-      <c r="F2" s="92" t="s">
+      <c r="E2" s="124"/>
+      <c r="F2" s="123" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="96">
+      <c r="G2" s="124"/>
+      <c r="H2" s="127">
         <v>45806</v>
       </c>
-      <c r="I2" s="71"/>
-      <c r="J2" s="74"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="105"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="106"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="76"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="107"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -6786,19 +7612,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="145"/>
+      <c r="F1" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="145"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6810,48 +7636,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="139"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115" t="s">
+      <c r="E2" s="147"/>
+      <c r="F2" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="147"/>
+      <c r="H2" s="129">
         <v>45810</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="133"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="139"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="134"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="141"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="135"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -8202,19 +9028,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="145"/>
+      <c r="F1" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="145"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -8226,190 +9052,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="139"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115">
+      <c r="E2" s="147"/>
+      <c r="F2" s="146">
         <v>56</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="147"/>
+      <c r="H2" s="129">
         <v>45810</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="133"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="139"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="134"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="108"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="103"/>
+      <c r="A4" s="139"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="134"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="123" t="s">
+      <c r="B5" s="151"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="124"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="155"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="125"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="156"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="157"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="159"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="108"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="129"/>
+      <c r="A8" s="139"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="160"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="108"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="129"/>
+      <c r="A9" s="139"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="160"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="129"/>
+      <c r="A10" s="139"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="160"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="129"/>
+      <c r="A11" s="139"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="160"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="108"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="129"/>
+      <c r="A12" s="139"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="160"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="108"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="129"/>
+      <c r="A13" s="139"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="160"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="122" t="s">
+      <c r="A14" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="125"/>
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="156"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="130" t="s">
+      <c r="B15" s="80"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -8418,11 +9244,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="122" t="s">
+      <c r="A16" s="153" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="81"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -8435,18 +9261,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="131" t="s">
+      <c r="H16" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="125"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="156"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="121">
+      <c r="A17" s="152">
         <v>1</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="81"/>
       <c r="D17" s="16" t="s">
         <v>69</v>
       </c>
@@ -8459,16 +9285,16 @@
       <c r="G17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="130"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="125"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="156"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="121">
+      <c r="A18" s="152">
         <v>2</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="81"/>
       <c r="D18" s="16" t="s">
         <v>75</v>
       </c>
@@ -8481,16 +9307,16 @@
       <c r="G18" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="130"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="125"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="156"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="121">
+      <c r="A19" s="152">
         <v>3</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="81"/>
       <c r="D19" s="16" t="s">
         <v>76</v>
       </c>
@@ -8503,16 +9329,16 @@
       <c r="G19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="130"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="125"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="156"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="121">
+      <c r="A20" s="152">
         <v>4</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="16" t="s">
         <v>77</v>
       </c>
@@ -8525,16 +9351,16 @@
       <c r="G20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="130"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="125"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="156"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="121">
+      <c r="A21" s="152">
         <v>5</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="16" t="s">
         <v>78</v>
       </c>
@@ -8547,16 +9373,16 @@
       <c r="G21" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="130"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="125"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="156"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="121">
+      <c r="A22" s="152">
         <v>6</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="81"/>
       <c r="D22" s="16" t="s">
         <v>71</v>
       </c>
@@ -8569,16 +9395,16 @@
       <c r="G22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="130"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="125"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="156"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="121">
+      <c r="A23" s="152">
         <v>7</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="81"/>
       <c r="D23" s="18" t="s">
         <v>71</v>
       </c>
@@ -8591,9 +9417,9 @@
       <c r="G23" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="132"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="H23" s="163"/>
+      <c r="I23" s="164"/>
+      <c r="J23" s="165"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9624,190 +10450,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="173" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="113" t="s">
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="113" t="s">
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="113" t="s">
+      <c r="P1" s="145"/>
+      <c r="Q1" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="114"/>
-      <c r="S1" s="113" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="124"/>
+      <c r="T1" s="155"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="115" t="s">
+      <c r="A2" s="139"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="115" t="s">
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="140">
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="171">
         <v>45821</v>
       </c>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="115" t="s">
+      <c r="P2" s="147"/>
+      <c r="Q2" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="116"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="128"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="159"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="129"/>
+      <c r="A3" s="139"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="148"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="148"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="148"/>
+      <c r="R3" s="140"/>
+      <c r="S3" s="148"/>
+      <c r="T3" s="160"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="141"/>
+      <c r="A4" s="141"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="142"/>
+      <c r="I4" s="142"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="142"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="149"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="149"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="149"/>
+      <c r="T4" s="172"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="143" t="s">
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="174" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
-      <c r="M5" s="120"/>
-      <c r="N5" s="120"/>
-      <c r="O5" s="120"/>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="124"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
+      <c r="L5" s="151"/>
+      <c r="M5" s="151"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="151"/>
+      <c r="P5" s="151"/>
+      <c r="Q5" s="151"/>
+      <c r="R5" s="151"/>
+      <c r="S5" s="151"/>
+      <c r="T5" s="155"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="130" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="161" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="125"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="156"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="122" t="s">
+      <c r="A7" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="130" t="s">
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="161" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="125"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80"/>
+      <c r="T7" s="156"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -10006,37 +10832,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="149" t="s">
+      <c r="B15" s="81"/>
+      <c r="C15" s="180" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="131" t="s">
+      <c r="D15" s="81"/>
+      <c r="E15" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="131" t="s">
+      <c r="F15" s="81"/>
+      <c r="G15" s="162" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="131" t="s">
+      <c r="H15" s="80"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="131" t="s">
+      <c r="K15" s="81"/>
+      <c r="L15" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="49"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="131" t="s">
+      <c r="M15" s="80"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="50"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="81"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -10048,40 +10874,46 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="144">
+      <c r="A16" s="175">
         <v>1</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="145" t="s">
+      <c r="B16" s="81"/>
+      <c r="C16" s="176" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="145" t="s">
+      <c r="D16" s="81"/>
+      <c r="E16" s="176" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="135" t="s">
+      <c r="F16" s="81"/>
+      <c r="G16" s="166" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="135" t="s">
+      <c r="H16" s="80"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="166" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="50"/>
-      <c r="L16" s="146" t="s">
+      <c r="K16" s="81"/>
+      <c r="L16" s="177" t="s">
         <v>92</v>
       </c>
-      <c r="M16" s="147"/>
-      <c r="N16" s="148"/>
-      <c r="O16" s="138" t="s">
+      <c r="M16" s="178"/>
+      <c r="N16" s="179"/>
+      <c r="O16" s="169" t="s">
         <v>93</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="33"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="61">
+        <v>45825</v>
+      </c>
+      <c r="S16" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="T16" s="33" t="s">
+        <v>128</v>
+      </c>
       <c r="U16" s="34"/>
       <c r="V16" s="34"/>
       <c r="W16" s="34"/>
@@ -10090,40 +10922,46 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="62.25" customHeight="1">
-      <c r="A17" s="144">
+      <c r="A17" s="175">
         <v>2</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="145" t="s">
+      <c r="B17" s="81"/>
+      <c r="C17" s="176" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="145" t="s">
+      <c r="D17" s="81"/>
+      <c r="E17" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="135" t="s">
+      <c r="F17" s="81"/>
+      <c r="G17" s="166" t="s">
         <v>96</v>
       </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="135" t="s">
+      <c r="H17" s="80"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="166" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="50"/>
-      <c r="L17" s="138" t="s">
+      <c r="K17" s="81"/>
+      <c r="L17" s="169" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="138" t="s">
+      <c r="M17" s="80"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="169" t="s">
         <v>99</v>
       </c>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="33"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="61">
+        <v>45825</v>
+      </c>
+      <c r="S17" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="T17" s="33" t="s">
+        <v>128</v>
+      </c>
       <c r="U17" s="34"/>
       <c r="V17" s="34"/>
       <c r="W17" s="34"/>
@@ -10132,40 +10970,46 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="54" customHeight="1">
-      <c r="A18" s="144">
+      <c r="A18" s="175">
         <v>3</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="145" t="s">
+      <c r="B18" s="81"/>
+      <c r="C18" s="176" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="145" t="s">
+      <c r="D18" s="81"/>
+      <c r="E18" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="135" t="s">
+      <c r="F18" s="81"/>
+      <c r="G18" s="166" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="135" t="s">
+      <c r="H18" s="80"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="166" t="s">
         <v>101</v>
       </c>
-      <c r="K18" s="50"/>
-      <c r="L18" s="138" t="s">
+      <c r="K18" s="81"/>
+      <c r="L18" s="169" t="s">
         <v>102</v>
       </c>
-      <c r="M18" s="49"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="138" t="s">
+      <c r="M18" s="80"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="169" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="33"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="61">
+        <v>45825</v>
+      </c>
+      <c r="S18" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="T18" s="33" t="s">
+        <v>128</v>
+      </c>
       <c r="U18" s="34"/>
       <c r="V18" s="34"/>
       <c r="W18" s="34"/>
@@ -10174,40 +11018,46 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A19" s="144">
+      <c r="A19" s="175">
         <v>4</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="145" t="s">
+      <c r="B19" s="81"/>
+      <c r="C19" s="176" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="145" t="s">
+      <c r="D19" s="81"/>
+      <c r="E19" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="135" t="s">
+      <c r="F19" s="81"/>
+      <c r="G19" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="135" t="s">
+      <c r="H19" s="80"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="166" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="50"/>
-      <c r="L19" s="138" t="s">
+      <c r="K19" s="81"/>
+      <c r="L19" s="169" t="s">
         <v>102</v>
       </c>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="138" t="s">
+      <c r="M19" s="80"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="169" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="33"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="61">
+        <v>45825</v>
+      </c>
+      <c r="S19" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="T19" s="33" t="s">
+        <v>128</v>
+      </c>
       <c r="U19" s="34"/>
       <c r="V19" s="34"/>
       <c r="W19" s="34"/>
@@ -10216,40 +11066,26 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="57" customHeight="1">
-      <c r="A20" s="152">
-        <v>7</v>
-      </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="153" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="153" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="58"/>
-      <c r="G20" s="154" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="154" t="s">
-        <v>110</v>
-      </c>
-      <c r="K20" s="58"/>
-      <c r="L20" s="155" t="s">
-        <v>112</v>
-      </c>
-      <c r="M20" s="156"/>
-      <c r="N20" s="156"/>
-      <c r="O20" s="138" t="s">
-        <v>111</v>
-      </c>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="157"/>
-      <c r="S20" s="157"/>
-      <c r="T20" s="158"/>
+      <c r="A20" s="175"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="166"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="166"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="169"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="169"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="33"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -10258,23 +11094,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="144"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="135"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="138"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="138"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="50"/>
+      <c r="A21" s="175"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="166"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="81"/>
+      <c r="O21" s="169"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="81"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -10286,23 +11122,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="144"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="138"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="50"/>
+      <c r="A22" s="175"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="166"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="166"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="169"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="81"/>
+      <c r="O22" s="169"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="81"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -10314,23 +11150,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="144"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="138"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="138"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="50"/>
+      <c r="A23" s="175"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="166"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="166"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="169"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="169"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="81"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -10342,23 +11178,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="144"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="145"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="145"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="135"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="138"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="138"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="176"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="166"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="166"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="169"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="169"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="81"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -10370,23 +11206,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="144"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="145"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="135"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="138"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="138"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
+      <c r="A25" s="175"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="166"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="169"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="169"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="81"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -10398,23 +11234,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="144"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="145"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="135"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="135"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="138"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="138"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="50"/>
+      <c r="A26" s="175"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="166"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="166"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="169"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="169"/>
+      <c r="P26" s="80"/>
+      <c r="Q26" s="81"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -10426,23 +11262,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="144"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="145"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="138"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="138"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
+      <c r="A27" s="175"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="166"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="166"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="169"/>
+      <c r="M27" s="80"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="169"/>
+      <c r="P27" s="80"/>
+      <c r="Q27" s="81"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -10454,23 +11290,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="144"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="145"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="135"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="135"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="138"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
+      <c r="A28" s="175"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="166"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="166"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="169"/>
+      <c r="M28" s="80"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="169"/>
+      <c r="P28" s="80"/>
+      <c r="Q28" s="81"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -10482,23 +11318,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="144"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="145"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="145"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="135"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="138"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="138"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
+      <c r="A29" s="175"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="166"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="166"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="169"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="169"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="81"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -10510,23 +11346,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="144"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="145"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="135"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="138"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="138"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
+      <c r="A30" s="175"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="166"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="166"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="169"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="169"/>
+      <c r="P30" s="80"/>
+      <c r="Q30" s="81"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -10538,23 +11374,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="150"/>
-      <c r="B31" s="137"/>
-      <c r="C31" s="151"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="136"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="139"/>
-      <c r="M31" s="133"/>
-      <c r="N31" s="137"/>
-      <c r="O31" s="139"/>
-      <c r="P31" s="133"/>
-      <c r="Q31" s="137"/>
+      <c r="A31" s="181"/>
+      <c r="B31" s="168"/>
+      <c r="C31" s="182"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="167"/>
+      <c r="H31" s="164"/>
+      <c r="I31" s="168"/>
+      <c r="J31" s="167"/>
+      <c r="K31" s="168"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="164"/>
+      <c r="N31" s="168"/>
+      <c r="O31" s="170"/>
+      <c r="P31" s="164"/>
+      <c r="Q31" s="168"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -11690,10 +12526,2881 @@
     <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
-  <hyperlinks>
-    <hyperlink ref="L20" r:id="rId1" xr:uid="{29959F9C-D2C5-4624-BB77-C32F70D08F79}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20100C0A-C86A-4465-B785-9157351E8AB1}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="49" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="60" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="49" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="60" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="49" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="49" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="49"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="192" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="192"/>
+      <c r="C1" s="193" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="194"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="196" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="196" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="196" t="s">
+        <v>112</v>
+      </c>
+      <c r="S1" s="198"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="192"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="194"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="196" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="198"/>
+      <c r="N2" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="O2" s="199">
+        <v>45818</v>
+      </c>
+      <c r="P2" s="200"/>
+      <c r="Q2" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="R2" s="201" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="202"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="183" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="185"/>
+      <c r="H4" s="183" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="185"/>
+      <c r="N4" s="183" t="s">
+        <v>121</v>
+      </c>
+      <c r="O4" s="184"/>
+      <c r="P4" s="185"/>
+      <c r="Q4" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="R4" s="183" t="s">
+        <v>123</v>
+      </c>
+      <c r="S4" s="185"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="55">
+        <v>1</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="186" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="186" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="186"/>
+      <c r="N5" s="187" t="s">
+        <v>127</v>
+      </c>
+      <c r="O5" s="188"/>
+      <c r="P5" s="189"/>
+      <c r="Q5" s="57">
+        <v>45824</v>
+      </c>
+      <c r="R5" s="190"/>
+      <c r="S5" s="191"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="203"/>
+      <c r="H6" s="203"/>
+      <c r="I6" s="203"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="208"/>
+      <c r="O6" s="209"/>
+      <c r="P6" s="210"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="207"/>
+      <c r="S6" s="207"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="203"/>
+      <c r="F7" s="203"/>
+      <c r="G7" s="203"/>
+      <c r="H7" s="203"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="203"/>
+      <c r="K7" s="203"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="203"/>
+      <c r="N7" s="204"/>
+      <c r="O7" s="205"/>
+      <c r="P7" s="206"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="207"/>
+      <c r="S7" s="207"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="203"/>
+      <c r="H8" s="203"/>
+      <c r="I8" s="203"/>
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="203"/>
+      <c r="N8" s="204"/>
+      <c r="O8" s="205"/>
+      <c r="P8" s="206"/>
+      <c r="Q8" s="59"/>
+      <c r="R8" s="207"/>
+      <c r="S8" s="207"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="203"/>
+      <c r="H9" s="203"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="203"/>
+      <c r="K9" s="203"/>
+      <c r="L9" s="203"/>
+      <c r="M9" s="203"/>
+      <c r="N9" s="204"/>
+      <c r="O9" s="205"/>
+      <c r="P9" s="206"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="207"/>
+      <c r="S9" s="207"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="211"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
+      <c r="L10" s="212"/>
+      <c r="M10" s="213"/>
+      <c r="N10" s="204"/>
+      <c r="O10" s="205"/>
+      <c r="P10" s="206"/>
+      <c r="Q10" s="59"/>
+      <c r="R10" s="207"/>
+      <c r="S10" s="207"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="203"/>
+      <c r="H11" s="211"/>
+      <c r="I11" s="212"/>
+      <c r="J11" s="212"/>
+      <c r="K11" s="212"/>
+      <c r="L11" s="212"/>
+      <c r="M11" s="213"/>
+      <c r="N11" s="204"/>
+      <c r="O11" s="205"/>
+      <c r="P11" s="206"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="207"/>
+      <c r="S11" s="207"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="211"/>
+      <c r="I12" s="212"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="212"/>
+      <c r="L12" s="212"/>
+      <c r="M12" s="213"/>
+      <c r="N12" s="204"/>
+      <c r="O12" s="205"/>
+      <c r="P12" s="206"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="207"/>
+      <c r="S12" s="207"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="58"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="212"/>
+      <c r="J13" s="212"/>
+      <c r="K13" s="212"/>
+      <c r="L13" s="212"/>
+      <c r="M13" s="213"/>
+      <c r="N13" s="204"/>
+      <c r="O13" s="205"/>
+      <c r="P13" s="206"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="207"/>
+      <c r="S13" s="207"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="211"/>
+      <c r="I14" s="212"/>
+      <c r="J14" s="212"/>
+      <c r="K14" s="212"/>
+      <c r="L14" s="212"/>
+      <c r="M14" s="213"/>
+      <c r="N14" s="204"/>
+      <c r="O14" s="205"/>
+      <c r="P14" s="206"/>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="207"/>
+      <c r="S14" s="207"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="58"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="212"/>
+      <c r="J15" s="212"/>
+      <c r="K15" s="212"/>
+      <c r="L15" s="212"/>
+      <c r="M15" s="213"/>
+      <c r="N15" s="204"/>
+      <c r="O15" s="205"/>
+      <c r="P15" s="206"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="207"/>
+      <c r="S15" s="207"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="211"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
+      <c r="L16" s="212"/>
+      <c r="M16" s="213"/>
+      <c r="N16" s="204"/>
+      <c r="O16" s="205"/>
+      <c r="P16" s="206"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="207"/>
+      <c r="S16" s="207"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="203"/>
+      <c r="H17" s="211"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
+      <c r="L17" s="212"/>
+      <c r="M17" s="213"/>
+      <c r="N17" s="204"/>
+      <c r="O17" s="205"/>
+      <c r="P17" s="206"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="207"/>
+      <c r="S17" s="207"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="58"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="211"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
+      <c r="L18" s="212"/>
+      <c r="M18" s="213"/>
+      <c r="N18" s="204"/>
+      <c r="O18" s="205"/>
+      <c r="P18" s="206"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="207"/>
+      <c r="S18" s="207"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="203"/>
+      <c r="H19" s="211"/>
+      <c r="I19" s="212"/>
+      <c r="J19" s="212"/>
+      <c r="K19" s="212"/>
+      <c r="L19" s="212"/>
+      <c r="M19" s="213"/>
+      <c r="N19" s="204"/>
+      <c r="O19" s="205"/>
+      <c r="P19" s="206"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="207"/>
+      <c r="S19" s="207"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="203"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="212"/>
+      <c r="J20" s="212"/>
+      <c r="K20" s="212"/>
+      <c r="L20" s="212"/>
+      <c r="M20" s="213"/>
+      <c r="N20" s="204"/>
+      <c r="O20" s="205"/>
+      <c r="P20" s="206"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="207"/>
+      <c r="S20" s="207"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="203"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212"/>
+      <c r="L21" s="212"/>
+      <c r="M21" s="213"/>
+      <c r="N21" s="204"/>
+      <c r="O21" s="205"/>
+      <c r="P21" s="206"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="207"/>
+      <c r="S21" s="207"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="211"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="212"/>
+      <c r="K22" s="212"/>
+      <c r="L22" s="212"/>
+      <c r="M22" s="213"/>
+      <c r="N22" s="204"/>
+      <c r="O22" s="205"/>
+      <c r="P22" s="206"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="207"/>
+      <c r="S22" s="207"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="203"/>
+      <c r="H23" s="211"/>
+      <c r="I23" s="212"/>
+      <c r="J23" s="212"/>
+      <c r="K23" s="212"/>
+      <c r="L23" s="212"/>
+      <c r="M23" s="213"/>
+      <c r="N23" s="204"/>
+      <c r="O23" s="205"/>
+      <c r="P23" s="206"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="207"/>
+      <c r="S23" s="207"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="203"/>
+      <c r="H24" s="211"/>
+      <c r="I24" s="212"/>
+      <c r="J24" s="212"/>
+      <c r="K24" s="212"/>
+      <c r="L24" s="212"/>
+      <c r="M24" s="213"/>
+      <c r="N24" s="204"/>
+      <c r="O24" s="205"/>
+      <c r="P24" s="206"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="207"/>
+      <c r="S24" s="207"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="58"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="203"/>
+      <c r="H25" s="211"/>
+      <c r="I25" s="212"/>
+      <c r="J25" s="212"/>
+      <c r="K25" s="212"/>
+      <c r="L25" s="212"/>
+      <c r="M25" s="213"/>
+      <c r="N25" s="204"/>
+      <c r="O25" s="205"/>
+      <c r="P25" s="206"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="207"/>
+      <c r="S25" s="207"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="58"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
+      <c r="M26" s="213"/>
+      <c r="N26" s="204"/>
+      <c r="O26" s="205"/>
+      <c r="P26" s="206"/>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="207"/>
+      <c r="S26" s="207"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="58"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="203"/>
+      <c r="H27" s="211"/>
+      <c r="I27" s="212"/>
+      <c r="J27" s="212"/>
+      <c r="K27" s="212"/>
+      <c r="L27" s="212"/>
+      <c r="M27" s="213"/>
+      <c r="N27" s="204"/>
+      <c r="O27" s="205"/>
+      <c r="P27" s="206"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="207"/>
+      <c r="S27" s="207"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="58"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="203"/>
+      <c r="H28" s="211"/>
+      <c r="I28" s="212"/>
+      <c r="J28" s="212"/>
+      <c r="K28" s="212"/>
+      <c r="L28" s="212"/>
+      <c r="M28" s="213"/>
+      <c r="N28" s="204"/>
+      <c r="O28" s="205"/>
+      <c r="P28" s="206"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="207"/>
+      <c r="S28" s="207"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="58"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="211"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="212"/>
+      <c r="L29" s="212"/>
+      <c r="M29" s="213"/>
+      <c r="N29" s="204"/>
+      <c r="O29" s="205"/>
+      <c r="P29" s="206"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="207"/>
+      <c r="S29" s="207"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="58"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="211"/>
+      <c r="I30" s="212"/>
+      <c r="J30" s="212"/>
+      <c r="K30" s="212"/>
+      <c r="L30" s="212"/>
+      <c r="M30" s="213"/>
+      <c r="N30" s="204"/>
+      <c r="O30" s="205"/>
+      <c r="P30" s="206"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="207"/>
+      <c r="S30" s="207"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="58"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="203"/>
+      <c r="H31" s="211"/>
+      <c r="I31" s="212"/>
+      <c r="J31" s="212"/>
+      <c r="K31" s="212"/>
+      <c r="L31" s="212"/>
+      <c r="M31" s="213"/>
+      <c r="N31" s="204"/>
+      <c r="O31" s="205"/>
+      <c r="P31" s="206"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="207"/>
+      <c r="S31" s="207"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="58"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="211"/>
+      <c r="I32" s="212"/>
+      <c r="J32" s="212"/>
+      <c r="K32" s="212"/>
+      <c r="L32" s="212"/>
+      <c r="M32" s="213"/>
+      <c r="N32" s="204"/>
+      <c r="O32" s="205"/>
+      <c r="P32" s="206"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="207"/>
+      <c r="S32" s="207"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="58"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="211"/>
+      <c r="I33" s="212"/>
+      <c r="J33" s="212"/>
+      <c r="K33" s="212"/>
+      <c r="L33" s="212"/>
+      <c r="M33" s="213"/>
+      <c r="N33" s="204"/>
+      <c r="O33" s="205"/>
+      <c r="P33" s="206"/>
+      <c r="Q33" s="58"/>
+      <c r="R33" s="207"/>
+      <c r="S33" s="207"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="211"/>
+      <c r="I34" s="212"/>
+      <c r="J34" s="212"/>
+      <c r="K34" s="212"/>
+      <c r="L34" s="212"/>
+      <c r="M34" s="213"/>
+      <c r="N34" s="204"/>
+      <c r="O34" s="205"/>
+      <c r="P34" s="206"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="207"/>
+      <c r="S34" s="207"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="211"/>
+      <c r="I35" s="212"/>
+      <c r="J35" s="212"/>
+      <c r="K35" s="212"/>
+      <c r="L35" s="212"/>
+      <c r="M35" s="213"/>
+      <c r="N35" s="204"/>
+      <c r="O35" s="205"/>
+      <c r="P35" s="206"/>
+      <c r="Q35" s="58"/>
+      <c r="R35" s="207"/>
+      <c r="S35" s="207"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="203"/>
+      <c r="E36" s="203"/>
+      <c r="F36" s="203"/>
+      <c r="G36" s="203"/>
+      <c r="H36" s="211"/>
+      <c r="I36" s="212"/>
+      <c r="J36" s="212"/>
+      <c r="K36" s="212"/>
+      <c r="L36" s="212"/>
+      <c r="M36" s="213"/>
+      <c r="N36" s="204"/>
+      <c r="O36" s="205"/>
+      <c r="P36" s="206"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="207"/>
+      <c r="S36" s="207"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="211"/>
+      <c r="I37" s="212"/>
+      <c r="J37" s="212"/>
+      <c r="K37" s="212"/>
+      <c r="L37" s="212"/>
+      <c r="M37" s="213"/>
+      <c r="N37" s="204"/>
+      <c r="O37" s="205"/>
+      <c r="P37" s="206"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="207"/>
+      <c r="S37" s="207"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="58"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="203"/>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="203"/>
+      <c r="H38" s="211"/>
+      <c r="I38" s="212"/>
+      <c r="J38" s="212"/>
+      <c r="K38" s="212"/>
+      <c r="L38" s="212"/>
+      <c r="M38" s="213"/>
+      <c r="N38" s="204"/>
+      <c r="O38" s="205"/>
+      <c r="P38" s="206"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="207"/>
+      <c r="S38" s="207"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="58"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="203"/>
+      <c r="F39" s="203"/>
+      <c r="G39" s="203"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="212"/>
+      <c r="J39" s="212"/>
+      <c r="K39" s="212"/>
+      <c r="L39" s="212"/>
+      <c r="M39" s="213"/>
+      <c r="N39" s="204"/>
+      <c r="O39" s="205"/>
+      <c r="P39" s="206"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="207"/>
+      <c r="S39" s="207"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="58"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="211"/>
+      <c r="I40" s="212"/>
+      <c r="J40" s="212"/>
+      <c r="K40" s="212"/>
+      <c r="L40" s="212"/>
+      <c r="M40" s="213"/>
+      <c r="N40" s="204"/>
+      <c r="O40" s="205"/>
+      <c r="P40" s="206"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="207"/>
+      <c r="S40" s="207"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+      <c r="G41" s="203"/>
+      <c r="H41" s="211"/>
+      <c r="I41" s="212"/>
+      <c r="J41" s="212"/>
+      <c r="K41" s="212"/>
+      <c r="L41" s="212"/>
+      <c r="M41" s="213"/>
+      <c r="N41" s="204"/>
+      <c r="O41" s="205"/>
+      <c r="P41" s="206"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="207"/>
+      <c r="S41" s="207"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="58"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="211"/>
+      <c r="I42" s="212"/>
+      <c r="J42" s="212"/>
+      <c r="K42" s="212"/>
+      <c r="L42" s="212"/>
+      <c r="M42" s="213"/>
+      <c r="N42" s="204"/>
+      <c r="O42" s="205"/>
+      <c r="P42" s="206"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="207"/>
+      <c r="S42" s="207"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="58"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="211"/>
+      <c r="I43" s="212"/>
+      <c r="J43" s="212"/>
+      <c r="K43" s="212"/>
+      <c r="L43" s="212"/>
+      <c r="M43" s="213"/>
+      <c r="N43" s="204"/>
+      <c r="O43" s="205"/>
+      <c r="P43" s="206"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="207"/>
+      <c r="S43" s="207"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="58"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="203"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="203"/>
+      <c r="G44" s="203"/>
+      <c r="H44" s="211"/>
+      <c r="I44" s="212"/>
+      <c r="J44" s="212"/>
+      <c r="K44" s="212"/>
+      <c r="L44" s="212"/>
+      <c r="M44" s="213"/>
+      <c r="N44" s="204"/>
+      <c r="O44" s="205"/>
+      <c r="P44" s="206"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="207"/>
+      <c r="S44" s="207"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="203"/>
+      <c r="F45" s="203"/>
+      <c r="G45" s="203"/>
+      <c r="H45" s="211"/>
+      <c r="I45" s="212"/>
+      <c r="J45" s="212"/>
+      <c r="K45" s="212"/>
+      <c r="L45" s="212"/>
+      <c r="M45" s="213"/>
+      <c r="N45" s="204"/>
+      <c r="O45" s="205"/>
+      <c r="P45" s="206"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="207"/>
+      <c r="S45" s="207"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="58"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="203"/>
+      <c r="F46" s="203"/>
+      <c r="G46" s="203"/>
+      <c r="H46" s="211"/>
+      <c r="I46" s="212"/>
+      <c r="J46" s="212"/>
+      <c r="K46" s="212"/>
+      <c r="L46" s="212"/>
+      <c r="M46" s="213"/>
+      <c r="N46" s="204"/>
+      <c r="O46" s="205"/>
+      <c r="P46" s="206"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="207"/>
+      <c r="S46" s="207"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="58"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="203"/>
+      <c r="E47" s="203"/>
+      <c r="F47" s="203"/>
+      <c r="G47" s="203"/>
+      <c r="H47" s="211"/>
+      <c r="I47" s="212"/>
+      <c r="J47" s="212"/>
+      <c r="K47" s="212"/>
+      <c r="L47" s="212"/>
+      <c r="M47" s="213"/>
+      <c r="N47" s="204"/>
+      <c r="O47" s="205"/>
+      <c r="P47" s="206"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="207"/>
+      <c r="S47" s="207"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="58"/>
+      <c r="B48" s="58"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="203"/>
+      <c r="E48" s="203"/>
+      <c r="F48" s="203"/>
+      <c r="G48" s="203"/>
+      <c r="H48" s="211"/>
+      <c r="I48" s="212"/>
+      <c r="J48" s="212"/>
+      <c r="K48" s="212"/>
+      <c r="L48" s="212"/>
+      <c r="M48" s="213"/>
+      <c r="N48" s="204"/>
+      <c r="O48" s="205"/>
+      <c r="P48" s="206"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="207"/>
+      <c r="S48" s="207"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="58"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="203"/>
+      <c r="D49" s="203"/>
+      <c r="E49" s="203"/>
+      <c r="F49" s="203"/>
+      <c r="G49" s="203"/>
+      <c r="H49" s="211"/>
+      <c r="I49" s="212"/>
+      <c r="J49" s="212"/>
+      <c r="K49" s="212"/>
+      <c r="L49" s="212"/>
+      <c r="M49" s="213"/>
+      <c r="N49" s="204"/>
+      <c r="O49" s="205"/>
+      <c r="P49" s="206"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="207"/>
+      <c r="S49" s="207"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="58"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="203"/>
+      <c r="D50" s="203"/>
+      <c r="E50" s="203"/>
+      <c r="F50" s="203"/>
+      <c r="G50" s="203"/>
+      <c r="H50" s="211"/>
+      <c r="I50" s="212"/>
+      <c r="J50" s="212"/>
+      <c r="K50" s="212"/>
+      <c r="L50" s="212"/>
+      <c r="M50" s="213"/>
+      <c r="N50" s="204"/>
+      <c r="O50" s="205"/>
+      <c r="P50" s="206"/>
+      <c r="Q50" s="58"/>
+      <c r="R50" s="207"/>
+      <c r="S50" s="207"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="58"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="203"/>
+      <c r="D51" s="203"/>
+      <c r="E51" s="203"/>
+      <c r="F51" s="203"/>
+      <c r="G51" s="203"/>
+      <c r="H51" s="211"/>
+      <c r="I51" s="212"/>
+      <c r="J51" s="212"/>
+      <c r="K51" s="212"/>
+      <c r="L51" s="212"/>
+      <c r="M51" s="213"/>
+      <c r="N51" s="204"/>
+      <c r="O51" s="205"/>
+      <c r="P51" s="206"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="207"/>
+      <c r="S51" s="207"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="58"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="203"/>
+      <c r="D52" s="203"/>
+      <c r="E52" s="203"/>
+      <c r="F52" s="203"/>
+      <c r="G52" s="203"/>
+      <c r="H52" s="211"/>
+      <c r="I52" s="212"/>
+      <c r="J52" s="212"/>
+      <c r="K52" s="212"/>
+      <c r="L52" s="212"/>
+      <c r="M52" s="213"/>
+      <c r="N52" s="204"/>
+      <c r="O52" s="205"/>
+      <c r="P52" s="206"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="207"/>
+      <c r="S52" s="207"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B200AB0-1F40-44FD-BC67-C6A716D65C8A}">
+  <dimension ref="A1:BA115"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="24.95" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="3" style="67" customWidth="1"/>
+    <col min="3" max="3" width="3" style="68" customWidth="1"/>
+    <col min="4" max="5" width="3" style="67" customWidth="1"/>
+    <col min="6" max="6" width="3" style="68" customWidth="1"/>
+    <col min="7" max="16384" width="3" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:53" ht="30" customHeight="1">
+      <c r="A1" s="62"/>
+      <c r="B1" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="64"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="217" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP1" s="217"/>
+      <c r="AQ1" s="217"/>
+      <c r="AR1" s="217"/>
+      <c r="AS1" s="217"/>
+      <c r="AT1" s="218">
+        <v>45818</v>
+      </c>
+      <c r="AU1" s="219"/>
+      <c r="AV1" s="219"/>
+      <c r="AW1" s="219"/>
+      <c r="AX1" s="219"/>
+      <c r="AY1" s="219"/>
+      <c r="AZ1" s="219"/>
+      <c r="BA1" s="219"/>
+    </row>
+    <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="4" spans="1:53" ht="18" customHeight="1">
+      <c r="A4" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="69"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="69"/>
+      <c r="Z4" s="69"/>
+      <c r="AA4" s="69"/>
+      <c r="AB4" s="69"/>
+      <c r="AC4" s="69"/>
+      <c r="AD4" s="69"/>
+      <c r="AE4" s="69"/>
+      <c r="AF4" s="69"/>
+      <c r="AG4" s="69"/>
+      <c r="AH4" s="69"/>
+      <c r="AI4" s="69"/>
+      <c r="AJ4" s="69"/>
+      <c r="AK4" s="69"/>
+    </row>
+    <row r="5" spans="1:53" ht="24.95" customHeight="1">
+      <c r="A5" s="214" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="215"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="220" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="221"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="221"/>
+      <c r="K5" s="221"/>
+      <c r="L5" s="221"/>
+      <c r="M5" s="221"/>
+      <c r="N5" s="221"/>
+      <c r="O5" s="221"/>
+      <c r="P5" s="221"/>
+      <c r="Q5" s="221"/>
+      <c r="R5" s="221"/>
+      <c r="S5" s="222"/>
+    </row>
+    <row r="6" spans="1:53" ht="24.95" customHeight="1">
+      <c r="A6" s="214" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="215"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="223">
+        <v>1</v>
+      </c>
+      <c r="H6" s="221"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="221"/>
+      <c r="O6" s="221"/>
+      <c r="P6" s="221"/>
+      <c r="Q6" s="221"/>
+      <c r="R6" s="221"/>
+      <c r="S6" s="222"/>
+    </row>
+    <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
+    <row r="8" spans="1:53" ht="18" customHeight="1">
+      <c r="A8" s="69" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" ht="18" customHeight="1">
+      <c r="A9" s="214" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="215"/>
+      <c r="C9" s="215"/>
+      <c r="D9" s="215"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="215"/>
+      <c r="H9" s="215"/>
+      <c r="I9" s="215"/>
+      <c r="J9" s="215"/>
+      <c r="K9" s="215"/>
+      <c r="L9" s="215"/>
+      <c r="M9" s="215"/>
+      <c r="N9" s="215"/>
+      <c r="O9" s="215"/>
+      <c r="P9" s="215"/>
+      <c r="Q9" s="215"/>
+      <c r="R9" s="215"/>
+      <c r="S9" s="215"/>
+      <c r="T9" s="215"/>
+      <c r="U9" s="215"/>
+      <c r="V9" s="215"/>
+      <c r="W9" s="215"/>
+      <c r="X9" s="215"/>
+      <c r="Y9" s="215"/>
+      <c r="Z9" s="215"/>
+      <c r="AA9" s="215"/>
+      <c r="AB9" s="215"/>
+      <c r="AC9" s="215"/>
+      <c r="AD9" s="215"/>
+      <c r="AE9" s="215"/>
+      <c r="AF9" s="215"/>
+      <c r="AG9" s="215"/>
+      <c r="AH9" s="215"/>
+      <c r="AI9" s="215"/>
+      <c r="AJ9" s="215"/>
+      <c r="AK9" s="215"/>
+      <c r="AL9" s="215"/>
+      <c r="AM9" s="215"/>
+      <c r="AN9" s="215"/>
+      <c r="AO9" s="215"/>
+      <c r="AP9" s="215"/>
+      <c r="AQ9" s="215"/>
+      <c r="AR9" s="215"/>
+      <c r="AS9" s="215"/>
+      <c r="AT9" s="215"/>
+      <c r="AU9" s="215"/>
+      <c r="AV9" s="215"/>
+      <c r="AW9" s="215"/>
+      <c r="AX9" s="215"/>
+      <c r="AY9" s="215"/>
+      <c r="AZ9" s="215"/>
+      <c r="BA9" s="216"/>
+    </row>
+    <row r="10" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="72"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="72"/>
+      <c r="AB10" s="72"/>
+      <c r="AC10" s="72"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="72"/>
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="72"/>
+      <c r="BA10" s="73"/>
+    </row>
+    <row r="11" spans="1:53" ht="21.75" customHeight="1">
+      <c r="A11" s="71"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="72"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="72"/>
+      <c r="Y11" s="72"/>
+      <c r="Z11" s="72"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="72"/>
+      <c r="AC11" s="72"/>
+      <c r="AD11" s="72"/>
+      <c r="AE11" s="72"/>
+      <c r="AF11" s="72"/>
+      <c r="AG11" s="72"/>
+      <c r="AH11" s="72"/>
+      <c r="AI11" s="72"/>
+      <c r="AJ11" s="72"/>
+      <c r="AK11" s="72"/>
+      <c r="BA11" s="73"/>
+    </row>
+    <row r="12" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A12" s="71"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="72"/>
+      <c r="Y12" s="72"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="72"/>
+      <c r="AB12" s="72"/>
+      <c r="AC12" s="72"/>
+      <c r="AD12" s="72"/>
+      <c r="AE12" s="72"/>
+      <c r="AF12" s="72"/>
+      <c r="AG12" s="72"/>
+      <c r="AH12" s="72"/>
+      <c r="AI12" s="72"/>
+      <c r="AJ12" s="72"/>
+      <c r="AK12" s="72"/>
+      <c r="BA12" s="73"/>
+    </row>
+    <row r="13" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="72"/>
+      <c r="U13" s="72"/>
+      <c r="V13" s="72"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="72"/>
+      <c r="Y13" s="72"/>
+      <c r="Z13" s="72"/>
+      <c r="AA13" s="72"/>
+      <c r="AB13" s="72"/>
+      <c r="AC13" s="72"/>
+      <c r="AD13" s="72"/>
+      <c r="AE13" s="72"/>
+      <c r="AF13" s="72"/>
+      <c r="AG13" s="72"/>
+      <c r="AH13" s="72"/>
+      <c r="AI13" s="72"/>
+      <c r="AJ13" s="72"/>
+      <c r="AK13" s="72"/>
+      <c r="BA13" s="73"/>
+    </row>
+    <row r="14" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A14" s="71"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
+      <c r="AB14" s="72"/>
+      <c r="AC14" s="72"/>
+      <c r="AD14" s="72"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
+      <c r="AJ14" s="72"/>
+      <c r="AK14" s="72"/>
+      <c r="BA14" s="73"/>
+    </row>
+    <row r="15" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A15" s="71"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72"/>
+      <c r="X15" s="72"/>
+      <c r="Y15" s="72"/>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="72"/>
+      <c r="AB15" s="72"/>
+      <c r="AC15" s="72"/>
+      <c r="AD15" s="72"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="72"/>
+      <c r="AG15" s="72"/>
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
+      <c r="AJ15" s="72"/>
+      <c r="AK15" s="72"/>
+      <c r="BA15" s="73"/>
+    </row>
+    <row r="16" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A16" s="71"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="72"/>
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="72"/>
+      <c r="AD16" s="72"/>
+      <c r="AE16" s="72"/>
+      <c r="AF16" s="72"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="72"/>
+      <c r="BA16" s="73"/>
+    </row>
+    <row r="17" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A17" s="71"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="72"/>
+      <c r="X17" s="72"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="72"/>
+      <c r="AB17" s="72"/>
+      <c r="AC17" s="72"/>
+      <c r="AD17" s="72"/>
+      <c r="AE17" s="72"/>
+      <c r="AF17" s="72"/>
+      <c r="AG17" s="72"/>
+      <c r="AH17" s="72"/>
+      <c r="AI17" s="72"/>
+      <c r="AJ17" s="72"/>
+      <c r="AK17" s="72"/>
+      <c r="BA17" s="73"/>
+    </row>
+    <row r="18" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A18" s="71"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="72"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="72"/>
+      <c r="AA18" s="72"/>
+      <c r="AB18" s="72"/>
+      <c r="AC18" s="72"/>
+      <c r="AD18" s="72"/>
+      <c r="AE18" s="72"/>
+      <c r="AF18" s="72"/>
+      <c r="AG18" s="72"/>
+      <c r="AH18" s="72"/>
+      <c r="AI18" s="72"/>
+      <c r="AJ18" s="72"/>
+      <c r="AK18" s="72"/>
+      <c r="BA18" s="73"/>
+    </row>
+    <row r="19" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A19" s="71"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="72"/>
+      <c r="V19" s="72"/>
+      <c r="W19" s="72"/>
+      <c r="X19" s="72"/>
+      <c r="Y19" s="72"/>
+      <c r="Z19" s="72"/>
+      <c r="AA19" s="72"/>
+      <c r="AB19" s="72"/>
+      <c r="AC19" s="72"/>
+      <c r="AD19" s="72"/>
+      <c r="AE19" s="72"/>
+      <c r="AF19" s="72"/>
+      <c r="AG19" s="72"/>
+      <c r="AH19" s="72"/>
+      <c r="AI19" s="72"/>
+      <c r="AJ19" s="72"/>
+      <c r="AK19" s="72"/>
+      <c r="BA19" s="73"/>
+    </row>
+    <row r="20" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A20" s="71"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="72"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="72"/>
+      <c r="X20" s="72"/>
+      <c r="Y20" s="72"/>
+      <c r="Z20" s="72"/>
+      <c r="AA20" s="72"/>
+      <c r="AB20" s="72"/>
+      <c r="AC20" s="72"/>
+      <c r="AD20" s="72"/>
+      <c r="AE20" s="72"/>
+      <c r="AF20" s="72"/>
+      <c r="AG20" s="72"/>
+      <c r="AH20" s="72"/>
+      <c r="AI20" s="72"/>
+      <c r="AJ20" s="72"/>
+      <c r="AK20" s="72"/>
+      <c r="BA20" s="73"/>
+    </row>
+    <row r="21" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A21" s="71"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="72"/>
+      <c r="X21" s="72"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="72"/>
+      <c r="AB21" s="72"/>
+      <c r="AC21" s="72"/>
+      <c r="AD21" s="72"/>
+      <c r="AE21" s="72"/>
+      <c r="AF21" s="72"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="72"/>
+      <c r="BA21" s="73"/>
+    </row>
+    <row r="22" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A22" s="71"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="72"/>
+      <c r="AC22" s="72"/>
+      <c r="AD22" s="72"/>
+      <c r="AE22" s="72"/>
+      <c r="AF22" s="72"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
+      <c r="BA22" s="73"/>
+    </row>
+    <row r="23" spans="1:53" ht="21.75" customHeight="1">
+      <c r="A23" s="71"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="72"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="72"/>
+      <c r="AD23" s="72"/>
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="72"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
+      <c r="AJ23" s="72"/>
+      <c r="AK23" s="72"/>
+      <c r="BA23" s="73"/>
+    </row>
+    <row r="24" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A24" s="71"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="72"/>
+      <c r="AC24" s="72"/>
+      <c r="AD24" s="72"/>
+      <c r="AE24" s="72"/>
+      <c r="AF24" s="72"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
+      <c r="AJ24" s="72"/>
+      <c r="AK24" s="72"/>
+      <c r="BA24" s="73"/>
+    </row>
+    <row r="25" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A25" s="214" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="215"/>
+      <c r="C25" s="215"/>
+      <c r="D25" s="215"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="215"/>
+      <c r="G25" s="215"/>
+      <c r="H25" s="215"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="215"/>
+      <c r="K25" s="215"/>
+      <c r="L25" s="215"/>
+      <c r="M25" s="215"/>
+      <c r="N25" s="215"/>
+      <c r="O25" s="215"/>
+      <c r="P25" s="215"/>
+      <c r="Q25" s="215"/>
+      <c r="R25" s="215"/>
+      <c r="S25" s="215"/>
+      <c r="T25" s="215"/>
+      <c r="U25" s="215"/>
+      <c r="V25" s="215"/>
+      <c r="W25" s="215"/>
+      <c r="X25" s="215"/>
+      <c r="Y25" s="215"/>
+      <c r="Z25" s="215"/>
+      <c r="AA25" s="215"/>
+      <c r="AB25" s="215"/>
+      <c r="AC25" s="215"/>
+      <c r="AD25" s="215"/>
+      <c r="AE25" s="215"/>
+      <c r="AF25" s="215"/>
+      <c r="AG25" s="215"/>
+      <c r="AH25" s="215"/>
+      <c r="AI25" s="215"/>
+      <c r="AJ25" s="215"/>
+      <c r="AK25" s="215"/>
+      <c r="AL25" s="215"/>
+      <c r="AM25" s="215"/>
+      <c r="AN25" s="215"/>
+      <c r="AO25" s="215"/>
+      <c r="AP25" s="215"/>
+      <c r="AQ25" s="215"/>
+      <c r="AR25" s="215"/>
+      <c r="AS25" s="215"/>
+      <c r="AT25" s="215"/>
+      <c r="AU25" s="215"/>
+      <c r="AV25" s="215"/>
+      <c r="AW25" s="215"/>
+      <c r="AX25" s="215"/>
+      <c r="AY25" s="215"/>
+      <c r="AZ25" s="215"/>
+      <c r="BA25" s="216"/>
+    </row>
+    <row r="26" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A26" s="74"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="75"/>
+      <c r="X26" s="75"/>
+      <c r="Y26" s="75"/>
+      <c r="Z26" s="75"/>
+      <c r="AA26" s="75"/>
+      <c r="AB26" s="75"/>
+      <c r="AC26" s="75"/>
+      <c r="AD26" s="75"/>
+      <c r="AE26" s="75"/>
+      <c r="AF26" s="75"/>
+      <c r="AG26" s="75"/>
+      <c r="AH26" s="75"/>
+      <c r="AI26" s="72"/>
+      <c r="AJ26" s="72"/>
+      <c r="AK26" s="72"/>
+      <c r="BA26" s="73"/>
+    </row>
+    <row r="27" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A27" s="71"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="72"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+      <c r="T27" s="72"/>
+      <c r="U27" s="72"/>
+      <c r="V27" s="72"/>
+      <c r="W27" s="72"/>
+      <c r="X27" s="72"/>
+      <c r="Y27" s="72"/>
+      <c r="Z27" s="72"/>
+      <c r="AA27" s="72"/>
+      <c r="AB27" s="72"/>
+      <c r="AC27" s="72"/>
+      <c r="AD27" s="72"/>
+      <c r="AE27" s="72"/>
+      <c r="AF27" s="72"/>
+      <c r="AG27" s="72"/>
+      <c r="AH27" s="72"/>
+      <c r="AI27" s="72"/>
+      <c r="AJ27" s="72"/>
+      <c r="AK27" s="72"/>
+      <c r="BA27" s="73"/>
+    </row>
+    <row r="28" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A28" s="71"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+      <c r="V28" s="72"/>
+      <c r="W28" s="72"/>
+      <c r="X28" s="72"/>
+      <c r="Y28" s="72"/>
+      <c r="Z28" s="72"/>
+      <c r="AA28" s="72"/>
+      <c r="AB28" s="72"/>
+      <c r="AC28" s="72"/>
+      <c r="AD28" s="72"/>
+      <c r="AE28" s="72"/>
+      <c r="AF28" s="72"/>
+      <c r="AG28" s="72"/>
+      <c r="AH28" s="72"/>
+      <c r="AI28" s="72"/>
+      <c r="AJ28" s="72"/>
+      <c r="AK28" s="72"/>
+      <c r="BA28" s="73"/>
+    </row>
+    <row r="29" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A29" s="71"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="72"/>
+      <c r="V29" s="72"/>
+      <c r="W29" s="72"/>
+      <c r="X29" s="72"/>
+      <c r="Y29" s="72"/>
+      <c r="Z29" s="72"/>
+      <c r="AA29" s="72"/>
+      <c r="AB29" s="72"/>
+      <c r="AC29" s="72"/>
+      <c r="AD29" s="72"/>
+      <c r="AE29" s="72"/>
+      <c r="AF29" s="72"/>
+      <c r="AG29" s="72"/>
+      <c r="AH29" s="72"/>
+      <c r="AI29" s="72"/>
+      <c r="AJ29" s="72"/>
+      <c r="AK29" s="72"/>
+      <c r="BA29" s="73"/>
+    </row>
+    <row r="30" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A30" s="71"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
+      <c r="X30" s="72"/>
+      <c r="Y30" s="72"/>
+      <c r="Z30" s="72"/>
+      <c r="AA30" s="72"/>
+      <c r="AB30" s="72"/>
+      <c r="AC30" s="72"/>
+      <c r="AD30" s="72"/>
+      <c r="AE30" s="72"/>
+      <c r="AF30" s="72"/>
+      <c r="AG30" s="72"/>
+      <c r="AH30" s="72"/>
+      <c r="AI30" s="72"/>
+      <c r="AJ30" s="72"/>
+      <c r="AK30" s="72"/>
+      <c r="BA30" s="73"/>
+    </row>
+    <row r="31" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A31" s="71"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="72"/>
+      <c r="W31" s="72"/>
+      <c r="X31" s="72"/>
+      <c r="Y31" s="72"/>
+      <c r="Z31" s="72"/>
+      <c r="AA31" s="72"/>
+      <c r="AB31" s="72"/>
+      <c r="AC31" s="72"/>
+      <c r="AD31" s="72"/>
+      <c r="AE31" s="72"/>
+      <c r="AF31" s="72"/>
+      <c r="AG31" s="72"/>
+      <c r="AH31" s="72"/>
+      <c r="AI31" s="72"/>
+      <c r="AJ31" s="72"/>
+      <c r="AK31" s="72"/>
+      <c r="BA31" s="73"/>
+    </row>
+    <row r="32" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A32" s="71"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="72"/>
+      <c r="AA32" s="72"/>
+      <c r="AB32" s="72"/>
+      <c r="AC32" s="72"/>
+      <c r="AD32" s="72"/>
+      <c r="AE32" s="72"/>
+      <c r="AF32" s="72"/>
+      <c r="AG32" s="72"/>
+      <c r="AH32" s="72"/>
+      <c r="AI32" s="72"/>
+      <c r="AJ32" s="72"/>
+      <c r="AK32" s="72"/>
+      <c r="BA32" s="73"/>
+    </row>
+    <row r="33" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A33" s="76"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+      <c r="M33" s="77"/>
+      <c r="N33" s="77"/>
+      <c r="O33" s="77"/>
+      <c r="P33" s="77"/>
+      <c r="Q33" s="77"/>
+      <c r="R33" s="77"/>
+      <c r="S33" s="77"/>
+      <c r="T33" s="77"/>
+      <c r="U33" s="77"/>
+      <c r="V33" s="77"/>
+      <c r="W33" s="77"/>
+      <c r="X33" s="77"/>
+      <c r="Y33" s="77"/>
+      <c r="Z33" s="77"/>
+      <c r="AA33" s="77"/>
+      <c r="AB33" s="77"/>
+      <c r="AC33" s="77"/>
+      <c r="AD33" s="77"/>
+      <c r="AE33" s="77"/>
+      <c r="AF33" s="77"/>
+      <c r="AG33" s="77"/>
+      <c r="AH33" s="77"/>
+      <c r="AI33" s="77"/>
+      <c r="AJ33" s="77"/>
+      <c r="AK33" s="72"/>
+      <c r="BA33" s="73"/>
+    </row>
+    <row r="34" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A34" s="214" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" s="215"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="215"/>
+      <c r="E34" s="215"/>
+      <c r="F34" s="215"/>
+      <c r="G34" s="215"/>
+      <c r="H34" s="215"/>
+      <c r="I34" s="215"/>
+      <c r="J34" s="215"/>
+      <c r="K34" s="215"/>
+      <c r="L34" s="215"/>
+      <c r="M34" s="215"/>
+      <c r="N34" s="215"/>
+      <c r="O34" s="215"/>
+      <c r="P34" s="215"/>
+      <c r="Q34" s="215"/>
+      <c r="R34" s="215"/>
+      <c r="S34" s="215"/>
+      <c r="T34" s="215"/>
+      <c r="U34" s="215"/>
+      <c r="V34" s="215"/>
+      <c r="W34" s="215"/>
+      <c r="X34" s="215"/>
+      <c r="Y34" s="215"/>
+      <c r="Z34" s="215"/>
+      <c r="AA34" s="215"/>
+      <c r="AB34" s="215"/>
+      <c r="AC34" s="215"/>
+      <c r="AD34" s="215"/>
+      <c r="AE34" s="215"/>
+      <c r="AF34" s="215"/>
+      <c r="AG34" s="215"/>
+      <c r="AH34" s="215"/>
+      <c r="AI34" s="215"/>
+      <c r="AJ34" s="215"/>
+      <c r="AK34" s="215"/>
+      <c r="AL34" s="215"/>
+      <c r="AM34" s="215"/>
+      <c r="AN34" s="215"/>
+      <c r="AO34" s="215"/>
+      <c r="AP34" s="215"/>
+      <c r="AQ34" s="215"/>
+      <c r="AR34" s="215"/>
+      <c r="AS34" s="215"/>
+      <c r="AT34" s="215"/>
+      <c r="AU34" s="215"/>
+      <c r="AV34" s="215"/>
+      <c r="AW34" s="215"/>
+      <c r="AX34" s="215"/>
+      <c r="AY34" s="215"/>
+      <c r="AZ34" s="215"/>
+      <c r="BA34" s="215"/>
+    </row>
+    <row r="35" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A35" s="74"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="75"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="75"/>
+      <c r="M35" s="75"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="75"/>
+      <c r="Q35" s="75"/>
+      <c r="R35" s="75"/>
+      <c r="S35" s="75"/>
+      <c r="T35" s="75"/>
+      <c r="U35" s="75"/>
+      <c r="V35" s="75"/>
+      <c r="W35" s="75"/>
+      <c r="X35" s="75"/>
+      <c r="Y35" s="75"/>
+      <c r="Z35" s="75"/>
+      <c r="AA35" s="75"/>
+      <c r="AB35" s="75"/>
+      <c r="AC35" s="75"/>
+      <c r="AD35" s="75"/>
+      <c r="AE35" s="75"/>
+      <c r="AF35" s="75"/>
+      <c r="AG35" s="75"/>
+      <c r="AH35" s="75"/>
+      <c r="AI35" s="75"/>
+      <c r="AJ35" s="75"/>
+      <c r="AK35" s="72"/>
+      <c r="BA35" s="73"/>
+    </row>
+    <row r="36" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A36" s="71"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+      <c r="T36" s="72"/>
+      <c r="U36" s="72"/>
+      <c r="V36" s="72"/>
+      <c r="W36" s="72"/>
+      <c r="X36" s="72"/>
+      <c r="Y36" s="72"/>
+      <c r="Z36" s="72"/>
+      <c r="AA36" s="72"/>
+      <c r="AB36" s="72"/>
+      <c r="AC36" s="72"/>
+      <c r="AD36" s="72"/>
+      <c r="AE36" s="72"/>
+      <c r="AF36" s="72"/>
+      <c r="AG36" s="72"/>
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="72"/>
+      <c r="AJ36" s="72"/>
+      <c r="AK36" s="72"/>
+      <c r="BA36" s="73"/>
+    </row>
+    <row r="37" spans="1:53" ht="21.95" customHeight="1">
+      <c r="A37" s="76"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="77"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="77"/>
+      <c r="M37" s="77"/>
+      <c r="N37" s="77"/>
+      <c r="O37" s="77"/>
+      <c r="P37" s="77"/>
+      <c r="Q37" s="77"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="77"/>
+      <c r="U37" s="77"/>
+      <c r="V37" s="77"/>
+      <c r="W37" s="77"/>
+      <c r="X37" s="77"/>
+      <c r="Y37" s="77"/>
+      <c r="Z37" s="77"/>
+      <c r="AA37" s="77"/>
+      <c r="AB37" s="77"/>
+      <c r="AC37" s="77"/>
+      <c r="AD37" s="77"/>
+      <c r="AE37" s="77"/>
+      <c r="AF37" s="77"/>
+      <c r="AG37" s="77"/>
+      <c r="AH37" s="77"/>
+      <c r="AI37" s="77"/>
+      <c r="AJ37" s="77"/>
+      <c r="AK37" s="77"/>
+      <c r="AL37" s="62"/>
+      <c r="AM37" s="62"/>
+      <c r="AN37" s="62"/>
+      <c r="AO37" s="62"/>
+      <c r="AP37" s="62"/>
+      <c r="AQ37" s="62"/>
+      <c r="AR37" s="62"/>
+      <c r="AS37" s="62"/>
+      <c r="AT37" s="62"/>
+      <c r="AU37" s="62"/>
+      <c r="AV37" s="62"/>
+      <c r="AW37" s="62"/>
+      <c r="AX37" s="62"/>
+      <c r="AY37" s="62"/>
+      <c r="AZ37" s="62"/>
+      <c r="BA37" s="78"/>
+    </row>
+    <row r="38" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="39" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="40" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="41" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="42" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="43" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="44" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="45" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="46" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="47" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="48" spans="1:53" ht="21.95" customHeight="1"/>
+    <row r="49" ht="21.95" customHeight="1"/>
+    <row r="50" ht="21.95" customHeight="1"/>
+    <row r="51" ht="21.95" customHeight="1"/>
+    <row r="52" ht="21.95" customHeight="1"/>
+    <row r="53" ht="21.95" customHeight="1"/>
+    <row r="54" ht="21.95" customHeight="1"/>
+    <row r="55" ht="21.95" customHeight="1"/>
+    <row r="56" ht="21.95" customHeight="1"/>
+    <row r="57" ht="21.95" customHeight="1"/>
+    <row r="58" ht="21.95" customHeight="1"/>
+    <row r="59" ht="21.95" customHeight="1"/>
+    <row r="60" ht="21.95" customHeight="1"/>
+    <row r="61" ht="21.95" customHeight="1"/>
+    <row r="62" ht="21.95" customHeight="1"/>
+    <row r="63" ht="21.95" customHeight="1"/>
+    <row r="64" ht="21.95" customHeight="1"/>
+    <row r="65" ht="21.95" customHeight="1"/>
+    <row r="66" ht="21.95" customHeight="1"/>
+    <row r="67" ht="21.95" customHeight="1"/>
+    <row r="68" ht="21.95" customHeight="1"/>
+    <row r="69" ht="21.95" customHeight="1"/>
+    <row r="70" ht="21.95" customHeight="1"/>
+    <row r="71" ht="21.95" customHeight="1"/>
+    <row r="72" ht="21.95" customHeight="1"/>
+    <row r="73" ht="21.95" customHeight="1"/>
+    <row r="74" ht="21.95" customHeight="1"/>
+    <row r="75" ht="21.95" customHeight="1"/>
+    <row r="76" ht="21.95" customHeight="1"/>
+    <row r="77" ht="21.95" customHeight="1"/>
+    <row r="78" ht="21.95" customHeight="1"/>
+    <row r="79" ht="21.95" customHeight="1"/>
+    <row r="80" ht="21.95" customHeight="1"/>
+    <row r="81" ht="21.95" customHeight="1"/>
+    <row r="82" ht="21.95" customHeight="1"/>
+    <row r="83" ht="21.95" customHeight="1"/>
+    <row r="84" ht="21.95" customHeight="1"/>
+    <row r="85" ht="21.95" customHeight="1"/>
+    <row r="86" ht="21.95" customHeight="1"/>
+    <row r="87" ht="21.95" customHeight="1"/>
+    <row r="88" ht="21.95" customHeight="1"/>
+    <row r="89" ht="21.95" customHeight="1"/>
+    <row r="90" ht="21.95" customHeight="1"/>
+    <row r="91" ht="21.95" customHeight="1"/>
+    <row r="92" ht="21.95" customHeight="1"/>
+    <row r="93" ht="21.95" customHeight="1"/>
+    <row r="94" ht="21.95" customHeight="1"/>
+    <row r="95" ht="21.95" customHeight="1"/>
+    <row r="96" ht="21.95" customHeight="1"/>
+    <row r="97" ht="21.95" customHeight="1"/>
+    <row r="98" ht="21.95" customHeight="1"/>
+    <row r="99" ht="21.95" customHeight="1"/>
+    <row r="100" ht="21.95" customHeight="1"/>
+    <row r="101" ht="21.95" customHeight="1"/>
+    <row r="102" ht="21.95" customHeight="1"/>
+    <row r="103" ht="18" customHeight="1"/>
+    <row r="104" ht="21.95" customHeight="1"/>
+    <row r="105" ht="21.95" customHeight="1"/>
+    <row r="106" ht="21.95" customHeight="1"/>
+    <row r="107" ht="21.95" customHeight="1"/>
+    <row r="108" ht="21.95" customHeight="1"/>
+    <row r="109" ht="21.95" customHeight="1"/>
+    <row r="110" ht="21.95" customHeight="1"/>
+    <row r="111" ht="87.75" customHeight="1"/>
+    <row r="112" ht="18" customHeight="1"/>
+    <row r="113" ht="21.95" customHeight="1"/>
+    <row r="114" ht="21.95" customHeight="1"/>
+    <row r="115" ht="21.95" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A9:BA9"/>
+    <mergeCell ref="A25:BA25"/>
+    <mergeCell ref="A34:BA34"/>
+    <mergeCell ref="AO1:AS1"/>
+    <mergeCell ref="AT1:BA1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:S5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:S6"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <dataValidations count="2">
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A10:AK24 N1:O1 I1:L1 A35:AK37 G5:G6 V1 AC1 AE1 A26:AK33" xr:uid="{7285EC31-B17E-4D7C-AB2D-B4F287840705}"/>
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{F7184FFA-F0BE-4178-8330-DC22A549836B}"/>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Documents/タスク編集設計書.xlsx
+++ b/Documents/タスク編集設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477E75AA-1030-4729-8A2E-AD07214BB930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28168027-0602-435C-8E2D-117614C2D403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6495" yWindow="300" windowWidth="11415" windowHeight="8955" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -19,20 +19,13 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
-    <sheet name="JUnitテスト仕様書兼報告書 (2)" sheetId="10" r:id="rId7"/>
-    <sheet name="カバレッジレポート" sheetId="11" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="ああ">#REF!</definedName>
-    <definedName name="範囲１" localSheetId="6">#REF!</definedName>
-    <definedName name="範囲１">#REF!</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -769,220 +762,48 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>JUnitテスト仕様書兼報告書</t>
-    <rPh sb="8" eb="11">
-      <t>シヨウショ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ホウコクショ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>システム名</t>
-    <rPh sb="4" eb="5">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>作成者</t>
-  </si>
-  <si>
-    <t>会社名</t>
-    <rPh sb="0" eb="3">
-      <t>カイシャメイ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>コンサイズ</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>サブシステム名</t>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>タスク一覧</t>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
+    <t>異常系</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>作成日</t>
-    <rPh sb="0" eb="3">
-      <t>サクセイビ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>実施者</t>
-    <rPh sb="0" eb="2">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>No</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>分類</t>
-    <rPh sb="0" eb="2">
-      <t>ブンルイ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>テストクラス</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>検証するメソッド</t>
-    <rPh sb="0" eb="2">
-      <t>ケンショウ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>期待する結果</t>
-    <rPh sb="0" eb="2">
-      <t>キタイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>実施日</t>
-    <rPh sb="0" eb="3">
-      <t>ジッシビ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>備考・特記事項</t>
-    <rPh sb="0" eb="2">
-      <t>ビコウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トッキ</t>
-    </rPh>
+    <t>ログアウト状態でのページ表示</t>
     <rPh sb="5" eb="7">
-      <t>ジコウ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>正常系</t>
-    <rPh sb="0" eb="3">
-      <t>セイジョウケイ</t>
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>TaskDAOTest</t>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>update()</t>
+    <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>count==1</t>
+    <t>http://localhost:8080/taskUN/task-edit.jsp</t>
     <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>カバレッジレポート</t>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>実施日</t>
-    <rPh sb="0" eb="3">
-      <t>ジッシビ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>（１）概要</t>
-    <rPh sb="3" eb="5">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>対象クラス</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>TaskDAO.Java</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>カバレッジ率</t>
-    <rPh sb="5" eb="6">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>（２）報告事項</t>
-    <rPh sb="3" eb="5">
-      <t>ホウコク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジコウ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>調査結果</t>
-    <rPh sb="0" eb="2">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>分析・考察</t>
-    <rPh sb="0" eb="2">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウサツ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
-  </si>
-  <si>
-    <t>備　考</t>
-    <rPh sb="0" eb="1">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>コウ</t>
-    </rPh>
-    <phoneticPr fontId="21"/>
   </si>
 </sst>
 </file>
@@ -992,7 +813,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1076,95 +897,8 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ 明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ 明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="ＭＳ 明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ＭＳ 明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1177,20 +911,8 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="77">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1850,256 +1572,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2244,97 +1723,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="72" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="73" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="74" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="75" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2647,137 +2035,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="71" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="71" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{6C10B5B7-E36B-40F5-9E99-A4A9558B5B5A}"/>
-    <cellStyle name="標準 2 2" xfId="5" xr:uid="{8FFEA0FA-F7CE-41FE-99C2-37F49EFBDA58}"/>
-    <cellStyle name="標準_生産計画ED書" xfId="3" xr:uid="{4DFE3633-1B59-43CE-8502-06E7AFD138DD}"/>
-    <cellStyle name="標準_東京理科大DBレイアウト" xfId="4" xr:uid="{ECCD0612-EF6C-4CEE-A273-74138412619D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3469,111 +2748,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>68036</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>176893</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>84365</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>13607</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{299333A8-2380-54B8-3613-2996A46A4ABE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1292679" y="2245179"/>
-          <a:ext cx="7772400" cy="3646714"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>68036</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>163243</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>132482</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>49193</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60EC6485-0A9A-3224-BE22-88C70F03FDF2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3333750" y="6585814"/>
-          <a:ext cx="3534268" cy="1790950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3781,85 +2955,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3879,46 +3053,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="81"/>
-      <c r="I13" s="79" t="s">
+      <c r="H13" s="50"/>
+      <c r="I13" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="80"/>
-      <c r="K13" s="81"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="79"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="81"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="50"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="79"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="81"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3927,13 +3101,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4948,19 +4122,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="110"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4972,190 +4146,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="117"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="123" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="124"/>
-      <c r="F2" s="123" t="s">
+      <c r="E2" s="93"/>
+      <c r="F2" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="124"/>
-      <c r="H2" s="127">
+      <c r="G2" s="93"/>
+      <c r="H2" s="96">
         <v>45806</v>
       </c>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="105"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="106"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="119"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="107"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="111" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="112"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="81"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="90" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="91"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="88"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="90" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="91"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="90" t="s">
+      <c r="B8" s="57"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="91"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="101" t="s">
+      <c r="C9" s="58"/>
+      <c r="D9" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="91"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="60"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="100" t="s">
+      <c r="A10" s="67"/>
+      <c r="B10" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="91"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="68"/>
+      <c r="B11" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="89"/>
-      <c r="D11" s="101" t="s">
+      <c r="C11" s="58"/>
+      <c r="D11" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="91"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="88"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="90" t="s">
+      <c r="B12" s="57"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="91"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="93"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="96"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6192,19 +5366,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="110"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -6216,46 +5390,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="117"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="123" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="124"/>
-      <c r="F2" s="123" t="s">
+      <c r="E2" s="93"/>
+      <c r="F2" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="124"/>
-      <c r="H2" s="127">
+      <c r="G2" s="93"/>
+      <c r="H2" s="96">
         <v>45806</v>
       </c>
-      <c r="I2" s="102"/>
-      <c r="J2" s="105"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="106"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="119"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="107"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -7612,19 +6786,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="144" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="145"/>
-      <c r="F1" s="144" t="s">
+      <c r="E1" s="114"/>
+      <c r="F1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="145"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7636,48 +6810,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="139"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="146" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="147"/>
-      <c r="F2" s="146" t="s">
+      <c r="E2" s="116"/>
+      <c r="F2" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="147"/>
-      <c r="H2" s="129">
+      <c r="G2" s="116"/>
+      <c r="H2" s="98">
         <v>45810</v>
       </c>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="133"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="139"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="134"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="141"/>
-      <c r="B4" s="142"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="135"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -9028,19 +8202,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="144" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="145"/>
-      <c r="F1" s="144" t="s">
+      <c r="E1" s="114"/>
+      <c r="F1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="145"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -9052,190 +8226,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="139"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="146" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="147"/>
-      <c r="F2" s="146">
+      <c r="E2" s="116"/>
+      <c r="F2" s="115">
         <v>56</v>
       </c>
-      <c r="G2" s="147"/>
-      <c r="H2" s="129">
+      <c r="G2" s="116"/>
+      <c r="H2" s="98">
         <v>45810</v>
       </c>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="133"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="139"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="134"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="139"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="148"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="134"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="103"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="151"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="154" t="s">
+      <c r="B5" s="120"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="155"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="156"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="125"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="157"/>
-      <c r="B7" s="158"/>
-      <c r="C7" s="158"/>
-      <c r="D7" s="158"/>
-      <c r="E7" s="158"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="158"/>
-      <c r="H7" s="158"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="159"/>
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="139"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="160"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="139"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="160"/>
+      <c r="A9" s="108"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="139"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="160"/>
+      <c r="A10" s="108"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="139"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="160"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="139"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="160"/>
+      <c r="A12" s="108"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="139"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="160"/>
+      <c r="A13" s="108"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="129"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="156"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="125"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="153" t="s">
+      <c r="A15" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="81"/>
-      <c r="D15" s="161" t="s">
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="81"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -9244,11 +8418,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="153" t="s">
+      <c r="A16" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="80"/>
-      <c r="C16" s="81"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -9261,18 +8435,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="162" t="s">
+      <c r="H16" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="80"/>
-      <c r="J16" s="156"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="125"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="152">
+      <c r="A17" s="121">
         <v>1</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="81"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="16" t="s">
         <v>69</v>
       </c>
@@ -9285,16 +8459,16 @@
       <c r="G17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="161"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="156"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="125"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="152">
+      <c r="A18" s="121">
         <v>2</v>
       </c>
-      <c r="B18" s="80"/>
-      <c r="C18" s="81"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="16" t="s">
         <v>75</v>
       </c>
@@ -9307,16 +8481,16 @@
       <c r="G18" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="161"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="156"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="125"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="152">
+      <c r="A19" s="121">
         <v>3</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="81"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="16" t="s">
         <v>76</v>
       </c>
@@ -9329,16 +8503,16 @@
       <c r="G19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="161"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="156"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="125"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="152">
+      <c r="A20" s="121">
         <v>4</v>
       </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="81"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="16" t="s">
         <v>77</v>
       </c>
@@ -9351,16 +8525,16 @@
       <c r="G20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="161"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="156"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="125"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="152">
+      <c r="A21" s="121">
         <v>5</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="16" t="s">
         <v>78</v>
       </c>
@@ -9373,16 +8547,16 @@
       <c r="G21" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="161"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="156"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="125"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="152">
+      <c r="A22" s="121">
         <v>6</v>
       </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="81"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="16" t="s">
         <v>71</v>
       </c>
@@ -9395,16 +8569,16 @@
       <c r="G22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="161"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="156"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="125"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="152">
+      <c r="A23" s="121">
         <v>7</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="81"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="18" t="s">
         <v>71</v>
       </c>
@@ -9417,9 +8591,9 @@
       <c r="G23" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="163"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="165"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10450,190 +9624,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="144" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="144" t="s">
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="144" t="s">
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="144" t="s">
+      <c r="P1" s="114"/>
+      <c r="Q1" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="145"/>
-      <c r="S1" s="144" t="s">
+      <c r="R1" s="114"/>
+      <c r="S1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="155"/>
+      <c r="T1" s="124"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="139"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="146" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="146" t="s">
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="171">
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="140">
         <v>45821</v>
       </c>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="146" t="s">
+      <c r="P2" s="116"/>
+      <c r="Q2" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="147"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="159"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="128"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="139"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="148"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="140"/>
-      <c r="O3" s="148"/>
-      <c r="P3" s="140"/>
-      <c r="Q3" s="148"/>
-      <c r="R3" s="140"/>
-      <c r="S3" s="148"/>
-      <c r="T3" s="160"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="129"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="141"/>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="149"/>
-      <c r="L4" s="142"/>
-      <c r="M4" s="142"/>
-      <c r="N4" s="143"/>
-      <c r="O4" s="149"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="149"/>
-      <c r="R4" s="143"/>
-      <c r="S4" s="149"/>
-      <c r="T4" s="172"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="141"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="174" t="s">
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="151"/>
-      <c r="M5" s="151"/>
-      <c r="N5" s="151"/>
-      <c r="O5" s="151"/>
-      <c r="P5" s="151"/>
-      <c r="Q5" s="151"/>
-      <c r="R5" s="151"/>
-      <c r="S5" s="151"/>
-      <c r="T5" s="155"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="124"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="161" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="80"/>
-      <c r="R6" s="80"/>
-      <c r="S6" s="80"/>
-      <c r="T6" s="156"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="125"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="161" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="80"/>
-      <c r="Q7" s="80"/>
-      <c r="R7" s="80"/>
-      <c r="S7" s="80"/>
-      <c r="T7" s="156"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="125"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -10832,37 +10006,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="153" t="s">
+      <c r="A15" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="81"/>
-      <c r="C15" s="180" t="s">
+      <c r="B15" s="50"/>
+      <c r="C15" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="162" t="s">
+      <c r="D15" s="50"/>
+      <c r="E15" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="81"/>
-      <c r="G15" s="162" t="s">
+      <c r="F15" s="50"/>
+      <c r="G15" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="80"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="162" t="s">
+      <c r="H15" s="49"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="81"/>
-      <c r="L15" s="162" t="s">
+      <c r="K15" s="50"/>
+      <c r="L15" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="80"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="162" t="s">
+      <c r="M15" s="49"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="131" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="81"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="50"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -10874,46 +10048,40 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="175">
+      <c r="A16" s="144">
         <v>1</v>
       </c>
-      <c r="B16" s="81"/>
-      <c r="C16" s="176" t="s">
+      <c r="B16" s="50"/>
+      <c r="C16" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="176" t="s">
+      <c r="D16" s="50"/>
+      <c r="E16" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="81"/>
-      <c r="G16" s="166" t="s">
+      <c r="F16" s="50"/>
+      <c r="G16" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="80"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="166" t="s">
+      <c r="H16" s="49"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="135" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="81"/>
-      <c r="L16" s="177" t="s">
+      <c r="K16" s="50"/>
+      <c r="L16" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="M16" s="178"/>
-      <c r="N16" s="179"/>
-      <c r="O16" s="169" t="s">
+      <c r="M16" s="147"/>
+      <c r="N16" s="148"/>
+      <c r="O16" s="138" t="s">
         <v>93</v>
       </c>
-      <c r="P16" s="80"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="61">
-        <v>45825</v>
-      </c>
-      <c r="S16" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="T16" s="33" t="s">
-        <v>128</v>
-      </c>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="33"/>
       <c r="U16" s="34"/>
       <c r="V16" s="34"/>
       <c r="W16" s="34"/>
@@ -10922,46 +10090,40 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="62.25" customHeight="1">
-      <c r="A17" s="175">
+      <c r="A17" s="144">
         <v>2</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="176" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="145" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="176" t="s">
+      <c r="D17" s="50"/>
+      <c r="E17" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="81"/>
-      <c r="G17" s="166" t="s">
+      <c r="F17" s="50"/>
+      <c r="G17" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="166" t="s">
+      <c r="H17" s="49"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="135" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="81"/>
-      <c r="L17" s="169" t="s">
+      <c r="K17" s="50"/>
+      <c r="L17" s="138" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="80"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="169" t="s">
+      <c r="M17" s="49"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="138" t="s">
         <v>99</v>
       </c>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="61">
-        <v>45825</v>
-      </c>
-      <c r="S17" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="T17" s="33" t="s">
-        <v>128</v>
-      </c>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="33"/>
       <c r="U17" s="34"/>
       <c r="V17" s="34"/>
       <c r="W17" s="34"/>
@@ -10970,46 +10132,40 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="54" customHeight="1">
-      <c r="A18" s="175">
+      <c r="A18" s="144">
         <v>3</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="176" t="s">
+      <c r="B18" s="50"/>
+      <c r="C18" s="145" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="176" t="s">
+      <c r="D18" s="50"/>
+      <c r="E18" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="166" t="s">
+      <c r="F18" s="50"/>
+      <c r="G18" s="135" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="80"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="166" t="s">
+      <c r="H18" s="49"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="135" t="s">
         <v>101</v>
       </c>
-      <c r="K18" s="81"/>
-      <c r="L18" s="169" t="s">
+      <c r="K18" s="50"/>
+      <c r="L18" s="138" t="s">
         <v>102</v>
       </c>
-      <c r="M18" s="80"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="169" t="s">
+      <c r="M18" s="49"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="138" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="61">
-        <v>45825</v>
-      </c>
-      <c r="S18" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>128</v>
-      </c>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="33"/>
       <c r="U18" s="34"/>
       <c r="V18" s="34"/>
       <c r="W18" s="34"/>
@@ -11018,46 +10174,40 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A19" s="175">
+      <c r="A19" s="144">
         <v>4</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="176" t="s">
+      <c r="B19" s="50"/>
+      <c r="C19" s="145" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="176" t="s">
+      <c r="D19" s="50"/>
+      <c r="E19" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="81"/>
-      <c r="G19" s="166" t="s">
+      <c r="F19" s="50"/>
+      <c r="G19" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="80"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="166" t="s">
+      <c r="H19" s="49"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="135" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="81"/>
-      <c r="L19" s="169" t="s">
+      <c r="K19" s="50"/>
+      <c r="L19" s="138" t="s">
         <v>102</v>
       </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="169" t="s">
+      <c r="M19" s="49"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="138" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="61">
-        <v>45825</v>
-      </c>
-      <c r="S19" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="T19" s="33" t="s">
-        <v>128</v>
-      </c>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="33"/>
       <c r="U19" s="34"/>
       <c r="V19" s="34"/>
       <c r="W19" s="34"/>
@@ -11066,26 +10216,40 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="57" customHeight="1">
-      <c r="A20" s="175"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="166"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="166"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="169"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="169"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="33"/>
+      <c r="A20" s="152">
+        <v>7</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="153" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="58"/>
+      <c r="E20" s="153" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="58"/>
+      <c r="G20" s="154" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="57"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="154" t="s">
+        <v>110</v>
+      </c>
+      <c r="K20" s="58"/>
+      <c r="L20" s="155" t="s">
+        <v>112</v>
+      </c>
+      <c r="M20" s="156"/>
+      <c r="N20" s="156"/>
+      <c r="O20" s="138" t="s">
+        <v>111</v>
+      </c>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="157"/>
+      <c r="S20" s="157"/>
+      <c r="T20" s="158"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -11094,23 +10258,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="175"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="176"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="166"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="169"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="169"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="81"/>
+      <c r="A21" s="144"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="138"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="50"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -11122,23 +10286,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="175"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="166"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="169"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="169"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="81"/>
+      <c r="A22" s="144"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="145"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="50"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -11150,23 +10314,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="175"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="169"/>
-      <c r="M23" s="80"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="169"/>
-      <c r="P23" s="80"/>
-      <c r="Q23" s="81"/>
+      <c r="A23" s="144"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="50"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -11178,23 +10342,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="175"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="166"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="166"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="169"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="169"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="81"/>
+      <c r="A24" s="144"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="50"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -11206,23 +10370,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="175"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="81"/>
-      <c r="E25" s="176"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="166"/>
-      <c r="K25" s="81"/>
-      <c r="L25" s="169"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="169"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="81"/>
+      <c r="A25" s="144"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="50"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="50"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -11234,23 +10398,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="175"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="166"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="166"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="169"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="169"/>
-      <c r="P26" s="80"/>
-      <c r="Q26" s="81"/>
+      <c r="A26" s="144"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="145"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="135"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="50"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -11262,23 +10426,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="175"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="176"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="166"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="166"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="169"/>
-      <c r="M27" s="80"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="169"/>
-      <c r="P27" s="80"/>
-      <c r="Q27" s="81"/>
+      <c r="A27" s="144"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="138"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="50"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -11290,23 +10454,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="175"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="166"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="166"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="169"/>
-      <c r="M28" s="80"/>
-      <c r="N28" s="81"/>
-      <c r="O28" s="169"/>
-      <c r="P28" s="80"/>
-      <c r="Q28" s="81"/>
+      <c r="A28" s="144"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="135"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="50"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -11318,23 +10482,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="175"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="166"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="166"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="169"/>
-      <c r="M29" s="80"/>
-      <c r="N29" s="81"/>
-      <c r="O29" s="169"/>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="81"/>
+      <c r="A29" s="144"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="50"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -11346,23 +10510,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="175"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="166"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="169"/>
-      <c r="M30" s="80"/>
-      <c r="N30" s="81"/>
-      <c r="O30" s="169"/>
-      <c r="P30" s="80"/>
-      <c r="Q30" s="81"/>
+      <c r="A30" s="144"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="145"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="49"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="50"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -11374,23 +10538,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="181"/>
-      <c r="B31" s="168"/>
-      <c r="C31" s="182"/>
-      <c r="D31" s="168"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="167"/>
-      <c r="H31" s="164"/>
-      <c r="I31" s="168"/>
-      <c r="J31" s="167"/>
-      <c r="K31" s="168"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="164"/>
-      <c r="N31" s="168"/>
-      <c r="O31" s="170"/>
-      <c r="P31" s="164"/>
-      <c r="Q31" s="168"/>
+      <c r="A31" s="150"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="151"/>
+      <c r="F31" s="137"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="133"/>
+      <c r="I31" s="137"/>
+      <c r="J31" s="136"/>
+      <c r="K31" s="137"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="133"/>
+      <c r="N31" s="137"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="133"/>
+      <c r="Q31" s="137"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -12526,2881 +11690,10 @@
     <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="L20" r:id="rId1" xr:uid="{29959F9C-D2C5-4624-BB77-C32F70D08F79}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20100C0A-C86A-4465-B785-9157351E8AB1}">
-  <dimension ref="A1:S52"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" style="49" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="60" customWidth="1"/>
-    <col min="3" max="6" width="8.140625" style="49" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="60" customWidth="1"/>
-    <col min="8" max="13" width="8.140625" style="49" customWidth="1"/>
-    <col min="14" max="19" width="12.140625" style="49" customWidth="1"/>
-    <col min="20" max="16384" width="8" style="49"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="192" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="193" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="196" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="O1" s="196" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" s="198"/>
-      <c r="Q1" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="R1" s="196" t="s">
-        <v>112</v>
-      </c>
-      <c r="S1" s="198"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="192"/>
-      <c r="B2" s="192"/>
-      <c r="C2" s="193" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="194"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="196" t="s">
-        <v>114</v>
-      </c>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="197"/>
-      <c r="L2" s="197"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="48" t="s">
-        <v>115</v>
-      </c>
-      <c r="O2" s="199">
-        <v>45818</v>
-      </c>
-      <c r="P2" s="200"/>
-      <c r="Q2" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="R2" s="201" t="s">
-        <v>56</v>
-      </c>
-      <c r="S2" s="202"/>
-    </row>
-    <row r="3" spans="1:19" ht="11.25" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-    </row>
-    <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="183" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="183" t="s">
-        <v>120</v>
-      </c>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
-      <c r="M4" s="185"/>
-      <c r="N4" s="183" t="s">
-        <v>121</v>
-      </c>
-      <c r="O4" s="184"/>
-      <c r="P4" s="185"/>
-      <c r="Q4" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="R4" s="183" t="s">
-        <v>123</v>
-      </c>
-      <c r="S4" s="185"/>
-    </row>
-    <row r="5" spans="1:19" ht="30" customHeight="1">
-      <c r="A5" s="55">
-        <v>1</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="186" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="186" t="s">
-        <v>126</v>
-      </c>
-      <c r="I5" s="186"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="186"/>
-      <c r="L5" s="186"/>
-      <c r="M5" s="186"/>
-      <c r="N5" s="187" t="s">
-        <v>127</v>
-      </c>
-      <c r="O5" s="188"/>
-      <c r="P5" s="189"/>
-      <c r="Q5" s="57">
-        <v>45824</v>
-      </c>
-      <c r="R5" s="190"/>
-      <c r="S5" s="191"/>
-    </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="203"/>
-      <c r="D6" s="203"/>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="208"/>
-      <c r="O6" s="209"/>
-      <c r="P6" s="210"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="207"/>
-      <c r="S6" s="207"/>
-    </row>
-    <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="58"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="203"/>
-      <c r="K7" s="203"/>
-      <c r="L7" s="203"/>
-      <c r="M7" s="203"/>
-      <c r="N7" s="204"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="206"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="207"/>
-      <c r="S7" s="207"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" customHeight="1">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="203"/>
-      <c r="H8" s="203"/>
-      <c r="I8" s="203"/>
-      <c r="J8" s="203"/>
-      <c r="K8" s="203"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="203"/>
-      <c r="N8" s="204"/>
-      <c r="O8" s="205"/>
-      <c r="P8" s="206"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
-    </row>
-    <row r="9" spans="1:19" ht="30" customHeight="1">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="203"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="203"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="203"/>
-      <c r="H9" s="203"/>
-      <c r="I9" s="203"/>
-      <c r="J9" s="203"/>
-      <c r="K9" s="203"/>
-      <c r="L9" s="203"/>
-      <c r="M9" s="203"/>
-      <c r="N9" s="204"/>
-      <c r="O9" s="205"/>
-      <c r="P9" s="206"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="207"/>
-      <c r="S9" s="207"/>
-    </row>
-    <row r="10" spans="1:19" ht="30" customHeight="1">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="203"/>
-      <c r="H10" s="211"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="212"/>
-      <c r="K10" s="212"/>
-      <c r="L10" s="212"/>
-      <c r="M10" s="213"/>
-      <c r="N10" s="204"/>
-      <c r="O10" s="205"/>
-      <c r="P10" s="206"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="207"/>
-      <c r="S10" s="207"/>
-    </row>
-    <row r="11" spans="1:19" ht="30" customHeight="1">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="203"/>
-      <c r="D11" s="203"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="211"/>
-      <c r="I11" s="212"/>
-      <c r="J11" s="212"/>
-      <c r="K11" s="212"/>
-      <c r="L11" s="212"/>
-      <c r="M11" s="213"/>
-      <c r="N11" s="204"/>
-      <c r="O11" s="205"/>
-      <c r="P11" s="206"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="207"/>
-      <c r="S11" s="207"/>
-    </row>
-    <row r="12" spans="1:19" ht="30" customHeight="1">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="211"/>
-      <c r="I12" s="212"/>
-      <c r="J12" s="212"/>
-      <c r="K12" s="212"/>
-      <c r="L12" s="212"/>
-      <c r="M12" s="213"/>
-      <c r="N12" s="204"/>
-      <c r="O12" s="205"/>
-      <c r="P12" s="206"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="207"/>
-      <c r="S12" s="207"/>
-    </row>
-    <row r="13" spans="1:19" ht="30" customHeight="1">
-      <c r="A13" s="58"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="211"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
-      <c r="M13" s="213"/>
-      <c r="N13" s="204"/>
-      <c r="O13" s="205"/>
-      <c r="P13" s="206"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="207"/>
-      <c r="S13" s="207"/>
-    </row>
-    <row r="14" spans="1:19" ht="30" customHeight="1">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="211"/>
-      <c r="I14" s="212"/>
-      <c r="J14" s="212"/>
-      <c r="K14" s="212"/>
-      <c r="L14" s="212"/>
-      <c r="M14" s="213"/>
-      <c r="N14" s="204"/>
-      <c r="O14" s="205"/>
-      <c r="P14" s="206"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="207"/>
-      <c r="S14" s="207"/>
-    </row>
-    <row r="15" spans="1:19" ht="30" customHeight="1">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="203"/>
-      <c r="H15" s="211"/>
-      <c r="I15" s="212"/>
-      <c r="J15" s="212"/>
-      <c r="K15" s="212"/>
-      <c r="L15" s="212"/>
-      <c r="M15" s="213"/>
-      <c r="N15" s="204"/>
-      <c r="O15" s="205"/>
-      <c r="P15" s="206"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="207"/>
-      <c r="S15" s="207"/>
-    </row>
-    <row r="16" spans="1:19" ht="30" customHeight="1">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="203"/>
-      <c r="G16" s="203"/>
-      <c r="H16" s="211"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="212"/>
-      <c r="L16" s="212"/>
-      <c r="M16" s="213"/>
-      <c r="N16" s="204"/>
-      <c r="O16" s="205"/>
-      <c r="P16" s="206"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="207"/>
-      <c r="S16" s="207"/>
-    </row>
-    <row r="17" spans="1:19" ht="30" customHeight="1">
-      <c r="A17" s="58"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="203"/>
-      <c r="H17" s="211"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="212"/>
-      <c r="L17" s="212"/>
-      <c r="M17" s="213"/>
-      <c r="N17" s="204"/>
-      <c r="O17" s="205"/>
-      <c r="P17" s="206"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="207"/>
-      <c r="S17" s="207"/>
-    </row>
-    <row r="18" spans="1:19" ht="30" customHeight="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="211"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212"/>
-      <c r="L18" s="212"/>
-      <c r="M18" s="213"/>
-      <c r="N18" s="204"/>
-      <c r="O18" s="205"/>
-      <c r="P18" s="206"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="207"/>
-      <c r="S18" s="207"/>
-    </row>
-    <row r="19" spans="1:19" ht="30" customHeight="1">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="203"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="203"/>
-      <c r="H19" s="211"/>
-      <c r="I19" s="212"/>
-      <c r="J19" s="212"/>
-      <c r="K19" s="212"/>
-      <c r="L19" s="212"/>
-      <c r="M19" s="213"/>
-      <c r="N19" s="204"/>
-      <c r="O19" s="205"/>
-      <c r="P19" s="206"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="207"/>
-      <c r="S19" s="207"/>
-    </row>
-    <row r="20" spans="1:19" ht="30" customHeight="1">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="203"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="203"/>
-      <c r="G20" s="203"/>
-      <c r="H20" s="211"/>
-      <c r="I20" s="212"/>
-      <c r="J20" s="212"/>
-      <c r="K20" s="212"/>
-      <c r="L20" s="212"/>
-      <c r="M20" s="213"/>
-      <c r="N20" s="204"/>
-      <c r="O20" s="205"/>
-      <c r="P20" s="206"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="207"/>
-      <c r="S20" s="207"/>
-    </row>
-    <row r="21" spans="1:19" ht="30" customHeight="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="203"/>
-      <c r="D21" s="203"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="203"/>
-      <c r="H21" s="211"/>
-      <c r="I21" s="212"/>
-      <c r="J21" s="212"/>
-      <c r="K21" s="212"/>
-      <c r="L21" s="212"/>
-      <c r="M21" s="213"/>
-      <c r="N21" s="204"/>
-      <c r="O21" s="205"/>
-      <c r="P21" s="206"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="207"/>
-      <c r="S21" s="207"/>
-    </row>
-    <row r="22" spans="1:19" ht="30" customHeight="1">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="211"/>
-      <c r="I22" s="212"/>
-      <c r="J22" s="212"/>
-      <c r="K22" s="212"/>
-      <c r="L22" s="212"/>
-      <c r="M22" s="213"/>
-      <c r="N22" s="204"/>
-      <c r="O22" s="205"/>
-      <c r="P22" s="206"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="207"/>
-      <c r="S22" s="207"/>
-    </row>
-    <row r="23" spans="1:19" ht="30" customHeight="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="203"/>
-      <c r="D23" s="203"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="203"/>
-      <c r="G23" s="203"/>
-      <c r="H23" s="211"/>
-      <c r="I23" s="212"/>
-      <c r="J23" s="212"/>
-      <c r="K23" s="212"/>
-      <c r="L23" s="212"/>
-      <c r="M23" s="213"/>
-      <c r="N23" s="204"/>
-      <c r="O23" s="205"/>
-      <c r="P23" s="206"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="207"/>
-      <c r="S23" s="207"/>
-    </row>
-    <row r="24" spans="1:19" ht="30" customHeight="1">
-      <c r="A24" s="58"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="203"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="203"/>
-      <c r="G24" s="203"/>
-      <c r="H24" s="211"/>
-      <c r="I24" s="212"/>
-      <c r="J24" s="212"/>
-      <c r="K24" s="212"/>
-      <c r="L24" s="212"/>
-      <c r="M24" s="213"/>
-      <c r="N24" s="204"/>
-      <c r="O24" s="205"/>
-      <c r="P24" s="206"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="207"/>
-      <c r="S24" s="207"/>
-    </row>
-    <row r="25" spans="1:19" ht="30" customHeight="1">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="203"/>
-      <c r="D25" s="203"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="203"/>
-      <c r="H25" s="211"/>
-      <c r="I25" s="212"/>
-      <c r="J25" s="212"/>
-      <c r="K25" s="212"/>
-      <c r="L25" s="212"/>
-      <c r="M25" s="213"/>
-      <c r="N25" s="204"/>
-      <c r="O25" s="205"/>
-      <c r="P25" s="206"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="207"/>
-      <c r="S25" s="207"/>
-    </row>
-    <row r="26" spans="1:19" ht="30" customHeight="1">
-      <c r="A26" s="58"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="211"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
-      <c r="M26" s="213"/>
-      <c r="N26" s="204"/>
-      <c r="O26" s="205"/>
-      <c r="P26" s="206"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="207"/>
-      <c r="S26" s="207"/>
-    </row>
-    <row r="27" spans="1:19" ht="30" customHeight="1">
-      <c r="A27" s="58"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="211"/>
-      <c r="I27" s="212"/>
-      <c r="J27" s="212"/>
-      <c r="K27" s="212"/>
-      <c r="L27" s="212"/>
-      <c r="M27" s="213"/>
-      <c r="N27" s="204"/>
-      <c r="O27" s="205"/>
-      <c r="P27" s="206"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="207"/>
-      <c r="S27" s="207"/>
-    </row>
-    <row r="28" spans="1:19" ht="30" customHeight="1">
-      <c r="A28" s="58"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="203"/>
-      <c r="D28" s="203"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="203"/>
-      <c r="G28" s="203"/>
-      <c r="H28" s="211"/>
-      <c r="I28" s="212"/>
-      <c r="J28" s="212"/>
-      <c r="K28" s="212"/>
-      <c r="L28" s="212"/>
-      <c r="M28" s="213"/>
-      <c r="N28" s="204"/>
-      <c r="O28" s="205"/>
-      <c r="P28" s="206"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="207"/>
-      <c r="S28" s="207"/>
-    </row>
-    <row r="29" spans="1:19" ht="30" customHeight="1">
-      <c r="A29" s="58"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="203"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="203"/>
-      <c r="H29" s="211"/>
-      <c r="I29" s="212"/>
-      <c r="J29" s="212"/>
-      <c r="K29" s="212"/>
-      <c r="L29" s="212"/>
-      <c r="M29" s="213"/>
-      <c r="N29" s="204"/>
-      <c r="O29" s="205"/>
-      <c r="P29" s="206"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="207"/>
-      <c r="S29" s="207"/>
-    </row>
-    <row r="30" spans="1:19" ht="30" customHeight="1">
-      <c r="A30" s="58"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="203"/>
-      <c r="G30" s="203"/>
-      <c r="H30" s="211"/>
-      <c r="I30" s="212"/>
-      <c r="J30" s="212"/>
-      <c r="K30" s="212"/>
-      <c r="L30" s="212"/>
-      <c r="M30" s="213"/>
-      <c r="N30" s="204"/>
-      <c r="O30" s="205"/>
-      <c r="P30" s="206"/>
-      <c r="Q30" s="58"/>
-      <c r="R30" s="207"/>
-      <c r="S30" s="207"/>
-    </row>
-    <row r="31" spans="1:19" ht="30" customHeight="1">
-      <c r="A31" s="58"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="203"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="203"/>
-      <c r="H31" s="211"/>
-      <c r="I31" s="212"/>
-      <c r="J31" s="212"/>
-      <c r="K31" s="212"/>
-      <c r="L31" s="212"/>
-      <c r="M31" s="213"/>
-      <c r="N31" s="204"/>
-      <c r="O31" s="205"/>
-      <c r="P31" s="206"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="207"/>
-      <c r="S31" s="207"/>
-    </row>
-    <row r="32" spans="1:19" ht="30" customHeight="1">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="203"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="203"/>
-      <c r="H32" s="211"/>
-      <c r="I32" s="212"/>
-      <c r="J32" s="212"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="212"/>
-      <c r="M32" s="213"/>
-      <c r="N32" s="204"/>
-      <c r="O32" s="205"/>
-      <c r="P32" s="206"/>
-      <c r="Q32" s="58"/>
-      <c r="R32" s="207"/>
-      <c r="S32" s="207"/>
-    </row>
-    <row r="33" spans="1:19" ht="30" customHeight="1">
-      <c r="A33" s="58"/>
-      <c r="B33" s="58"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="203"/>
-      <c r="H33" s="211"/>
-      <c r="I33" s="212"/>
-      <c r="J33" s="212"/>
-      <c r="K33" s="212"/>
-      <c r="L33" s="212"/>
-      <c r="M33" s="213"/>
-      <c r="N33" s="204"/>
-      <c r="O33" s="205"/>
-      <c r="P33" s="206"/>
-      <c r="Q33" s="58"/>
-      <c r="R33" s="207"/>
-      <c r="S33" s="207"/>
-    </row>
-    <row r="34" spans="1:19" ht="30" customHeight="1">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="203"/>
-      <c r="D34" s="203"/>
-      <c r="E34" s="203"/>
-      <c r="F34" s="203"/>
-      <c r="G34" s="203"/>
-      <c r="H34" s="211"/>
-      <c r="I34" s="212"/>
-      <c r="J34" s="212"/>
-      <c r="K34" s="212"/>
-      <c r="L34" s="212"/>
-      <c r="M34" s="213"/>
-      <c r="N34" s="204"/>
-      <c r="O34" s="205"/>
-      <c r="P34" s="206"/>
-      <c r="Q34" s="58"/>
-      <c r="R34" s="207"/>
-      <c r="S34" s="207"/>
-    </row>
-    <row r="35" spans="1:19" ht="30" customHeight="1">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="203"/>
-      <c r="D35" s="203"/>
-      <c r="E35" s="203"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="203"/>
-      <c r="H35" s="211"/>
-      <c r="I35" s="212"/>
-      <c r="J35" s="212"/>
-      <c r="K35" s="212"/>
-      <c r="L35" s="212"/>
-      <c r="M35" s="213"/>
-      <c r="N35" s="204"/>
-      <c r="O35" s="205"/>
-      <c r="P35" s="206"/>
-      <c r="Q35" s="58"/>
-      <c r="R35" s="207"/>
-      <c r="S35" s="207"/>
-    </row>
-    <row r="36" spans="1:19" ht="30" customHeight="1">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="211"/>
-      <c r="I36" s="212"/>
-      <c r="J36" s="212"/>
-      <c r="K36" s="212"/>
-      <c r="L36" s="212"/>
-      <c r="M36" s="213"/>
-      <c r="N36" s="204"/>
-      <c r="O36" s="205"/>
-      <c r="P36" s="206"/>
-      <c r="Q36" s="58"/>
-      <c r="R36" s="207"/>
-      <c r="S36" s="207"/>
-    </row>
-    <row r="37" spans="1:19" ht="30" customHeight="1">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="211"/>
-      <c r="I37" s="212"/>
-      <c r="J37" s="212"/>
-      <c r="K37" s="212"/>
-      <c r="L37" s="212"/>
-      <c r="M37" s="213"/>
-      <c r="N37" s="204"/>
-      <c r="O37" s="205"/>
-      <c r="P37" s="206"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="207"/>
-      <c r="S37" s="207"/>
-    </row>
-    <row r="38" spans="1:19" ht="30" customHeight="1">
-      <c r="A38" s="58"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="203"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="203"/>
-      <c r="F38" s="203"/>
-      <c r="G38" s="203"/>
-      <c r="H38" s="211"/>
-      <c r="I38" s="212"/>
-      <c r="J38" s="212"/>
-      <c r="K38" s="212"/>
-      <c r="L38" s="212"/>
-      <c r="M38" s="213"/>
-      <c r="N38" s="204"/>
-      <c r="O38" s="205"/>
-      <c r="P38" s="206"/>
-      <c r="Q38" s="58"/>
-      <c r="R38" s="207"/>
-      <c r="S38" s="207"/>
-    </row>
-    <row r="39" spans="1:19" ht="30" customHeight="1">
-      <c r="A39" s="58"/>
-      <c r="B39" s="58"/>
-      <c r="C39" s="203"/>
-      <c r="D39" s="203"/>
-      <c r="E39" s="203"/>
-      <c r="F39" s="203"/>
-      <c r="G39" s="203"/>
-      <c r="H39" s="211"/>
-      <c r="I39" s="212"/>
-      <c r="J39" s="212"/>
-      <c r="K39" s="212"/>
-      <c r="L39" s="212"/>
-      <c r="M39" s="213"/>
-      <c r="N39" s="204"/>
-      <c r="O39" s="205"/>
-      <c r="P39" s="206"/>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="207"/>
-      <c r="S39" s="207"/>
-    </row>
-    <row r="40" spans="1:19" ht="30" customHeight="1">
-      <c r="A40" s="58"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="203"/>
-      <c r="D40" s="203"/>
-      <c r="E40" s="203"/>
-      <c r="F40" s="203"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="211"/>
-      <c r="I40" s="212"/>
-      <c r="J40" s="212"/>
-      <c r="K40" s="212"/>
-      <c r="L40" s="212"/>
-      <c r="M40" s="213"/>
-      <c r="N40" s="204"/>
-      <c r="O40" s="205"/>
-      <c r="P40" s="206"/>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="207"/>
-      <c r="S40" s="207"/>
-    </row>
-    <row r="41" spans="1:19" ht="30" customHeight="1">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="203"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="203"/>
-      <c r="G41" s="203"/>
-      <c r="H41" s="211"/>
-      <c r="I41" s="212"/>
-      <c r="J41" s="212"/>
-      <c r="K41" s="212"/>
-      <c r="L41" s="212"/>
-      <c r="M41" s="213"/>
-      <c r="N41" s="204"/>
-      <c r="O41" s="205"/>
-      <c r="P41" s="206"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="207"/>
-      <c r="S41" s="207"/>
-    </row>
-    <row r="42" spans="1:19" ht="30" customHeight="1">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="203"/>
-      <c r="D42" s="203"/>
-      <c r="E42" s="203"/>
-      <c r="F42" s="203"/>
-      <c r="G42" s="203"/>
-      <c r="H42" s="211"/>
-      <c r="I42" s="212"/>
-      <c r="J42" s="212"/>
-      <c r="K42" s="212"/>
-      <c r="L42" s="212"/>
-      <c r="M42" s="213"/>
-      <c r="N42" s="204"/>
-      <c r="O42" s="205"/>
-      <c r="P42" s="206"/>
-      <c r="Q42" s="58"/>
-      <c r="R42" s="207"/>
-      <c r="S42" s="207"/>
-    </row>
-    <row r="43" spans="1:19" ht="30" customHeight="1">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="203"/>
-      <c r="D43" s="203"/>
-      <c r="E43" s="203"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="211"/>
-      <c r="I43" s="212"/>
-      <c r="J43" s="212"/>
-      <c r="K43" s="212"/>
-      <c r="L43" s="212"/>
-      <c r="M43" s="213"/>
-      <c r="N43" s="204"/>
-      <c r="O43" s="205"/>
-      <c r="P43" s="206"/>
-      <c r="Q43" s="58"/>
-      <c r="R43" s="207"/>
-      <c r="S43" s="207"/>
-    </row>
-    <row r="44" spans="1:19" ht="30" customHeight="1">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="203"/>
-      <c r="D44" s="203"/>
-      <c r="E44" s="203"/>
-      <c r="F44" s="203"/>
-      <c r="G44" s="203"/>
-      <c r="H44" s="211"/>
-      <c r="I44" s="212"/>
-      <c r="J44" s="212"/>
-      <c r="K44" s="212"/>
-      <c r="L44" s="212"/>
-      <c r="M44" s="213"/>
-      <c r="N44" s="204"/>
-      <c r="O44" s="205"/>
-      <c r="P44" s="206"/>
-      <c r="Q44" s="58"/>
-      <c r="R44" s="207"/>
-      <c r="S44" s="207"/>
-    </row>
-    <row r="45" spans="1:19" ht="30" customHeight="1">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="203"/>
-      <c r="D45" s="203"/>
-      <c r="E45" s="203"/>
-      <c r="F45" s="203"/>
-      <c r="G45" s="203"/>
-      <c r="H45" s="211"/>
-      <c r="I45" s="212"/>
-      <c r="J45" s="212"/>
-      <c r="K45" s="212"/>
-      <c r="L45" s="212"/>
-      <c r="M45" s="213"/>
-      <c r="N45" s="204"/>
-      <c r="O45" s="205"/>
-      <c r="P45" s="206"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="207"/>
-      <c r="S45" s="207"/>
-    </row>
-    <row r="46" spans="1:19" ht="30" customHeight="1">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="203"/>
-      <c r="D46" s="203"/>
-      <c r="E46" s="203"/>
-      <c r="F46" s="203"/>
-      <c r="G46" s="203"/>
-      <c r="H46" s="211"/>
-      <c r="I46" s="212"/>
-      <c r="J46" s="212"/>
-      <c r="K46" s="212"/>
-      <c r="L46" s="212"/>
-      <c r="M46" s="213"/>
-      <c r="N46" s="204"/>
-      <c r="O46" s="205"/>
-      <c r="P46" s="206"/>
-      <c r="Q46" s="58"/>
-      <c r="R46" s="207"/>
-      <c r="S46" s="207"/>
-    </row>
-    <row r="47" spans="1:19" ht="30" customHeight="1">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="203"/>
-      <c r="D47" s="203"/>
-      <c r="E47" s="203"/>
-      <c r="F47" s="203"/>
-      <c r="G47" s="203"/>
-      <c r="H47" s="211"/>
-      <c r="I47" s="212"/>
-      <c r="J47" s="212"/>
-      <c r="K47" s="212"/>
-      <c r="L47" s="212"/>
-      <c r="M47" s="213"/>
-      <c r="N47" s="204"/>
-      <c r="O47" s="205"/>
-      <c r="P47" s="206"/>
-      <c r="Q47" s="58"/>
-      <c r="R47" s="207"/>
-      <c r="S47" s="207"/>
-    </row>
-    <row r="48" spans="1:19" ht="30" customHeight="1">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="203"/>
-      <c r="D48" s="203"/>
-      <c r="E48" s="203"/>
-      <c r="F48" s="203"/>
-      <c r="G48" s="203"/>
-      <c r="H48" s="211"/>
-      <c r="I48" s="212"/>
-      <c r="J48" s="212"/>
-      <c r="K48" s="212"/>
-      <c r="L48" s="212"/>
-      <c r="M48" s="213"/>
-      <c r="N48" s="204"/>
-      <c r="O48" s="205"/>
-      <c r="P48" s="206"/>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="207"/>
-      <c r="S48" s="207"/>
-    </row>
-    <row r="49" spans="1:19" ht="30" customHeight="1">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="203"/>
-      <c r="D49" s="203"/>
-      <c r="E49" s="203"/>
-      <c r="F49" s="203"/>
-      <c r="G49" s="203"/>
-      <c r="H49" s="211"/>
-      <c r="I49" s="212"/>
-      <c r="J49" s="212"/>
-      <c r="K49" s="212"/>
-      <c r="L49" s="212"/>
-      <c r="M49" s="213"/>
-      <c r="N49" s="204"/>
-      <c r="O49" s="205"/>
-      <c r="P49" s="206"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="207"/>
-      <c r="S49" s="207"/>
-    </row>
-    <row r="50" spans="1:19" ht="30" customHeight="1">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="203"/>
-      <c r="D50" s="203"/>
-      <c r="E50" s="203"/>
-      <c r="F50" s="203"/>
-      <c r="G50" s="203"/>
-      <c r="H50" s="211"/>
-      <c r="I50" s="212"/>
-      <c r="J50" s="212"/>
-      <c r="K50" s="212"/>
-      <c r="L50" s="212"/>
-      <c r="M50" s="213"/>
-      <c r="N50" s="204"/>
-      <c r="O50" s="205"/>
-      <c r="P50" s="206"/>
-      <c r="Q50" s="58"/>
-      <c r="R50" s="207"/>
-      <c r="S50" s="207"/>
-    </row>
-    <row r="51" spans="1:19" ht="30" customHeight="1">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="203"/>
-      <c r="D51" s="203"/>
-      <c r="E51" s="203"/>
-      <c r="F51" s="203"/>
-      <c r="G51" s="203"/>
-      <c r="H51" s="211"/>
-      <c r="I51" s="212"/>
-      <c r="J51" s="212"/>
-      <c r="K51" s="212"/>
-      <c r="L51" s="212"/>
-      <c r="M51" s="213"/>
-      <c r="N51" s="204"/>
-      <c r="O51" s="205"/>
-      <c r="P51" s="206"/>
-      <c r="Q51" s="58"/>
-      <c r="R51" s="207"/>
-      <c r="S51" s="207"/>
-    </row>
-    <row r="52" spans="1:19" ht="30" customHeight="1">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="203"/>
-      <c r="D52" s="203"/>
-      <c r="E52" s="203"/>
-      <c r="F52" s="203"/>
-      <c r="G52" s="203"/>
-      <c r="H52" s="211"/>
-      <c r="I52" s="212"/>
-      <c r="J52" s="212"/>
-      <c r="K52" s="212"/>
-      <c r="L52" s="212"/>
-      <c r="M52" s="213"/>
-      <c r="N52" s="204"/>
-      <c r="O52" s="205"/>
-      <c r="P52" s="206"/>
-      <c r="Q52" s="58"/>
-      <c r="R52" s="207"/>
-      <c r="S52" s="207"/>
-    </row>
-  </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="R2:S2"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B200AB0-1F40-44FD-BC67-C6A716D65C8A}">
-  <dimension ref="A1:BA115"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="24.95" customHeight="1"/>
-  <cols>
-    <col min="1" max="2" width="3" style="67" customWidth="1"/>
-    <col min="3" max="3" width="3" style="68" customWidth="1"/>
-    <col min="4" max="5" width="3" style="67" customWidth="1"/>
-    <col min="6" max="6" width="3" style="68" customWidth="1"/>
-    <col min="7" max="16384" width="3" style="67"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:53" ht="30" customHeight="1">
-      <c r="A1" s="62"/>
-      <c r="B1" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="217" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP1" s="217"/>
-      <c r="AQ1" s="217"/>
-      <c r="AR1" s="217"/>
-      <c r="AS1" s="217"/>
-      <c r="AT1" s="218">
-        <v>45818</v>
-      </c>
-      <c r="AU1" s="219"/>
-      <c r="AV1" s="219"/>
-      <c r="AW1" s="219"/>
-      <c r="AX1" s="219"/>
-      <c r="AY1" s="219"/>
-      <c r="AZ1" s="219"/>
-      <c r="BA1" s="219"/>
-    </row>
-    <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
-    <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
-    <row r="4" spans="1:53" ht="18" customHeight="1">
-      <c r="A4" s="69" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="69"/>
-      <c r="Z4" s="69"/>
-      <c r="AA4" s="69"/>
-      <c r="AB4" s="69"/>
-      <c r="AC4" s="69"/>
-      <c r="AD4" s="69"/>
-      <c r="AE4" s="69"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="69"/>
-      <c r="AH4" s="69"/>
-      <c r="AI4" s="69"/>
-      <c r="AJ4" s="69"/>
-      <c r="AK4" s="69"/>
-    </row>
-    <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="214" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="215"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="215"/>
-      <c r="E5" s="215"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="220" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="221"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="221"/>
-      <c r="K5" s="221"/>
-      <c r="L5" s="221"/>
-      <c r="M5" s="221"/>
-      <c r="N5" s="221"/>
-      <c r="O5" s="221"/>
-      <c r="P5" s="221"/>
-      <c r="Q5" s="221"/>
-      <c r="R5" s="221"/>
-      <c r="S5" s="222"/>
-    </row>
-    <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="214" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="215"/>
-      <c r="C6" s="215"/>
-      <c r="D6" s="215"/>
-      <c r="E6" s="215"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="223">
-        <v>1</v>
-      </c>
-      <c r="H6" s="221"/>
-      <c r="I6" s="221"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="221"/>
-      <c r="O6" s="221"/>
-      <c r="P6" s="221"/>
-      <c r="Q6" s="221"/>
-      <c r="R6" s="221"/>
-      <c r="S6" s="222"/>
-    </row>
-    <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
-    <row r="8" spans="1:53" ht="18" customHeight="1">
-      <c r="A8" s="69" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="214" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="215"/>
-      <c r="C9" s="215"/>
-      <c r="D9" s="215"/>
-      <c r="E9" s="215"/>
-      <c r="F9" s="215"/>
-      <c r="G9" s="215"/>
-      <c r="H9" s="215"/>
-      <c r="I9" s="215"/>
-      <c r="J9" s="215"/>
-      <c r="K9" s="215"/>
-      <c r="L9" s="215"/>
-      <c r="M9" s="215"/>
-      <c r="N9" s="215"/>
-      <c r="O9" s="215"/>
-      <c r="P9" s="215"/>
-      <c r="Q9" s="215"/>
-      <c r="R9" s="215"/>
-      <c r="S9" s="215"/>
-      <c r="T9" s="215"/>
-      <c r="U9" s="215"/>
-      <c r="V9" s="215"/>
-      <c r="W9" s="215"/>
-      <c r="X9" s="215"/>
-      <c r="Y9" s="215"/>
-      <c r="Z9" s="215"/>
-      <c r="AA9" s="215"/>
-      <c r="AB9" s="215"/>
-      <c r="AC9" s="215"/>
-      <c r="AD9" s="215"/>
-      <c r="AE9" s="215"/>
-      <c r="AF9" s="215"/>
-      <c r="AG9" s="215"/>
-      <c r="AH9" s="215"/>
-      <c r="AI9" s="215"/>
-      <c r="AJ9" s="215"/>
-      <c r="AK9" s="215"/>
-      <c r="AL9" s="215"/>
-      <c r="AM9" s="215"/>
-      <c r="AN9" s="215"/>
-      <c r="AO9" s="215"/>
-      <c r="AP9" s="215"/>
-      <c r="AQ9" s="215"/>
-      <c r="AR9" s="215"/>
-      <c r="AS9" s="215"/>
-      <c r="AT9" s="215"/>
-      <c r="AU9" s="215"/>
-      <c r="AV9" s="215"/>
-      <c r="AW9" s="215"/>
-      <c r="AX9" s="215"/>
-      <c r="AY9" s="215"/>
-      <c r="AZ9" s="215"/>
-      <c r="BA9" s="216"/>
-    </row>
-    <row r="10" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="72"/>
-      <c r="AB10" s="72"/>
-      <c r="AC10" s="72"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="72"/>
-      <c r="AJ10" s="72"/>
-      <c r="AK10" s="72"/>
-      <c r="BA10" s="73"/>
-    </row>
-    <row r="11" spans="1:53" ht="21.75" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="72"/>
-      <c r="AB11" s="72"/>
-      <c r="AC11" s="72"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="72"/>
-      <c r="AF11" s="72"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="72"/>
-      <c r="AJ11" s="72"/>
-      <c r="AK11" s="72"/>
-      <c r="BA11" s="73"/>
-    </row>
-    <row r="12" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="72"/>
-      <c r="V12" s="72"/>
-      <c r="W12" s="72"/>
-      <c r="X12" s="72"/>
-      <c r="Y12" s="72"/>
-      <c r="Z12" s="72"/>
-      <c r="AA12" s="72"/>
-      <c r="AB12" s="72"/>
-      <c r="AC12" s="72"/>
-      <c r="AD12" s="72"/>
-      <c r="AE12" s="72"/>
-      <c r="AF12" s="72"/>
-      <c r="AG12" s="72"/>
-      <c r="AH12" s="72"/>
-      <c r="AI12" s="72"/>
-      <c r="AJ12" s="72"/>
-      <c r="AK12" s="72"/>
-      <c r="BA12" s="73"/>
-    </row>
-    <row r="13" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="72"/>
-      <c r="V13" s="72"/>
-      <c r="W13" s="72"/>
-      <c r="X13" s="72"/>
-      <c r="Y13" s="72"/>
-      <c r="Z13" s="72"/>
-      <c r="AA13" s="72"/>
-      <c r="AB13" s="72"/>
-      <c r="AC13" s="72"/>
-      <c r="AD13" s="72"/>
-      <c r="AE13" s="72"/>
-      <c r="AF13" s="72"/>
-      <c r="AG13" s="72"/>
-      <c r="AH13" s="72"/>
-      <c r="AI13" s="72"/>
-      <c r="AJ13" s="72"/>
-      <c r="AK13" s="72"/>
-      <c r="BA13" s="73"/>
-    </row>
-    <row r="14" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="72"/>
-      <c r="V14" s="72"/>
-      <c r="W14" s="72"/>
-      <c r="X14" s="72"/>
-      <c r="Y14" s="72"/>
-      <c r="Z14" s="72"/>
-      <c r="AA14" s="72"/>
-      <c r="AB14" s="72"/>
-      <c r="AC14" s="72"/>
-      <c r="AD14" s="72"/>
-      <c r="AE14" s="72"/>
-      <c r="AF14" s="72"/>
-      <c r="AG14" s="72"/>
-      <c r="AH14" s="72"/>
-      <c r="AI14" s="72"/>
-      <c r="AJ14" s="72"/>
-      <c r="AK14" s="72"/>
-      <c r="BA14" s="73"/>
-    </row>
-    <row r="15" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="72"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="72"/>
-      <c r="X15" s="72"/>
-      <c r="Y15" s="72"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="72"/>
-      <c r="AB15" s="72"/>
-      <c r="AC15" s="72"/>
-      <c r="AD15" s="72"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="72"/>
-      <c r="AG15" s="72"/>
-      <c r="AH15" s="72"/>
-      <c r="AI15" s="72"/>
-      <c r="AJ15" s="72"/>
-      <c r="AK15" s="72"/>
-      <c r="BA15" s="73"/>
-    </row>
-    <row r="16" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="72"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="72"/>
-      <c r="V16" s="72"/>
-      <c r="W16" s="72"/>
-      <c r="X16" s="72"/>
-      <c r="Y16" s="72"/>
-      <c r="Z16" s="72"/>
-      <c r="AA16" s="72"/>
-      <c r="AB16" s="72"/>
-      <c r="AC16" s="72"/>
-      <c r="AD16" s="72"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="72"/>
-      <c r="AG16" s="72"/>
-      <c r="AH16" s="72"/>
-      <c r="AI16" s="72"/>
-      <c r="AJ16" s="72"/>
-      <c r="AK16" s="72"/>
-      <c r="BA16" s="73"/>
-    </row>
-    <row r="17" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="72"/>
-      <c r="V17" s="72"/>
-      <c r="W17" s="72"/>
-      <c r="X17" s="72"/>
-      <c r="Y17" s="72"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="72"/>
-      <c r="AC17" s="72"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="72"/>
-      <c r="BA17" s="73"/>
-    </row>
-    <row r="18" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
-      <c r="U18" s="72"/>
-      <c r="V18" s="72"/>
-      <c r="W18" s="72"/>
-      <c r="X18" s="72"/>
-      <c r="Y18" s="72"/>
-      <c r="Z18" s="72"/>
-      <c r="AA18" s="72"/>
-      <c r="AB18" s="72"/>
-      <c r="AC18" s="72"/>
-      <c r="AD18" s="72"/>
-      <c r="AE18" s="72"/>
-      <c r="AF18" s="72"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="72"/>
-      <c r="AJ18" s="72"/>
-      <c r="AK18" s="72"/>
-      <c r="BA18" s="73"/>
-    </row>
-    <row r="19" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="72"/>
-      <c r="V19" s="72"/>
-      <c r="W19" s="72"/>
-      <c r="X19" s="72"/>
-      <c r="Y19" s="72"/>
-      <c r="Z19" s="72"/>
-      <c r="AA19" s="72"/>
-      <c r="AB19" s="72"/>
-      <c r="AC19" s="72"/>
-      <c r="AD19" s="72"/>
-      <c r="AE19" s="72"/>
-      <c r="AF19" s="72"/>
-      <c r="AG19" s="72"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="72"/>
-      <c r="AJ19" s="72"/>
-      <c r="AK19" s="72"/>
-      <c r="BA19" s="73"/>
-    </row>
-    <row r="20" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A20" s="71"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
-      <c r="U20" s="72"/>
-      <c r="V20" s="72"/>
-      <c r="W20" s="72"/>
-      <c r="X20" s="72"/>
-      <c r="Y20" s="72"/>
-      <c r="Z20" s="72"/>
-      <c r="AA20" s="72"/>
-      <c r="AB20" s="72"/>
-      <c r="AC20" s="72"/>
-      <c r="AD20" s="72"/>
-      <c r="AE20" s="72"/>
-      <c r="AF20" s="72"/>
-      <c r="AG20" s="72"/>
-      <c r="AH20" s="72"/>
-      <c r="AI20" s="72"/>
-      <c r="AJ20" s="72"/>
-      <c r="AK20" s="72"/>
-      <c r="BA20" s="73"/>
-    </row>
-    <row r="21" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A21" s="71"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="72"/>
-      <c r="V21" s="72"/>
-      <c r="W21" s="72"/>
-      <c r="X21" s="72"/>
-      <c r="Y21" s="72"/>
-      <c r="Z21" s="72"/>
-      <c r="AA21" s="72"/>
-      <c r="AB21" s="72"/>
-      <c r="AC21" s="72"/>
-      <c r="AD21" s="72"/>
-      <c r="AE21" s="72"/>
-      <c r="AF21" s="72"/>
-      <c r="AG21" s="72"/>
-      <c r="AH21" s="72"/>
-      <c r="AI21" s="72"/>
-      <c r="AJ21" s="72"/>
-      <c r="AK21" s="72"/>
-      <c r="BA21" s="73"/>
-    </row>
-    <row r="22" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A22" s="71"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
-      <c r="T22" s="72"/>
-      <c r="U22" s="72"/>
-      <c r="V22" s="72"/>
-      <c r="W22" s="72"/>
-      <c r="X22" s="72"/>
-      <c r="Y22" s="72"/>
-      <c r="Z22" s="72"/>
-      <c r="AA22" s="72"/>
-      <c r="AB22" s="72"/>
-      <c r="AC22" s="72"/>
-      <c r="AD22" s="72"/>
-      <c r="AE22" s="72"/>
-      <c r="AF22" s="72"/>
-      <c r="AG22" s="72"/>
-      <c r="AH22" s="72"/>
-      <c r="AI22" s="72"/>
-      <c r="AJ22" s="72"/>
-      <c r="AK22" s="72"/>
-      <c r="BA22" s="73"/>
-    </row>
-    <row r="23" spans="1:53" ht="21.75" customHeight="1">
-      <c r="A23" s="71"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="72"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="72"/>
-      <c r="X23" s="72"/>
-      <c r="Y23" s="72"/>
-      <c r="Z23" s="72"/>
-      <c r="AA23" s="72"/>
-      <c r="AB23" s="72"/>
-      <c r="AC23" s="72"/>
-      <c r="AD23" s="72"/>
-      <c r="AE23" s="72"/>
-      <c r="AF23" s="72"/>
-      <c r="AG23" s="72"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="72"/>
-      <c r="AJ23" s="72"/>
-      <c r="AK23" s="72"/>
-      <c r="BA23" s="73"/>
-    </row>
-    <row r="24" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
-      <c r="T24" s="72"/>
-      <c r="U24" s="72"/>
-      <c r="V24" s="72"/>
-      <c r="W24" s="72"/>
-      <c r="X24" s="72"/>
-      <c r="Y24" s="72"/>
-      <c r="Z24" s="72"/>
-      <c r="AA24" s="72"/>
-      <c r="AB24" s="72"/>
-      <c r="AC24" s="72"/>
-      <c r="AD24" s="72"/>
-      <c r="AE24" s="72"/>
-      <c r="AF24" s="72"/>
-      <c r="AG24" s="72"/>
-      <c r="AH24" s="72"/>
-      <c r="AI24" s="72"/>
-      <c r="AJ24" s="72"/>
-      <c r="AK24" s="72"/>
-      <c r="BA24" s="73"/>
-    </row>
-    <row r="25" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A25" s="214" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="215"/>
-      <c r="C25" s="215"/>
-      <c r="D25" s="215"/>
-      <c r="E25" s="215"/>
-      <c r="F25" s="215"/>
-      <c r="G25" s="215"/>
-      <c r="H25" s="215"/>
-      <c r="I25" s="215"/>
-      <c r="J25" s="215"/>
-      <c r="K25" s="215"/>
-      <c r="L25" s="215"/>
-      <c r="M25" s="215"/>
-      <c r="N25" s="215"/>
-      <c r="O25" s="215"/>
-      <c r="P25" s="215"/>
-      <c r="Q25" s="215"/>
-      <c r="R25" s="215"/>
-      <c r="S25" s="215"/>
-      <c r="T25" s="215"/>
-      <c r="U25" s="215"/>
-      <c r="V25" s="215"/>
-      <c r="W25" s="215"/>
-      <c r="X25" s="215"/>
-      <c r="Y25" s="215"/>
-      <c r="Z25" s="215"/>
-      <c r="AA25" s="215"/>
-      <c r="AB25" s="215"/>
-      <c r="AC25" s="215"/>
-      <c r="AD25" s="215"/>
-      <c r="AE25" s="215"/>
-      <c r="AF25" s="215"/>
-      <c r="AG25" s="215"/>
-      <c r="AH25" s="215"/>
-      <c r="AI25" s="215"/>
-      <c r="AJ25" s="215"/>
-      <c r="AK25" s="215"/>
-      <c r="AL25" s="215"/>
-      <c r="AM25" s="215"/>
-      <c r="AN25" s="215"/>
-      <c r="AO25" s="215"/>
-      <c r="AP25" s="215"/>
-      <c r="AQ25" s="215"/>
-      <c r="AR25" s="215"/>
-      <c r="AS25" s="215"/>
-      <c r="AT25" s="215"/>
-      <c r="AU25" s="215"/>
-      <c r="AV25" s="215"/>
-      <c r="AW25" s="215"/>
-      <c r="AX25" s="215"/>
-      <c r="AY25" s="215"/>
-      <c r="AZ25" s="215"/>
-      <c r="BA25" s="216"/>
-    </row>
-    <row r="26" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A26" s="74"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="75"/>
-      <c r="X26" s="75"/>
-      <c r="Y26" s="75"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="75"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="75"/>
-      <c r="AF26" s="75"/>
-      <c r="AG26" s="75"/>
-      <c r="AH26" s="75"/>
-      <c r="AI26" s="72"/>
-      <c r="AJ26" s="72"/>
-      <c r="AK26" s="72"/>
-      <c r="BA26" s="73"/>
-    </row>
-    <row r="27" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A27" s="71"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="72"/>
-      <c r="Q27" s="72"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="72"/>
-      <c r="T27" s="72"/>
-      <c r="U27" s="72"/>
-      <c r="V27" s="72"/>
-      <c r="W27" s="72"/>
-      <c r="X27" s="72"/>
-      <c r="Y27" s="72"/>
-      <c r="Z27" s="72"/>
-      <c r="AA27" s="72"/>
-      <c r="AB27" s="72"/>
-      <c r="AC27" s="72"/>
-      <c r="AD27" s="72"/>
-      <c r="AE27" s="72"/>
-      <c r="AF27" s="72"/>
-      <c r="AG27" s="72"/>
-      <c r="AH27" s="72"/>
-      <c r="AI27" s="72"/>
-      <c r="AJ27" s="72"/>
-      <c r="AK27" s="72"/>
-      <c r="BA27" s="73"/>
-    </row>
-    <row r="28" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A28" s="71"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
-      <c r="T28" s="72"/>
-      <c r="U28" s="72"/>
-      <c r="V28" s="72"/>
-      <c r="W28" s="72"/>
-      <c r="X28" s="72"/>
-      <c r="Y28" s="72"/>
-      <c r="Z28" s="72"/>
-      <c r="AA28" s="72"/>
-      <c r="AB28" s="72"/>
-      <c r="AC28" s="72"/>
-      <c r="AD28" s="72"/>
-      <c r="AE28" s="72"/>
-      <c r="AF28" s="72"/>
-      <c r="AG28" s="72"/>
-      <c r="AH28" s="72"/>
-      <c r="AI28" s="72"/>
-      <c r="AJ28" s="72"/>
-      <c r="AK28" s="72"/>
-      <c r="BA28" s="73"/>
-    </row>
-    <row r="29" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A29" s="71"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="72"/>
-      <c r="T29" s="72"/>
-      <c r="U29" s="72"/>
-      <c r="V29" s="72"/>
-      <c r="W29" s="72"/>
-      <c r="X29" s="72"/>
-      <c r="Y29" s="72"/>
-      <c r="Z29" s="72"/>
-      <c r="AA29" s="72"/>
-      <c r="AB29" s="72"/>
-      <c r="AC29" s="72"/>
-      <c r="AD29" s="72"/>
-      <c r="AE29" s="72"/>
-      <c r="AF29" s="72"/>
-      <c r="AG29" s="72"/>
-      <c r="AH29" s="72"/>
-      <c r="AI29" s="72"/>
-      <c r="AJ29" s="72"/>
-      <c r="AK29" s="72"/>
-      <c r="BA29" s="73"/>
-    </row>
-    <row r="30" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A30" s="71"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="72"/>
-      <c r="T30" s="72"/>
-      <c r="U30" s="72"/>
-      <c r="V30" s="72"/>
-      <c r="W30" s="72"/>
-      <c r="X30" s="72"/>
-      <c r="Y30" s="72"/>
-      <c r="Z30" s="72"/>
-      <c r="AA30" s="72"/>
-      <c r="AB30" s="72"/>
-      <c r="AC30" s="72"/>
-      <c r="AD30" s="72"/>
-      <c r="AE30" s="72"/>
-      <c r="AF30" s="72"/>
-      <c r="AG30" s="72"/>
-      <c r="AH30" s="72"/>
-      <c r="AI30" s="72"/>
-      <c r="AJ30" s="72"/>
-      <c r="AK30" s="72"/>
-      <c r="BA30" s="73"/>
-    </row>
-    <row r="31" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A31" s="71"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
-      <c r="T31" s="72"/>
-      <c r="U31" s="72"/>
-      <c r="V31" s="72"/>
-      <c r="W31" s="72"/>
-      <c r="X31" s="72"/>
-      <c r="Y31" s="72"/>
-      <c r="Z31" s="72"/>
-      <c r="AA31" s="72"/>
-      <c r="AB31" s="72"/>
-      <c r="AC31" s="72"/>
-      <c r="AD31" s="72"/>
-      <c r="AE31" s="72"/>
-      <c r="AF31" s="72"/>
-      <c r="AG31" s="72"/>
-      <c r="AH31" s="72"/>
-      <c r="AI31" s="72"/>
-      <c r="AJ31" s="72"/>
-      <c r="AK31" s="72"/>
-      <c r="BA31" s="73"/>
-    </row>
-    <row r="32" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="72"/>
-      <c r="Q32" s="72"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="72"/>
-      <c r="T32" s="72"/>
-      <c r="U32" s="72"/>
-      <c r="V32" s="72"/>
-      <c r="W32" s="72"/>
-      <c r="X32" s="72"/>
-      <c r="Y32" s="72"/>
-      <c r="Z32" s="72"/>
-      <c r="AA32" s="72"/>
-      <c r="AB32" s="72"/>
-      <c r="AC32" s="72"/>
-      <c r="AD32" s="72"/>
-      <c r="AE32" s="72"/>
-      <c r="AF32" s="72"/>
-      <c r="AG32" s="72"/>
-      <c r="AH32" s="72"/>
-      <c r="AI32" s="72"/>
-      <c r="AJ32" s="72"/>
-      <c r="AK32" s="72"/>
-      <c r="BA32" s="73"/>
-    </row>
-    <row r="33" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A33" s="76"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
-      <c r="K33" s="77"/>
-      <c r="L33" s="77"/>
-      <c r="M33" s="77"/>
-      <c r="N33" s="77"/>
-      <c r="O33" s="77"/>
-      <c r="P33" s="77"/>
-      <c r="Q33" s="77"/>
-      <c r="R33" s="77"/>
-      <c r="S33" s="77"/>
-      <c r="T33" s="77"/>
-      <c r="U33" s="77"/>
-      <c r="V33" s="77"/>
-      <c r="W33" s="77"/>
-      <c r="X33" s="77"/>
-      <c r="Y33" s="77"/>
-      <c r="Z33" s="77"/>
-      <c r="AA33" s="77"/>
-      <c r="AB33" s="77"/>
-      <c r="AC33" s="77"/>
-      <c r="AD33" s="77"/>
-      <c r="AE33" s="77"/>
-      <c r="AF33" s="77"/>
-      <c r="AG33" s="77"/>
-      <c r="AH33" s="77"/>
-      <c r="AI33" s="77"/>
-      <c r="AJ33" s="77"/>
-      <c r="AK33" s="72"/>
-      <c r="BA33" s="73"/>
-    </row>
-    <row r="34" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A34" s="214" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="215"/>
-      <c r="C34" s="215"/>
-      <c r="D34" s="215"/>
-      <c r="E34" s="215"/>
-      <c r="F34" s="215"/>
-      <c r="G34" s="215"/>
-      <c r="H34" s="215"/>
-      <c r="I34" s="215"/>
-      <c r="J34" s="215"/>
-      <c r="K34" s="215"/>
-      <c r="L34" s="215"/>
-      <c r="M34" s="215"/>
-      <c r="N34" s="215"/>
-      <c r="O34" s="215"/>
-      <c r="P34" s="215"/>
-      <c r="Q34" s="215"/>
-      <c r="R34" s="215"/>
-      <c r="S34" s="215"/>
-      <c r="T34" s="215"/>
-      <c r="U34" s="215"/>
-      <c r="V34" s="215"/>
-      <c r="W34" s="215"/>
-      <c r="X34" s="215"/>
-      <c r="Y34" s="215"/>
-      <c r="Z34" s="215"/>
-      <c r="AA34" s="215"/>
-      <c r="AB34" s="215"/>
-      <c r="AC34" s="215"/>
-      <c r="AD34" s="215"/>
-      <c r="AE34" s="215"/>
-      <c r="AF34" s="215"/>
-      <c r="AG34" s="215"/>
-      <c r="AH34" s="215"/>
-      <c r="AI34" s="215"/>
-      <c r="AJ34" s="215"/>
-      <c r="AK34" s="215"/>
-      <c r="AL34" s="215"/>
-      <c r="AM34" s="215"/>
-      <c r="AN34" s="215"/>
-      <c r="AO34" s="215"/>
-      <c r="AP34" s="215"/>
-      <c r="AQ34" s="215"/>
-      <c r="AR34" s="215"/>
-      <c r="AS34" s="215"/>
-      <c r="AT34" s="215"/>
-      <c r="AU34" s="215"/>
-      <c r="AV34" s="215"/>
-      <c r="AW34" s="215"/>
-      <c r="AX34" s="215"/>
-      <c r="AY34" s="215"/>
-      <c r="AZ34" s="215"/>
-      <c r="BA34" s="215"/>
-    </row>
-    <row r="35" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A35" s="74"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="75"/>
-      <c r="P35" s="75"/>
-      <c r="Q35" s="75"/>
-      <c r="R35" s="75"/>
-      <c r="S35" s="75"/>
-      <c r="T35" s="75"/>
-      <c r="U35" s="75"/>
-      <c r="V35" s="75"/>
-      <c r="W35" s="75"/>
-      <c r="X35" s="75"/>
-      <c r="Y35" s="75"/>
-      <c r="Z35" s="75"/>
-      <c r="AA35" s="75"/>
-      <c r="AB35" s="75"/>
-      <c r="AC35" s="75"/>
-      <c r="AD35" s="75"/>
-      <c r="AE35" s="75"/>
-      <c r="AF35" s="75"/>
-      <c r="AG35" s="75"/>
-      <c r="AH35" s="75"/>
-      <c r="AI35" s="75"/>
-      <c r="AJ35" s="75"/>
-      <c r="AK35" s="72"/>
-      <c r="BA35" s="73"/>
-    </row>
-    <row r="36" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A36" s="71"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="72"/>
-      <c r="P36" s="72"/>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
-      <c r="T36" s="72"/>
-      <c r="U36" s="72"/>
-      <c r="V36" s="72"/>
-      <c r="W36" s="72"/>
-      <c r="X36" s="72"/>
-      <c r="Y36" s="72"/>
-      <c r="Z36" s="72"/>
-      <c r="AA36" s="72"/>
-      <c r="AB36" s="72"/>
-      <c r="AC36" s="72"/>
-      <c r="AD36" s="72"/>
-      <c r="AE36" s="72"/>
-      <c r="AF36" s="72"/>
-      <c r="AG36" s="72"/>
-      <c r="AH36" s="72"/>
-      <c r="AI36" s="72"/>
-      <c r="AJ36" s="72"/>
-      <c r="AK36" s="72"/>
-      <c r="BA36" s="73"/>
-    </row>
-    <row r="37" spans="1:53" ht="21.95" customHeight="1">
-      <c r="A37" s="76"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="77"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="77"/>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
-      <c r="P37" s="77"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="77"/>
-      <c r="AE37" s="77"/>
-      <c r="AF37" s="77"/>
-      <c r="AG37" s="77"/>
-      <c r="AH37" s="77"/>
-      <c r="AI37" s="77"/>
-      <c r="AJ37" s="77"/>
-      <c r="AK37" s="77"/>
-      <c r="AL37" s="62"/>
-      <c r="AM37" s="62"/>
-      <c r="AN37" s="62"/>
-      <c r="AO37" s="62"/>
-      <c r="AP37" s="62"/>
-      <c r="AQ37" s="62"/>
-      <c r="AR37" s="62"/>
-      <c r="AS37" s="62"/>
-      <c r="AT37" s="62"/>
-      <c r="AU37" s="62"/>
-      <c r="AV37" s="62"/>
-      <c r="AW37" s="62"/>
-      <c r="AX37" s="62"/>
-      <c r="AY37" s="62"/>
-      <c r="AZ37" s="62"/>
-      <c r="BA37" s="78"/>
-    </row>
-    <row r="38" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="39" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="40" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="41" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="42" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="43" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="44" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="45" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="46" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="47" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="48" spans="1:53" ht="21.95" customHeight="1"/>
-    <row r="49" ht="21.95" customHeight="1"/>
-    <row r="50" ht="21.95" customHeight="1"/>
-    <row r="51" ht="21.95" customHeight="1"/>
-    <row r="52" ht="21.95" customHeight="1"/>
-    <row r="53" ht="21.95" customHeight="1"/>
-    <row r="54" ht="21.95" customHeight="1"/>
-    <row r="55" ht="21.95" customHeight="1"/>
-    <row r="56" ht="21.95" customHeight="1"/>
-    <row r="57" ht="21.95" customHeight="1"/>
-    <row r="58" ht="21.95" customHeight="1"/>
-    <row r="59" ht="21.95" customHeight="1"/>
-    <row r="60" ht="21.95" customHeight="1"/>
-    <row r="61" ht="21.95" customHeight="1"/>
-    <row r="62" ht="21.95" customHeight="1"/>
-    <row r="63" ht="21.95" customHeight="1"/>
-    <row r="64" ht="21.95" customHeight="1"/>
-    <row r="65" ht="21.95" customHeight="1"/>
-    <row r="66" ht="21.95" customHeight="1"/>
-    <row r="67" ht="21.95" customHeight="1"/>
-    <row r="68" ht="21.95" customHeight="1"/>
-    <row r="69" ht="21.95" customHeight="1"/>
-    <row r="70" ht="21.95" customHeight="1"/>
-    <row r="71" ht="21.95" customHeight="1"/>
-    <row r="72" ht="21.95" customHeight="1"/>
-    <row r="73" ht="21.95" customHeight="1"/>
-    <row r="74" ht="21.95" customHeight="1"/>
-    <row r="75" ht="21.95" customHeight="1"/>
-    <row r="76" ht="21.95" customHeight="1"/>
-    <row r="77" ht="21.95" customHeight="1"/>
-    <row r="78" ht="21.95" customHeight="1"/>
-    <row r="79" ht="21.95" customHeight="1"/>
-    <row r="80" ht="21.95" customHeight="1"/>
-    <row r="81" ht="21.95" customHeight="1"/>
-    <row r="82" ht="21.95" customHeight="1"/>
-    <row r="83" ht="21.95" customHeight="1"/>
-    <row r="84" ht="21.95" customHeight="1"/>
-    <row r="85" ht="21.95" customHeight="1"/>
-    <row r="86" ht="21.95" customHeight="1"/>
-    <row r="87" ht="21.95" customHeight="1"/>
-    <row r="88" ht="21.95" customHeight="1"/>
-    <row r="89" ht="21.95" customHeight="1"/>
-    <row r="90" ht="21.95" customHeight="1"/>
-    <row r="91" ht="21.95" customHeight="1"/>
-    <row r="92" ht="21.95" customHeight="1"/>
-    <row r="93" ht="21.95" customHeight="1"/>
-    <row r="94" ht="21.95" customHeight="1"/>
-    <row r="95" ht="21.95" customHeight="1"/>
-    <row r="96" ht="21.95" customHeight="1"/>
-    <row r="97" ht="21.95" customHeight="1"/>
-    <row r="98" ht="21.95" customHeight="1"/>
-    <row r="99" ht="21.95" customHeight="1"/>
-    <row r="100" ht="21.95" customHeight="1"/>
-    <row r="101" ht="21.95" customHeight="1"/>
-    <row r="102" ht="21.95" customHeight="1"/>
-    <row r="103" ht="18" customHeight="1"/>
-    <row r="104" ht="21.95" customHeight="1"/>
-    <row r="105" ht="21.95" customHeight="1"/>
-    <row r="106" ht="21.95" customHeight="1"/>
-    <row r="107" ht="21.95" customHeight="1"/>
-    <row r="108" ht="21.95" customHeight="1"/>
-    <row r="109" ht="21.95" customHeight="1"/>
-    <row r="110" ht="21.95" customHeight="1"/>
-    <row r="111" ht="87.75" customHeight="1"/>
-    <row r="112" ht="18" customHeight="1"/>
-    <row r="113" ht="21.95" customHeight="1"/>
-    <row r="114" ht="21.95" customHeight="1"/>
-    <row r="115" ht="21.95" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A9:BA9"/>
-    <mergeCell ref="A25:BA25"/>
-    <mergeCell ref="A34:BA34"/>
-    <mergeCell ref="AO1:AS1"/>
-    <mergeCell ref="AT1:BA1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:S5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:S6"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <dataValidations count="2">
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A10:AK24 N1:O1 I1:L1 A35:AK37 G5:G6 V1 AC1 AE1 A26:AK33" xr:uid="{7285EC31-B17E-4D7C-AB2D-B4F287840705}"/>
-    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{F7184FFA-F0BE-4178-8330-DC22A549836B}"/>
-  </dataValidations>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>